--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -265,12 +265,12 @@
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -280,39 +280,39 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
     <t>St. George Saints</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Rockdale City Suns</t>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
   </si>
   <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Ansan Greeners</t>
+    <t>Dalian Huayi</t>
   </si>
   <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
+    <t>Tallinna Kalev</t>
   </si>
   <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
@@ -334,72 +334,72 @@
     <t>AIK</t>
   </si>
   <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
     <t>Unión Santa Fe</t>
   </si>
   <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
     <t>Sarmiento</t>
   </si>
   <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
+    <t>Santiago Morning</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Santiago Morning</t>
-  </si>
-  <si>
     <t>Antofagasta</t>
   </si>
   <si>
@@ -412,12 +412,12 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
@@ -430,15 +430,15 @@
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Criciúma</t>
-  </si>
-  <si>
     <t>Guarani</t>
   </si>
   <si>
@@ -457,19 +457,22 @@
     <t>Deportes Temuco</t>
   </si>
   <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Caxias</t>
+  </si>
+  <si>
     <t>Figueirense</t>
   </si>
   <si>
+    <t>FC Cincinnati II</t>
+  </si>
+  <si>
     <t>York9 FC</t>
   </si>
   <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
+    <t>Inter Miami II</t>
   </si>
   <si>
     <t>St. Louis City</t>
@@ -478,27 +481,24 @@
     <t>Orlando City II</t>
   </si>
   <si>
-    <t>Inter Miami II</t>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Atlanta United II</t>
   </si>
   <si>
     <t>Cruzeiro</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Atlanta United II</t>
+    <t>San Jose Earthquakes II</t>
+  </si>
+  <si>
+    <t>Houston Dynamo FC II</t>
   </si>
   <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -508,39 +508,39 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>APIA Leichhardt Tigers</t>
+  </si>
+  <si>
     <t>St George City FA</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>APIA Leichhardt Tigers</t>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
   </si>
   <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Seoul E-Land</t>
+    <t>Nanjing City</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Nanjing City</t>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
@@ -562,72 +562,72 @@
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
   </si>
   <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
     <t>Independiente</t>
   </si>
   <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
     <t>San Luis</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Viking</t>
   </si>
   <si>
+    <t>San Miguel</t>
+  </si>
+  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
@@ -658,15 +658,15 @@
     <t>Chacarita Juniors</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
     <t>Ituano</t>
   </si>
   <si>
@@ -685,19 +685,22 @@
     <t>Concepción</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
     <t>Náutico</t>
   </si>
   <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
     <t>Valour FC</t>
   </si>
   <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
+    <t>Crown Legacy</t>
   </si>
   <si>
     <t>Portland Timbers</t>
@@ -706,25 +709,22 @@
     <t>Carolina Core</t>
   </si>
   <si>
-    <t>Crown Legacy</t>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Columbus Crew II</t>
   </si>
   <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Columbus Crew II</t>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>North Texas</t>
   </si>
   <si>
     <t>Whitecaps II</t>
-  </si>
-  <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1272,7 +1272,7 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S2">
         <v>2.62</v>
@@ -1284,7 +1284,7 @@
         <v>1.36</v>
       </c>
       <c r="V2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -1299,7 +1299,7 @@
         <v>1.3</v>
       </c>
       <c r="AA2">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AB2">
         <v>1.9</v>
@@ -1308,7 +1308,7 @@
         <v>1.81</v>
       </c>
       <c r="AD2">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AE2">
         <v>1.25</v>
@@ -1323,7 +1323,7 @@
         <v>7.5</v>
       </c>
       <c r="AI2">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ2" t="s">
         <v>240</v>
@@ -1370,76 +1370,76 @@
         <v>239</v>
       </c>
       <c r="L3">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q3">
+        <v>2.2</v>
+      </c>
+      <c r="R3">
+        <v>1.22</v>
+      </c>
+      <c r="S3">
+        <v>4</v>
+      </c>
+      <c r="T3">
         <v>2.1</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AC3">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ3" t="s">
         <v>240</v>
@@ -1486,22 +1486,22 @@
         <v>239</v>
       </c>
       <c r="L4">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="M4">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N4">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1534,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1620,22 +1620,22 @@
         <v>2.24</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>3.3</v>
       </c>
       <c r="T5">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U5">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1644,34 +1644,34 @@
         <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA5">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AB5">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC5">
         <v>2.25</v>
       </c>
       <c r="AD5">
+        <v>2.45</v>
+      </c>
+      <c r="AE5">
+        <v>1.5</v>
+      </c>
+      <c r="AF5">
+        <v>1.55</v>
+      </c>
+      <c r="AG5">
         <v>2.3</v>
       </c>
-      <c r="AE5">
-        <v>1.53</v>
-      </c>
-      <c r="AF5">
-        <v>1.49</v>
-      </c>
-      <c r="AG5">
-        <v>2.4</v>
-      </c>
       <c r="AH5">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AI5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>240</v>
@@ -1718,76 +1718,76 @@
         <v>239</v>
       </c>
       <c r="L6">
-        <v>2.09</v>
+        <v>4.1</v>
       </c>
       <c r="M6">
-        <v>3.29</v>
+        <v>4.1</v>
       </c>
       <c r="N6">
-        <v>2.83</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC6">
         <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>240</v>
@@ -1834,22 +1834,22 @@
         <v>239</v>
       </c>
       <c r="L7">
-        <v>2.09</v>
+        <v>3.84</v>
       </c>
       <c r="M7">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N7">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="O7">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P7">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="R7">
         <v>1.44</v>
@@ -1873,37 +1873,37 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AA7">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD7">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>240</v>
@@ -2066,22 +2066,22 @@
         <v>239</v>
       </c>
       <c r="L9">
-        <v>3.84</v>
+        <v>2.09</v>
       </c>
       <c r="M9">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>3.09</v>
       </c>
       <c r="O9">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2105,37 +2105,37 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Z9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AA9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AB9">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD9">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH9">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AI9">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>240</v>
@@ -2182,76 +2182,76 @@
         <v>239</v>
       </c>
       <c r="L10">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N10">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="O10">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P10">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S10">
+        <v>2.62</v>
+      </c>
+      <c r="T10">
         <v>2.55</v>
       </c>
-      <c r="T10">
+      <c r="U10">
+        <v>1.36</v>
+      </c>
+      <c r="V10">
+        <v>7.9</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>8.5</v>
+      </c>
+      <c r="Z10">
+        <v>1.34</v>
+      </c>
+      <c r="AA10">
         <v>3.04</v>
       </c>
-      <c r="U10">
-        <v>1.33</v>
-      </c>
-      <c r="V10">
-        <v>8</v>
-      </c>
-      <c r="W10">
-        <v>1.05</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>8</v>
-      </c>
-      <c r="Z10">
-        <v>1.36</v>
-      </c>
-      <c r="AA10">
-        <v>2.9</v>
-      </c>
       <c r="AB10">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AC10">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AD10">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH10">
-        <v>7.1</v>
+        <v>5.2</v>
       </c>
       <c r="AI10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="s">
         <v>240</v>
@@ -2298,76 +2298,76 @@
         <v>239</v>
       </c>
       <c r="L11">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N11">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="O11">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="P11">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="Q11">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S11">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="U11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V11">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
+        <v>1.08</v>
+      </c>
+      <c r="Y11">
+        <v>7.1</v>
+      </c>
+      <c r="Z11">
+        <v>1.46</v>
+      </c>
+      <c r="AA11">
+        <v>2.6</v>
+      </c>
+      <c r="AB11">
+        <v>2.32</v>
+      </c>
+      <c r="AC11">
+        <v>1.52</v>
+      </c>
+      <c r="AD11">
+        <v>4.2</v>
+      </c>
+      <c r="AE11">
+        <v>1.18</v>
+      </c>
+      <c r="AF11">
+        <v>2.06</v>
+      </c>
+      <c r="AG11">
+        <v>1.73</v>
+      </c>
+      <c r="AH11">
+        <v>8.5</v>
+      </c>
+      <c r="AI11">
         <v>1.04</v>
-      </c>
-      <c r="Y11">
-        <v>8.5</v>
-      </c>
-      <c r="Z11">
-        <v>1.29</v>
-      </c>
-      <c r="AA11">
-        <v>3</v>
-      </c>
-      <c r="AB11">
-        <v>2.02</v>
-      </c>
-      <c r="AC11">
-        <v>1.7</v>
-      </c>
-      <c r="AD11">
-        <v>3.58</v>
-      </c>
-      <c r="AE11">
-        <v>1.25</v>
-      </c>
-      <c r="AF11">
-        <v>1.85</v>
-      </c>
-      <c r="AG11">
-        <v>1.85</v>
-      </c>
-      <c r="AH11">
-        <v>6.5</v>
-      </c>
-      <c r="AI11">
-        <v>1.08</v>
       </c>
       <c r="AJ11" t="s">
         <v>240</v>
@@ -2387,7 +2387,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>86</v>
@@ -2414,76 +2414,76 @@
         <v>239</v>
       </c>
       <c r="L12">
+        <v>3.01</v>
+      </c>
+      <c r="M12">
+        <v>3.63</v>
+      </c>
+      <c r="N12">
+        <v>1.96</v>
+      </c>
+      <c r="O12">
+        <v>2.13</v>
+      </c>
+      <c r="P12">
+        <v>19</v>
+      </c>
+      <c r="Q12">
+        <v>1.68</v>
+      </c>
+      <c r="R12">
+        <v>1.29</v>
+      </c>
+      <c r="S12">
+        <v>3.4</v>
+      </c>
+      <c r="T12">
+        <v>2.25</v>
+      </c>
+      <c r="U12">
         <v>1.57</v>
       </c>
-      <c r="M12">
-        <v>3.75</v>
-      </c>
-      <c r="N12">
-        <v>4.75</v>
-      </c>
-      <c r="O12">
-        <v>1.4</v>
-      </c>
-      <c r="P12">
-        <v>10.75</v>
-      </c>
-      <c r="Q12">
-        <v>3.4</v>
-      </c>
-      <c r="R12">
-        <v>1.37</v>
-      </c>
-      <c r="S12">
-        <v>2.76</v>
-      </c>
-      <c r="T12">
-        <v>2.94</v>
-      </c>
-      <c r="U12">
-        <v>1.33</v>
-      </c>
       <c r="V12">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>8.5</v>
+        <v>13.8</v>
       </c>
       <c r="Z12">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AA12">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC12">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AD12">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AE12">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH12">
-        <v>7.7</v>
+        <v>3.9</v>
       </c>
       <c r="AI12">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
         <v>240</v>
@@ -2503,7 +2503,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>86</v>
@@ -2530,76 +2530,76 @@
         <v>239</v>
       </c>
       <c r="L13">
-        <v>3.01</v>
+        <v>1.57</v>
       </c>
       <c r="M13">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="N13">
-        <v>1.96</v>
+        <v>4.75</v>
       </c>
       <c r="O13">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="P13">
-        <v>19</v>
+        <v>10.75</v>
       </c>
       <c r="Q13">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S13">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="T13">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="U13">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="V13">
-        <v>4.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z13">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AA13">
-        <v>4.95</v>
+        <v>2.95</v>
       </c>
       <c r="AB13">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AC13">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD13">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="AE13">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AH13">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI13">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AJ13" t="s">
         <v>240</v>
@@ -2694,10 +2694,10 @@
         <v>4.2</v>
       </c>
       <c r="AB14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC14">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD14">
         <v>2.85</v>
@@ -3012,34 +3012,34 @@
         <v>2.2</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S17">
         <v>3.3</v>
       </c>
       <c r="T17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
         <v>1.55</v>
       </c>
       <c r="V17">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Z17">
         <v>1.18</v>
       </c>
       <c r="AA17">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AB17">
         <v>1.57</v>
@@ -3048,22 +3048,22 @@
         <v>2.15</v>
       </c>
       <c r="AD17">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AE17">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AF17">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AG17">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH17">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AI17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AJ17" t="s">
         <v>240</v>
@@ -3110,13 +3110,13 @@
         <v>239</v>
       </c>
       <c r="L18">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="M18">
-        <v>4.52</v>
+        <v>4</v>
       </c>
       <c r="N18">
-        <v>5.32</v>
+        <v>5.5</v>
       </c>
       <c r="O18">
         <v>1.41</v>
@@ -3131,7 +3131,7 @@
         <v>1.33</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="T18">
         <v>2.62</v>
@@ -3167,7 +3167,7 @@
         <v>2.92</v>
       </c>
       <c r="AE18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF18">
         <v>1.91</v>
@@ -3744,10 +3744,10 @@
         <v>2</v>
       </c>
       <c r="AD23">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AE23">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AF23">
         <v>1.5</v>
@@ -3779,7 +3779,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>86</v>
@@ -3806,76 +3806,76 @@
         <v>239</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ24" t="s">
         <v>240</v>
@@ -3895,7 +3895,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
         <v>86</v>
@@ -3922,76 +3922,76 @@
         <v>239</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ25" t="s">
         <v>240</v>
@@ -4038,28 +4038,28 @@
         <v>239</v>
       </c>
       <c r="L26">
-        <v>3.38</v>
+        <v>1.42</v>
       </c>
       <c r="M26">
-        <v>3.27</v>
+        <v>4.1</v>
       </c>
       <c r="N26">
-        <v>1.93</v>
+        <v>5.8</v>
       </c>
       <c r="O26">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q26">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
         <v>2.5</v>
@@ -4068,40 +4068,40 @@
         <v>1.5</v>
       </c>
       <c r="V26">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA26">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC26">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AD26">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="AE26">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH26">
         <v>5.25</v>
@@ -4591,7 +4591,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
         <v>86</v>
@@ -4618,76 +4618,76 @@
         <v>239</v>
       </c>
       <c r="L31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="s">
         <v>240</v>
@@ -5082,13 +5082,13 @@
         <v>239</v>
       </c>
       <c r="L35">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="M35">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N35">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="O35">
         <v>2.52</v>
@@ -5139,19 +5139,19 @@
         <v>4.15</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF35">
         <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH35">
         <v>8</v>
       </c>
       <c r="AI35">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ35" t="s">
         <v>240</v>
@@ -5519,7 +5519,7 @@
         <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>86</v>
@@ -5546,76 +5546,76 @@
         <v>239</v>
       </c>
       <c r="L39">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="s">
         <v>240</v>
@@ -5680,34 +5680,34 @@
         <v>2.63</v>
       </c>
       <c r="R40">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S40">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T40">
         <v>2.38</v>
       </c>
       <c r="U40">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V40">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z40">
         <v>1.2</v>
       </c>
       <c r="AA40">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB40">
         <v>1.61</v>
@@ -5716,16 +5716,16 @@
         <v>2.05</v>
       </c>
       <c r="AD40">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AE40">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AF40">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH40">
         <v>4.33</v>
@@ -5751,7 +5751,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D41" t="s">
         <v>86</v>
@@ -5778,76 +5778,76 @@
         <v>239</v>
       </c>
       <c r="L41">
-        <v>1.56</v>
+        <v>3.03</v>
       </c>
       <c r="M41">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="N41">
-        <v>4.3</v>
+        <v>2.11</v>
       </c>
       <c r="O41">
+        <v>2.3</v>
+      </c>
+      <c r="P41">
+        <v>7.8</v>
+      </c>
+      <c r="Q41">
+        <v>1.81</v>
+      </c>
+      <c r="R41">
         <v>1.44</v>
       </c>
-      <c r="P41">
-        <v>11</v>
-      </c>
-      <c r="Q41">
+      <c r="S41">
+        <v>2.6</v>
+      </c>
+      <c r="T41">
+        <v>3.1</v>
+      </c>
+      <c r="U41">
+        <v>1.33</v>
+      </c>
+      <c r="V41">
+        <v>8</v>
+      </c>
+      <c r="W41">
+        <v>1.05</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>7.9</v>
+      </c>
+      <c r="Z41">
+        <v>1.32</v>
+      </c>
+      <c r="AA41">
         <v>2.88</v>
       </c>
-      <c r="R41">
-        <v>1.3</v>
-      </c>
-      <c r="S41">
-        <v>3.4</v>
-      </c>
-      <c r="T41">
-        <v>2.5</v>
-      </c>
-      <c r="U41">
-        <v>1.5</v>
-      </c>
-      <c r="V41">
-        <v>6</v>
-      </c>
-      <c r="W41">
-        <v>1.13</v>
-      </c>
-      <c r="X41">
-        <v>1.04</v>
-      </c>
-      <c r="Y41">
-        <v>11</v>
-      </c>
-      <c r="Z41">
-        <v>1.22</v>
-      </c>
-      <c r="AA41">
-        <v>4.33</v>
-      </c>
       <c r="AB41">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AD41">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="AE41">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI41">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AJ41" t="s">
         <v>240</v>
@@ -5867,7 +5867,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
         <v>86</v>
@@ -5894,76 +5894,76 @@
         <v>239</v>
       </c>
       <c r="L42">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="M42">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N42">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="O42">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="P42">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="Q42">
-        <v>1.81</v>
+        <v>2.88</v>
       </c>
       <c r="R42">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S42">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z42">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AA42">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC42">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AD42">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI42">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AJ42" t="s">
         <v>240</v>
@@ -6010,13 +6010,13 @@
         <v>239</v>
       </c>
       <c r="L43">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="M43">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="N43">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="O43">
         <v>1.61</v>
@@ -6028,16 +6028,16 @@
         <v>2.61</v>
       </c>
       <c r="R43">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S43">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V43">
         <v>8</v>
@@ -6049,37 +6049,37 @@
         <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="Z43">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AA43">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AB43">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AC43">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AD43">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH43">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI43">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ43" t="s">
         <v>240</v>
@@ -6144,28 +6144,28 @@
         <v>3.6</v>
       </c>
       <c r="R44">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S44">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T44">
         <v>3.7</v>
       </c>
       <c r="U44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V44">
         <v>10</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y44">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z44">
         <v>1.53</v>
@@ -6174,28 +6174,28 @@
         <v>2.25</v>
       </c>
       <c r="AB44">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AC44">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AD44">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="AG44">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH44">
         <v>11</v>
       </c>
       <c r="AI44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ44" t="s">
         <v>240</v>
@@ -6263,25 +6263,25 @@
         <v>1.53</v>
       </c>
       <c r="S45">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="T45">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V45">
-        <v>9.6</v>
+        <v>9.75</v>
       </c>
       <c r="W45">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
         <v>1.1</v>
       </c>
       <c r="Y45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z45">
         <v>1.57</v>
@@ -6290,13 +6290,13 @@
         <v>2.2</v>
       </c>
       <c r="AB45">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC45">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AD45">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AE45">
         <v>1.15</v>
@@ -6305,13 +6305,13 @@
         <v>2.5</v>
       </c>
       <c r="AG45">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AH45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI45">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ45" t="s">
         <v>240</v>
@@ -6337,10 +6337,10 @@
         <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F46" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6528,10 +6528,10 @@
         <v>2.15</v>
       </c>
       <c r="AD47">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AE47">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AF47">
         <v>1.4</v>
@@ -6590,64 +6590,64 @@
         <v>239</v>
       </c>
       <c r="L48">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="M48">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="N48">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="O48">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R48">
+        <v>1.6</v>
+      </c>
+      <c r="S48">
+        <v>2.2</v>
+      </c>
+      <c r="T48">
+        <v>3.8</v>
+      </c>
+      <c r="U48">
+        <v>1.22</v>
+      </c>
+      <c r="V48">
+        <v>10</v>
+      </c>
+      <c r="W48">
+        <v>1.02</v>
+      </c>
+      <c r="X48">
+        <v>1.11</v>
+      </c>
+      <c r="Y48">
+        <v>5.5</v>
+      </c>
+      <c r="Z48">
         <v>1.57</v>
       </c>
-      <c r="S48">
-        <v>2.1</v>
-      </c>
-      <c r="T48">
-        <v>3.75</v>
-      </c>
-      <c r="U48">
-        <v>1.25</v>
-      </c>
-      <c r="V48">
-        <v>7.8</v>
-      </c>
-      <c r="W48">
-        <v>1.04</v>
-      </c>
-      <c r="X48">
-        <v>1.13</v>
-      </c>
-      <c r="Y48">
-        <v>5.44</v>
-      </c>
-      <c r="Z48">
-        <v>1.6</v>
-      </c>
       <c r="AA48">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB48">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AC48">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AD48">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
         <v>2.25</v>
@@ -6656,10 +6656,10 @@
         <v>1.57</v>
       </c>
       <c r="AH48">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AI48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ48" t="s">
         <v>240</v>
@@ -6706,70 +6706,70 @@
         <v>239</v>
       </c>
       <c r="L49">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="M49">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="N49">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="O49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R49">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S49">
         <v>2.2</v>
       </c>
       <c r="T49">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
+        <v>1.08</v>
+      </c>
+      <c r="Y49">
+        <v>5.5</v>
+      </c>
+      <c r="Z49">
+        <v>1.58</v>
+      </c>
+      <c r="AA49">
+        <v>2.2</v>
+      </c>
+      <c r="AB49">
+        <v>2.37</v>
+      </c>
+      <c r="AC49">
+        <v>1.48</v>
+      </c>
+      <c r="AD49">
+        <v>5</v>
+      </c>
+      <c r="AE49">
         <v>1.13</v>
       </c>
-      <c r="Y49">
-        <v>5.75</v>
-      </c>
-      <c r="Z49">
-        <v>1.57</v>
-      </c>
-      <c r="AA49">
-        <v>2.15</v>
-      </c>
-      <c r="AB49">
-        <v>2.78</v>
-      </c>
-      <c r="AC49">
-        <v>1.34</v>
-      </c>
-      <c r="AD49">
-        <v>5.5</v>
-      </c>
-      <c r="AE49">
-        <v>1.11</v>
-      </c>
       <c r="AF49">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG49">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH49">
         <v>11.5</v>
@@ -6840,28 +6840,28 @@
         <v>2.88</v>
       </c>
       <c r="R50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S50">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="T50">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V50">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W50">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y50">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Z50">
         <v>1.53</v>
@@ -6870,28 +6870,28 @@
         <v>2.25</v>
       </c>
       <c r="AB50">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AC50">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AD50">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG50">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH50">
         <v>10</v>
       </c>
       <c r="AI50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ50" t="s">
         <v>240</v>
@@ -7078,13 +7078,13 @@
         <v>2</v>
       </c>
       <c r="T52">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U52">
         <v>1.18</v>
       </c>
       <c r="V52">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="W52">
         <v>1</v>
@@ -7105,25 +7105,25 @@
         <v>3.3</v>
       </c>
       <c r="AC52">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD52">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="AE52">
         <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AG52">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AH52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ52" t="s">
         <v>240</v>
@@ -7188,28 +7188,28 @@
         <v>2.75</v>
       </c>
       <c r="R53">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="S53">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="T53">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U53">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y53">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Z53">
         <v>1.65</v>
@@ -7218,28 +7218,28 @@
         <v>2.05</v>
       </c>
       <c r="AB53">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AC53">
         <v>1.36</v>
       </c>
       <c r="AD53">
-        <v>6.74</v>
+        <v>5.5</v>
       </c>
       <c r="AE53">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AG53">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AH53">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ53" t="s">
         <v>240</v>
@@ -7259,7 +7259,7 @@
         <v>56</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
         <v>86</v>
@@ -7286,76 +7286,76 @@
         <v>239</v>
       </c>
       <c r="L54">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="M54">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="N54">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="O54">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q54">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R54">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="S54">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="T54">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="U54">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="V54">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y54">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="Z54">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AA54">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="AB54">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC54">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AD54">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AE54">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG54">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH54">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AI54">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ54" t="s">
         <v>240</v>
@@ -7375,7 +7375,7 @@
         <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
         <v>86</v>
@@ -7402,52 +7402,52 @@
         <v>239</v>
       </c>
       <c r="L55">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="M55">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N55">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O55">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="P55">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R55">
         <v>1.5</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T55">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U55">
         <v>1.3</v>
       </c>
       <c r="V55">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W55">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y55">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z55">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AA55">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB55">
         <v>2.25</v>
@@ -7456,19 +7456,19 @@
         <v>1.57</v>
       </c>
       <c r="AD55">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AE55">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF55">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AG55">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AH55">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AI55">
         <v>1.05</v>
@@ -7491,7 +7491,7 @@
         <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
         <v>86</v>
@@ -7518,76 +7518,76 @@
         <v>239</v>
       </c>
       <c r="L56">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="M56">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="N56">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="O56">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="P56">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R56">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="S56">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>1.99</v>
       </c>
       <c r="U56">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="V56">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X56">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="Z56">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AA56">
-        <v>2.47</v>
+        <v>6</v>
       </c>
       <c r="AB56">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC56">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD56">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE56">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AF56">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="AG56">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AH56">
-        <v>11</v>
+        <v>2.92</v>
       </c>
       <c r="AI56">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AJ56" t="s">
         <v>240</v>
@@ -7607,16 +7607,16 @@
         <v>57</v>
       </c>
       <c r="C57" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
         <v>86</v>
       </c>
       <c r="E57" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7634,28 +7634,28 @@
         <v>239</v>
       </c>
       <c r="L57">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="M57">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N57">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="O57">
+        <v>1.62</v>
+      </c>
+      <c r="P57">
+        <v>7.5</v>
+      </c>
+      <c r="Q57">
+        <v>3</v>
+      </c>
+      <c r="R57">
         <v>1.5</v>
       </c>
-      <c r="P57">
-        <v>6.5</v>
-      </c>
-      <c r="Q57">
-        <v>3.25</v>
-      </c>
-      <c r="R57">
-        <v>1.53</v>
-      </c>
       <c r="S57">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="T57">
         <v>3.5</v>
@@ -7664,46 +7664,46 @@
         <v>1.29</v>
       </c>
       <c r="V57">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
         <v>1.09</v>
       </c>
       <c r="Y57">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z57">
+        <v>1.43</v>
+      </c>
+      <c r="AA57">
+        <v>2.4</v>
+      </c>
+      <c r="AB57">
+        <v>2.37</v>
+      </c>
+      <c r="AC57">
         <v>1.48</v>
-      </c>
-      <c r="AA57">
-        <v>2.6</v>
-      </c>
-      <c r="AB57">
-        <v>2.5</v>
-      </c>
-      <c r="AC57">
-        <v>1.5</v>
       </c>
       <c r="AD57">
         <v>4.75</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF57">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG57">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH57">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI57">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ57" t="s">
         <v>240</v>
@@ -7723,16 +7723,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="F58" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7750,7 +7750,7 @@
         <v>239</v>
       </c>
       <c r="L58">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M58">
         <v>3</v>
@@ -7759,67 +7759,67 @@
         <v>3.25</v>
       </c>
       <c r="O58">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P58">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="Q58">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R58">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="S58">
+        <v>2.47</v>
+      </c>
+      <c r="T58">
+        <v>3.3</v>
+      </c>
+      <c r="U58">
+        <v>1.29</v>
+      </c>
+      <c r="V58">
+        <v>9</v>
+      </c>
+      <c r="W58">
+        <v>1.03</v>
+      </c>
+      <c r="X58">
+        <v>1.08</v>
+      </c>
+      <c r="Y58">
+        <v>7.1</v>
+      </c>
+      <c r="Z58">
+        <v>1.43</v>
+      </c>
+      <c r="AA58">
+        <v>2.69</v>
+      </c>
+      <c r="AB58">
         <v>2.25</v>
       </c>
-      <c r="T58">
-        <v>3.75</v>
-      </c>
-      <c r="U58">
-        <v>1.25</v>
-      </c>
-      <c r="V58">
-        <v>11</v>
-      </c>
-      <c r="W58">
-        <v>1.05</v>
-      </c>
-      <c r="X58">
-        <v>1.11</v>
-      </c>
-      <c r="Y58">
-        <v>6.25</v>
-      </c>
-      <c r="Z58">
-        <v>1.5</v>
-      </c>
-      <c r="AA58">
-        <v>2.38</v>
-      </c>
-      <c r="AB58">
-        <v>2.6</v>
-      </c>
       <c r="AC58">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AD58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE58">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF58">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AG58">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH58">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="AI58">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ58" t="s">
         <v>240</v>
@@ -7839,16 +7839,16 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D59" t="s">
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7869,73 +7869,73 @@
         <v>1.8</v>
       </c>
       <c r="M59">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="O59">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P59">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q59">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R59">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S59">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T59">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U59">
         <v>1.29</v>
       </c>
       <c r="V59">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="W59">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y59">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z59">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AA59">
+        <v>2.6</v>
+      </c>
+      <c r="AB59">
         <v>2.5</v>
       </c>
-      <c r="AB59">
-        <v>2.37</v>
-      </c>
       <c r="AC59">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD59">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AE59">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF59">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG59">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH59">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI59">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ59" t="s">
         <v>240</v>
@@ -7955,16 +7955,16 @@
         <v>57</v>
       </c>
       <c r="C60" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D60" t="s">
         <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="F60" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7982,73 +7982,73 @@
         <v>239</v>
       </c>
       <c r="L60">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M60">
         <v>3</v>
       </c>
       <c r="N60">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O60">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P60">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="Q60">
+        <v>2.4</v>
+      </c>
+      <c r="R60">
+        <v>1.57</v>
+      </c>
+      <c r="S60">
         <v>2.25</v>
       </c>
-      <c r="R60">
+      <c r="T60">
+        <v>3.75</v>
+      </c>
+      <c r="U60">
+        <v>1.25</v>
+      </c>
+      <c r="V60">
+        <v>11</v>
+      </c>
+      <c r="W60">
+        <v>1.05</v>
+      </c>
+      <c r="X60">
+        <v>1.11</v>
+      </c>
+      <c r="Y60">
+        <v>6.25</v>
+      </c>
+      <c r="Z60">
         <v>1.5</v>
       </c>
-      <c r="S60">
-        <v>2.4</v>
-      </c>
-      <c r="T60">
-        <v>3.22</v>
-      </c>
-      <c r="U60">
-        <v>1.3</v>
-      </c>
-      <c r="V60">
-        <v>8.5</v>
-      </c>
-      <c r="W60">
-        <v>1.04</v>
-      </c>
-      <c r="X60">
-        <v>1.07</v>
-      </c>
-      <c r="Y60">
-        <v>7</v>
-      </c>
-      <c r="Z60">
-        <v>1.42</v>
-      </c>
       <c r="AA60">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AB60">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC60">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE60">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF60">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AG60">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH60">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI60">
         <v>1.05</v>
@@ -8098,13 +8098,13 @@
         <v>239</v>
       </c>
       <c r="L61">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="M61">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N61">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O61">
         <v>2</v>
@@ -8122,16 +8122,16 @@
         <v>3.6</v>
       </c>
       <c r="T61">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="U61">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V61">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -8140,34 +8140,34 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AA61">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AB61">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AC61">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AD61">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AE61">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AF61">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG61">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AH61">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AI61">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ61" t="s">
         <v>240</v>
@@ -8232,43 +8232,43 @@
         <v>2.6</v>
       </c>
       <c r="R62">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S62">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T62">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U62">
         <v>1.33</v>
       </c>
       <c r="V62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W62">
         <v>1.05</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y62">
         <v>7</v>
       </c>
       <c r="Z62">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA62">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AB62">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC62">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AD62">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AE62">
         <v>1.22</v>
@@ -8280,10 +8280,10 @@
         <v>1.75</v>
       </c>
       <c r="AH62">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI62">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ62" t="s">
         <v>240</v>
@@ -8330,13 +8330,13 @@
         <v>239</v>
       </c>
       <c r="L63">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="M63">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N63">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="O63">
         <v>1.67</v>
@@ -8354,7 +8354,7 @@
         <v>2.45</v>
       </c>
       <c r="T63">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U63">
         <v>1.3</v>
@@ -8375,13 +8375,13 @@
         <v>1.45</v>
       </c>
       <c r="AA63">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB63">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC63">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AD63">
         <v>4.5</v>
@@ -8446,10 +8446,10 @@
         <v>239</v>
       </c>
       <c r="L64">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="M64">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="N64">
         <v>2.8</v>
@@ -8464,16 +8464,16 @@
         <v>2.11</v>
       </c>
       <c r="R64">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S64">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T64">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U64">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V64">
         <v>7.6</v>
@@ -8488,16 +8488,16 @@
         <v>8</v>
       </c>
       <c r="Z64">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA64">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB64">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC64">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD64">
         <v>3.6</v>
@@ -8506,16 +8506,16 @@
         <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG64">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH64">
         <v>7</v>
       </c>
       <c r="AI64">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ64" t="s">
         <v>240</v>
@@ -8541,10 +8541,10 @@
         <v>86</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -8651,7 +8651,7 @@
         <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D66" t="s">
         <v>86</v>
@@ -8678,73 +8678,73 @@
         <v>239</v>
       </c>
       <c r="L66">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="N66">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O66">
         <v>1.67</v>
       </c>
       <c r="P66">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R66">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S66">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T66">
         <v>3.3</v>
       </c>
       <c r="U66">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V66">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="W66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z66">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AA66">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AB66">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AC66">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD66">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE66">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF66">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG66">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH66">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI66">
         <v>1.03</v>
@@ -8767,7 +8767,7 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
         <v>86</v>
@@ -8794,76 +8794,76 @@
         <v>239</v>
       </c>
       <c r="L67">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="M67">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N67">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="O67">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q67">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="R67">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="S67">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T67">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="V67">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB67">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC67">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ67" t="s">
         <v>240</v>
@@ -8910,76 +8910,76 @@
         <v>239</v>
       </c>
       <c r="L68">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="M68">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="N68">
+        <v>4.7</v>
+      </c>
+      <c r="O68">
+        <v>1.67</v>
+      </c>
+      <c r="P68">
+        <v>6.5</v>
+      </c>
+      <c r="Q68">
+        <v>2.75</v>
+      </c>
+      <c r="R68">
+        <v>1.53</v>
+      </c>
+      <c r="S68">
+        <v>2.33</v>
+      </c>
+      <c r="T68">
+        <v>3.4</v>
+      </c>
+      <c r="U68">
+        <v>1.25</v>
+      </c>
+      <c r="V68">
+        <v>9.75</v>
+      </c>
+      <c r="W68">
+        <v>1.03</v>
+      </c>
+      <c r="X68">
+        <v>1.12</v>
+      </c>
+      <c r="Y68">
         <v>6</v>
       </c>
-      <c r="O68">
-        <v>1.36</v>
-      </c>
-      <c r="P68">
-        <v>7.5</v>
-      </c>
-      <c r="Q68">
-        <v>4</v>
-      </c>
-      <c r="R68">
-        <v>1.46</v>
-      </c>
-      <c r="S68">
-        <v>2.5</v>
-      </c>
-      <c r="T68">
-        <v>3.2</v>
-      </c>
-      <c r="U68">
-        <v>1.3</v>
-      </c>
-      <c r="V68">
-        <v>8</v>
-      </c>
-      <c r="W68">
-        <v>1.05</v>
-      </c>
-      <c r="X68">
-        <v>1.06</v>
-      </c>
-      <c r="Y68">
-        <v>7.8</v>
-      </c>
       <c r="Z68">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AA68">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AB68">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AC68">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AD68">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AE68">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG68">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH68">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AI68">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ68" t="s">
         <v>240</v>
@@ -9044,58 +9044,58 @@
         <v>2.5</v>
       </c>
       <c r="R69">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S69">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T69">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="U69">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="V69">
+        <v>5</v>
+      </c>
+      <c r="W69">
+        <v>1.13</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
+        <v>12</v>
+      </c>
+      <c r="Z69">
+        <v>1.18</v>
+      </c>
+      <c r="AA69">
         <v>4.33</v>
       </c>
-      <c r="W69">
+      <c r="AB69">
+        <v>1.61</v>
+      </c>
+      <c r="AC69">
+        <v>2.24</v>
+      </c>
+      <c r="AD69">
+        <v>2.53</v>
+      </c>
+      <c r="AE69">
+        <v>1.47</v>
+      </c>
+      <c r="AF69">
+        <v>1.55</v>
+      </c>
+      <c r="AG69">
+        <v>2.34</v>
+      </c>
+      <c r="AH69">
+        <v>4.33</v>
+      </c>
+      <c r="AI69">
         <v>1.18</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>1.12</v>
-      </c>
-      <c r="AA69">
-        <v>5.25</v>
-      </c>
-      <c r="AB69">
-        <v>1.44</v>
-      </c>
-      <c r="AC69">
-        <v>2.6</v>
-      </c>
-      <c r="AD69">
-        <v>2.1</v>
-      </c>
-      <c r="AE69">
-        <v>1.64</v>
-      </c>
-      <c r="AF69">
-        <v>1.44</v>
-      </c>
-      <c r="AG69">
-        <v>2.54</v>
-      </c>
-      <c r="AH69">
-        <v>3.42</v>
-      </c>
-      <c r="AI69">
-        <v>1.29</v>
       </c>
       <c r="AJ69" t="s">
         <v>240</v>
@@ -9142,70 +9142,70 @@
         <v>239</v>
       </c>
       <c r="L70">
+        <v>1.71</v>
+      </c>
+      <c r="M70">
+        <v>3.6</v>
+      </c>
+      <c r="N70">
+        <v>4.2</v>
+      </c>
+      <c r="O70">
+        <v>1.44</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>2.88</v>
+      </c>
+      <c r="R70">
+        <v>1.3</v>
+      </c>
+      <c r="S70">
+        <v>3.4</v>
+      </c>
+      <c r="T70">
+        <v>2.38</v>
+      </c>
+      <c r="U70">
+        <v>1.53</v>
+      </c>
+      <c r="V70">
+        <v>5</v>
+      </c>
+      <c r="W70">
+        <v>1.14</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>1.6</v>
+      </c>
+      <c r="AC70">
+        <v>2.2</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>1.73</v>
+      </c>
+      <c r="AG70">
         <v>2</v>
-      </c>
-      <c r="M70">
-        <v>3.1</v>
-      </c>
-      <c r="N70">
-        <v>3.74</v>
-      </c>
-      <c r="O70">
-        <v>1.67</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>2.63</v>
-      </c>
-      <c r="R70">
-        <v>1.5</v>
-      </c>
-      <c r="S70">
-        <v>2.5</v>
-      </c>
-      <c r="T70">
-        <v>3.5</v>
-      </c>
-      <c r="U70">
-        <v>1.29</v>
-      </c>
-      <c r="V70">
-        <v>11</v>
-      </c>
-      <c r="W70">
-        <v>1.05</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
-      </c>
-      <c r="AB70">
-        <v>2.35</v>
-      </c>
-      <c r="AC70">
-        <v>1.57</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>2.05</v>
-      </c>
-      <c r="AG70">
-        <v>1.7</v>
       </c>
       <c r="AH70">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>63</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D71" t="s">
         <v>86</v>
@@ -9258,76 +9258,76 @@
         <v>239</v>
       </c>
       <c r="L71">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M71">
-        <v>3.53</v>
+        <v>4.33</v>
       </c>
       <c r="N71">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O71">
         <v>1.67</v>
       </c>
       <c r="P71">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R71">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S71">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T71">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U71">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V71">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y71">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z71">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AA71">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="AB71">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AC71">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AE71">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG71">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AH71">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="AI71">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ71" t="s">
         <v>240</v>
@@ -9347,7 +9347,7 @@
         <v>63</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D72" t="s">
         <v>86</v>
@@ -9374,76 +9374,76 @@
         <v>239</v>
       </c>
       <c r="L72">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="M72">
+        <v>3.53</v>
+      </c>
+      <c r="N72">
+        <v>2.85</v>
+      </c>
+      <c r="O72">
+        <v>1.67</v>
+      </c>
+      <c r="P72">
+        <v>13.5</v>
+      </c>
+      <c r="Q72">
+        <v>2.2</v>
+      </c>
+      <c r="R72">
+        <v>1.25</v>
+      </c>
+      <c r="S72">
         <v>3.75</v>
       </c>
-      <c r="N72">
-        <v>3.3</v>
-      </c>
-      <c r="O72">
+      <c r="T72">
+        <v>2.2</v>
+      </c>
+      <c r="U72">
         <v>1.62</v>
       </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>2.38</v>
-      </c>
-      <c r="R72">
-        <v>1.29</v>
-      </c>
-      <c r="S72">
-        <v>3.3</v>
-      </c>
-      <c r="T72">
-        <v>2.3</v>
-      </c>
-      <c r="U72">
-        <v>1.55</v>
-      </c>
       <c r="V72">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W72">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z72">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA72">
-        <v>4.33</v>
+        <v>5.36</v>
       </c>
       <c r="AB72">
+        <v>1.61</v>
+      </c>
+      <c r="AC72">
+        <v>2.15</v>
+      </c>
+      <c r="AD72">
+        <v>2.25</v>
+      </c>
+      <c r="AE72">
         <v>1.57</v>
       </c>
-      <c r="AC72">
-        <v>2.25</v>
-      </c>
-      <c r="AD72">
-        <v>2.43</v>
-      </c>
-      <c r="AE72">
+      <c r="AF72">
         <v>1.5</v>
       </c>
-      <c r="AF72">
-        <v>1.53</v>
-      </c>
       <c r="AG72">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH72">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="AI72">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ72" t="s">
         <v>240</v>
@@ -9490,76 +9490,76 @@
         <v>239</v>
       </c>
       <c r="L73">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="M73">
+        <v>3.72</v>
+      </c>
+      <c r="N73">
+        <v>2.08</v>
+      </c>
+      <c r="O73">
+        <v>1.62</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>2.38</v>
+      </c>
+      <c r="R73">
+        <v>1.3</v>
+      </c>
+      <c r="S73">
+        <v>3.5</v>
+      </c>
+      <c r="T73">
+        <v>2.4</v>
+      </c>
+      <c r="U73">
+        <v>1.53</v>
+      </c>
+      <c r="V73">
+        <v>5.5</v>
+      </c>
+      <c r="W73">
+        <v>1.11</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>11</v>
+      </c>
+      <c r="Z73">
+        <v>1.14</v>
+      </c>
+      <c r="AA73">
+        <v>4</v>
+      </c>
+      <c r="AB73">
+        <v>1.63</v>
+      </c>
+      <c r="AC73">
+        <v>2.2</v>
+      </c>
+      <c r="AD73">
+        <v>2.5</v>
+      </c>
+      <c r="AE73">
+        <v>1.46</v>
+      </c>
+      <c r="AF73">
+        <v>1.57</v>
+      </c>
+      <c r="AG73">
+        <v>2.25</v>
+      </c>
+      <c r="AH73">
         <v>4.33</v>
       </c>
-      <c r="N73">
-        <v>2.55</v>
-      </c>
-      <c r="O73">
-        <v>1.67</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>2.1</v>
-      </c>
-      <c r="R73">
-        <v>1.22</v>
-      </c>
-      <c r="S73">
-        <v>3.8</v>
-      </c>
-      <c r="T73">
-        <v>2</v>
-      </c>
-      <c r="U73">
-        <v>1.73</v>
-      </c>
-      <c r="V73">
-        <v>4</v>
-      </c>
-      <c r="W73">
-        <v>1.2</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
-      </c>
-      <c r="Z73">
-        <v>1.1</v>
-      </c>
-      <c r="AA73">
-        <v>5.75</v>
-      </c>
-      <c r="AB73">
-        <v>1.4</v>
-      </c>
-      <c r="AC73">
-        <v>2.75</v>
-      </c>
-      <c r="AD73">
-        <v>1.95</v>
-      </c>
-      <c r="AE73">
-        <v>1.75</v>
-      </c>
-      <c r="AF73">
-        <v>1.36</v>
-      </c>
-      <c r="AG73">
-        <v>2.9</v>
-      </c>
-      <c r="AH73">
-        <v>3.05</v>
-      </c>
       <c r="AI73">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AJ73" t="s">
         <v>240</v>
@@ -9579,7 +9579,7 @@
         <v>64</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D74" t="s">
         <v>86</v>
@@ -9606,34 +9606,34 @@
         <v>239</v>
       </c>
       <c r="L74">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="M74">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N74">
-        <v>5.1</v>
+        <v>3.57</v>
       </c>
       <c r="O74">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P74">
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R74">
         <v>1.44</v>
       </c>
       <c r="S74">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T74">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V74">
         <v>10</v>
@@ -9642,40 +9642,40 @@
         <v>1.06</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB74">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC74">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG74">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ74" t="s">
         <v>240</v>
@@ -9695,7 +9695,7 @@
         <v>64</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
         <v>86</v>
@@ -9722,76 +9722,76 @@
         <v>239</v>
       </c>
       <c r="L75">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="M75">
-        <v>3.01</v>
+        <v>3.95</v>
       </c>
       <c r="N75">
-        <v>3.57</v>
+        <v>3.68</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P75">
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB75">
-        <v>2.35</v>
+        <v>1.48</v>
       </c>
       <c r="AC75">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ75" t="s">
         <v>240</v>
@@ -9811,7 +9811,7 @@
         <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D76" t="s">
         <v>86</v>
@@ -9838,76 +9838,76 @@
         <v>239</v>
       </c>
       <c r="L76">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="M76">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N76">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="O76">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="P76">
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R76">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S76">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="T76">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="U76">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V76">
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="W76">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y76">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="Z76">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AA76">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="AB76">
+        <v>2.2</v>
+      </c>
+      <c r="AC76">
         <v>1.62</v>
       </c>
-      <c r="AC76">
-        <v>2.2</v>
-      </c>
       <c r="AD76">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AE76">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG76">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AH76">
-        <v>4.33</v>
+        <v>9</v>
       </c>
       <c r="AI76">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AJ76" t="s">
         <v>240</v>
@@ -9954,76 +9954,76 @@
         <v>239</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P77">
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R77">
+        <v>1.27</v>
+      </c>
+      <c r="S77">
+        <v>3.28</v>
+      </c>
+      <c r="T77">
+        <v>2.12</v>
+      </c>
+      <c r="U77">
+        <v>1.64</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>1.13</v>
+      </c>
+      <c r="AA77">
+        <v>4.5</v>
+      </c>
+      <c r="AB77">
+        <v>1.43</v>
+      </c>
+      <c r="AC77">
+        <v>2.56</v>
+      </c>
+      <c r="AD77">
+        <v>2.16</v>
+      </c>
+      <c r="AE77">
+        <v>1.61</v>
+      </c>
+      <c r="AF77">
+        <v>1.83</v>
+      </c>
+      <c r="AG77">
+        <v>1.83</v>
+      </c>
+      <c r="AH77">
+        <v>3.5</v>
+      </c>
+      <c r="AI77">
         <v>1.22</v>
-      </c>
-      <c r="S77">
-        <v>3.8</v>
-      </c>
-      <c r="T77">
-        <v>2</v>
-      </c>
-      <c r="U77">
-        <v>1.72</v>
-      </c>
-      <c r="V77">
-        <v>4</v>
-      </c>
-      <c r="W77">
-        <v>1.2</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <v>1.1</v>
-      </c>
-      <c r="AA77">
-        <v>5.75</v>
-      </c>
-      <c r="AB77">
-        <v>1.38</v>
-      </c>
-      <c r="AC77">
-        <v>2.8</v>
-      </c>
-      <c r="AD77">
-        <v>1.95</v>
-      </c>
-      <c r="AE77">
-        <v>1.75</v>
-      </c>
-      <c r="AF77">
-        <v>1.38</v>
-      </c>
-      <c r="AG77">
-        <v>2.8</v>
-      </c>
-      <c r="AH77">
-        <v>3.05</v>
-      </c>
-      <c r="AI77">
-        <v>1.3</v>
       </c>
       <c r="AJ77" t="s">
         <v>240</v>
@@ -10043,16 +10043,16 @@
         <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
         <v>86</v>
       </c>
       <c r="E78" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="F78" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10070,76 +10070,76 @@
         <v>239</v>
       </c>
       <c r="L78">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="M78">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N78">
+        <v>7.5</v>
+      </c>
+      <c r="O78">
+        <v>1.36</v>
+      </c>
+      <c r="P78">
+        <v>6.25</v>
+      </c>
+      <c r="Q78">
+        <v>4.5</v>
+      </c>
+      <c r="R78">
+        <v>1.57</v>
+      </c>
+      <c r="S78">
+        <v>2.25</v>
+      </c>
+      <c r="T78">
+        <v>3.75</v>
+      </c>
+      <c r="U78">
+        <v>1.25</v>
+      </c>
+      <c r="V78">
+        <v>11</v>
+      </c>
+      <c r="W78">
+        <v>1.05</v>
+      </c>
+      <c r="X78">
+        <v>1.1</v>
+      </c>
+      <c r="Y78">
+        <v>6.5</v>
+      </c>
+      <c r="Z78">
+        <v>1.45</v>
+      </c>
+      <c r="AA78">
+        <v>2.5</v>
+      </c>
+      <c r="AB78">
         <v>2.6</v>
       </c>
-      <c r="O78">
-        <v>1.73</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>2.05</v>
-      </c>
-      <c r="R78">
-        <v>1.22</v>
-      </c>
-      <c r="S78">
-        <v>3.8</v>
-      </c>
-      <c r="T78">
-        <v>2</v>
-      </c>
-      <c r="U78">
-        <v>1.73</v>
-      </c>
-      <c r="V78">
-        <v>4</v>
-      </c>
-      <c r="W78">
-        <v>1.2</v>
-      </c>
-      <c r="X78">
-        <v>0</v>
-      </c>
-      <c r="Y78">
-        <v>0</v>
-      </c>
-      <c r="Z78">
-        <v>1.11</v>
-      </c>
-      <c r="AA78">
-        <v>5.5</v>
-      </c>
-      <c r="AB78">
-        <v>1.35</v>
-      </c>
       <c r="AC78">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="AD78">
-        <v>2</v>
+        <v>5.25</v>
       </c>
       <c r="AE78">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="AG78">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="AH78">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="AI78">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="AJ78" t="s">
         <v>240</v>
@@ -10159,16 +10159,16 @@
         <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="F79" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10186,76 +10186,76 @@
         <v>239</v>
       </c>
       <c r="L79">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="M79">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N79">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="O79">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="P79">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>4.5</v>
+        <v>2.05</v>
       </c>
       <c r="R79">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="S79">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="T79">
-        <v>3.75</v>
+        <v>2.16</v>
       </c>
       <c r="U79">
+        <v>1.61</v>
+      </c>
+      <c r="V79">
+        <v>4.75</v>
+      </c>
+      <c r="W79">
+        <v>1.15</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>1.13</v>
+      </c>
+      <c r="AA79">
+        <v>5</v>
+      </c>
+      <c r="AB79">
+        <v>1.48</v>
+      </c>
+      <c r="AC79">
+        <v>2.43</v>
+      </c>
+      <c r="AD79">
+        <v>2.2</v>
+      </c>
+      <c r="AE79">
+        <v>1.6</v>
+      </c>
+      <c r="AF79">
+        <v>1.42</v>
+      </c>
+      <c r="AG79">
+        <v>2.62</v>
+      </c>
+      <c r="AH79">
+        <v>3.5</v>
+      </c>
+      <c r="AI79">
         <v>1.25</v>
-      </c>
-      <c r="V79">
-        <v>11</v>
-      </c>
-      <c r="W79">
-        <v>1.05</v>
-      </c>
-      <c r="X79">
-        <v>1.1</v>
-      </c>
-      <c r="Y79">
-        <v>6.5</v>
-      </c>
-      <c r="Z79">
-        <v>1.45</v>
-      </c>
-      <c r="AA79">
-        <v>2.5</v>
-      </c>
-      <c r="AB79">
-        <v>2.6</v>
-      </c>
-      <c r="AC79">
-        <v>1.48</v>
-      </c>
-      <c r="AD79">
-        <v>5.25</v>
-      </c>
-      <c r="AE79">
-        <v>1.15</v>
-      </c>
-      <c r="AF79">
-        <v>2.75</v>
-      </c>
-      <c r="AG79">
-        <v>1.4</v>
-      </c>
-      <c r="AH79">
-        <v>10</v>
-      </c>
-      <c r="AI79">
-        <v>1.04</v>
       </c>
       <c r="AJ79" t="s">
         <v>240</v>
@@ -10302,76 +10302,76 @@
         <v>239</v>
       </c>
       <c r="L80">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>1.25</v>
+      </c>
+      <c r="S80">
+        <v>3.6</v>
+      </c>
+      <c r="T80">
+        <v>2.1</v>
+      </c>
+      <c r="U80">
+        <v>1.67</v>
+      </c>
+      <c r="V80">
+        <v>4.33</v>
+      </c>
+      <c r="W80">
+        <v>1.18</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>1.11</v>
+      </c>
+      <c r="AA80">
+        <v>5.5</v>
+      </c>
+      <c r="AB80">
+        <v>1.42</v>
+      </c>
+      <c r="AC80">
+        <v>2.6</v>
+      </c>
+      <c r="AD80">
+        <v>2.06</v>
+      </c>
+      <c r="AE80">
+        <v>1.67</v>
+      </c>
+      <c r="AF80">
+        <v>1.42</v>
+      </c>
+      <c r="AG80">
+        <v>2.62</v>
+      </c>
+      <c r="AH80">
+        <v>3.3</v>
+      </c>
+      <c r="AI80">
         <v>1.29</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>4</v>
-      </c>
-      <c r="R80">
-        <v>1.27</v>
-      </c>
-      <c r="S80">
-        <v>3.28</v>
-      </c>
-      <c r="T80">
-        <v>2.35</v>
-      </c>
-      <c r="U80">
-        <v>1.5</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>1.15</v>
-      </c>
-      <c r="AA80">
-        <v>4.3</v>
-      </c>
-      <c r="AB80">
-        <v>1.59</v>
-      </c>
-      <c r="AC80">
-        <v>2.2</v>
-      </c>
-      <c r="AD80">
-        <v>2.43</v>
-      </c>
-      <c r="AE80">
-        <v>1.44</v>
-      </c>
-      <c r="AF80">
-        <v>1.84</v>
-      </c>
-      <c r="AG80">
-        <v>1.82</v>
-      </c>
-      <c r="AH80">
-        <v>4.35</v>
-      </c>
-      <c r="AI80">
-        <v>1.14</v>
       </c>
       <c r="AJ80" t="s">
         <v>240</v>
@@ -10391,7 +10391,7 @@
         <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D81" t="s">
         <v>86</v>
@@ -10552,13 +10552,13 @@
         <v>2.2</v>
       </c>
       <c r="R82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S82">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T82">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U82">
         <v>1.73</v>
@@ -10582,10 +10582,10 @@
         <v>5.75</v>
       </c>
       <c r="AB82">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC82">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD82">
         <v>1.95</v>
@@ -10600,10 +10600,10 @@
         <v>2.88</v>
       </c>
       <c r="AH82">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AI82">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AJ82" t="s">
         <v>240</v>

--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="243">
   <si>
     <t>Date</t>
   </si>
@@ -241,12 +241,12 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -280,18 +280,18 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
@@ -301,18 +301,18 @@
     <t>Bucheon 1995</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
+    <t>Hebei Kungfu</t>
   </si>
   <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
-    <t>Hebei Kungfu</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
@@ -322,22 +322,49 @@
     <t>Bryne</t>
   </si>
   <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
-    <t>Tobol</t>
+    <t>AIK</t>
   </si>
   <si>
     <t>Värnamo</t>
   </si>
   <si>
-    <t>AIK</t>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
   </si>
   <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
-    <t>Vélez Sarsfield</t>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
   </si>
   <si>
     <t>Kristiansund</t>
@@ -349,60 +376,36 @@
     <t>Strømsgodset</t>
   </si>
   <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
     <t>Santiago Morning</t>
   </si>
   <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
@@ -415,12 +418,12 @@
     <t>Alvarado</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
@@ -430,12 +433,12 @@
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Criciúma</t>
-  </si>
-  <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
@@ -451,54 +454,54 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
+    <t>Caxias</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Caxias</t>
+    <t>York9 FC</t>
+  </si>
+  <si>
+    <t>FC Cincinnati II</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>York9 FC</t>
+    <t>St. Louis City</t>
   </si>
   <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>St. Louis City</t>
-  </si>
-  <si>
     <t>Orlando City II</t>
   </si>
   <si>
+    <t>Atlanta United II</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Atlanta United II</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
+    <t>Colorado Rapids II</t>
+  </si>
+  <si>
     <t>Houston Dynamo FC II</t>
   </si>
   <si>
-    <t>Colorado Rapids II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -508,18 +511,18 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
+    <t>St George City FA</t>
+  </si>
+  <si>
+    <t>Sydney Olympic</t>
+  </si>
+  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
-    <t>St George City FA</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>Sydney Olympic</t>
-  </si>
-  <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
@@ -529,18 +532,18 @@
     <t>Gimpo Citizen</t>
   </si>
   <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
     <t>Nanjing City</t>
   </si>
   <si>
-    <t>Nantong Zhiyun</t>
+    <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
@@ -550,22 +553,49 @@
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>Okzhetpes</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Haka</t>
   </si>
   <si>
-    <t>Okzhetpes</t>
+    <t>Degerfors</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Degerfors</t>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
   </si>
   <si>
     <t>Newell's Old Boys</t>
   </si>
   <si>
-    <t>Tigre</t>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
   </si>
   <si>
     <t>Sarpsborg 08</t>
@@ -577,60 +607,36 @@
     <t>Tromsø</t>
   </si>
   <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
     <t>Copiapó</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
@@ -643,12 +649,12 @@
     <t>San Miguel</t>
   </si>
   <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
@@ -658,12 +664,12 @@
     <t>Chacarita Juniors</t>
   </si>
   <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
@@ -679,52 +685,52 @@
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Concepción</t>
+  </si>
+  <si>
     <t>Remo</t>
   </si>
   <si>
-    <t>Concepción</t>
+    <t>Anápolis</t>
   </si>
   <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Anápolis</t>
+    <t>Valour FC</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
   </si>
   <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
+    <t>Portland Timbers</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>Carolina Core</t>
   </si>
   <si>
+    <t>Columbus Crew II</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Columbus Crew II</t>
-  </si>
-  <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Sporting KC II</t>
   </si>
   <si>
+    <t>Whitecaps II</t>
+  </si>
+  <si>
     <t>North Texas</t>
-  </si>
-  <si>
-    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1100,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL82"/>
+  <dimension ref="A1:AL83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1236,7 +1242,7 @@
         <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1251,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L2">
         <v>2.01</v>
@@ -1272,64 +1278,64 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="T2">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
+        <v>7.5</v>
+      </c>
+      <c r="Z2">
+        <v>1.35</v>
+      </c>
+      <c r="AA2">
+        <v>2.74</v>
+      </c>
+      <c r="AB2">
+        <v>2.1</v>
+      </c>
+      <c r="AC2">
+        <v>1.61</v>
+      </c>
+      <c r="AD2">
+        <v>3.8</v>
+      </c>
+      <c r="AE2">
+        <v>1.2</v>
+      </c>
+      <c r="AF2">
+        <v>1.95</v>
+      </c>
+      <c r="AG2">
+        <v>1.7</v>
+      </c>
+      <c r="AH2">
         <v>8.5</v>
       </c>
-      <c r="Z2">
-        <v>1.3</v>
-      </c>
-      <c r="AA2">
-        <v>3</v>
-      </c>
-      <c r="AB2">
-        <v>1.9</v>
-      </c>
-      <c r="AC2">
-        <v>1.81</v>
-      </c>
-      <c r="AD2">
-        <v>3.7</v>
-      </c>
-      <c r="AE2">
-        <v>1.25</v>
-      </c>
-      <c r="AF2">
-        <v>1.91</v>
-      </c>
-      <c r="AG2">
-        <v>1.8</v>
-      </c>
-      <c r="AH2">
-        <v>7.5</v>
-      </c>
       <c r="AI2">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL2" s="3">
         <v>45851</v>
@@ -1352,7 +1358,7 @@
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1367,85 +1373,85 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="M3">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>20</v>
+        <v>16.75</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="W3">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AA3">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AB3">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="AD3">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="AE3">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AF3">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AH3">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AI3">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL3" s="3">
         <v>45851.08333333334</v>
@@ -1468,7 +1474,7 @@
         <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1483,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L4">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="M4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
         <v>1.8</v>
@@ -1534,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC4">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1558,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL4" s="3">
         <v>45851.08333333334</v>
@@ -1584,7 +1590,7 @@
         <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1599,85 +1605,85 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L5">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="M5">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="O5">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
         <v>1.53</v>
       </c>
-      <c r="V5">
-        <v>5.4</v>
-      </c>
-      <c r="W5">
-        <v>1.12</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>12</v>
-      </c>
-      <c r="Z5">
-        <v>1.15</v>
-      </c>
-      <c r="AA5">
-        <v>4.25</v>
-      </c>
-      <c r="AB5">
-        <v>1.61</v>
-      </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AD5">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL5" s="3">
         <v>45851.08333333334</v>
@@ -1700,7 +1706,7 @@
         <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1715,85 +1721,85 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L6">
-        <v>4.1</v>
+        <v>2.06</v>
       </c>
       <c r="M6">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB6">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC6">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL6" s="3">
         <v>45851.08333333334</v>
@@ -1816,7 +1822,7 @@
         <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1831,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L7">
         <v>3.84</v>
@@ -1906,10 +1912,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL7" s="3">
         <v>45851.29166666666</v>
@@ -1932,7 +1938,7 @@
         <v>93</v>
       </c>
       <c r="F8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1947,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L8">
         <v>1.74</v>
@@ -2022,10 +2028,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL8" s="3">
         <v>45851.29166666666</v>
@@ -2048,7 +2054,7 @@
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2063,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L9">
         <v>2.09</v>
@@ -2138,10 +2144,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL9" s="3">
         <v>45851.29166666666</v>
@@ -2164,7 +2170,7 @@
         <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2179,85 +2185,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L10">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="M10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N10">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="O10">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="P10">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T10">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="U10">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V10">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z10">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AA10">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="AB10">
-        <v>1.76</v>
+        <v>2.32</v>
       </c>
       <c r="AC10">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AD10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE10">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AH10">
-        <v>5.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL10" s="3">
         <v>45851.33333333334</v>
@@ -2280,7 +2286,7 @@
         <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2295,85 +2301,85 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L11">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="M11">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N11">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="O11">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P11">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="S11">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="T11">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V11">
+        <v>7.5</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
         <v>9</v>
       </c>
-      <c r="W11">
-        <v>1.03</v>
-      </c>
-      <c r="X11">
-        <v>1.08</v>
-      </c>
-      <c r="Y11">
-        <v>7.1</v>
-      </c>
       <c r="Z11">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AA11">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB11">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AC11">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AD11">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AE11">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF11">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH11">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AI11">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AJ11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL11" s="3">
         <v>45851.33333333334</v>
@@ -2387,7 +2393,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>86</v>
@@ -2396,7 +2402,7 @@
         <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2411,85 +2417,85 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L12">
-        <v>3.01</v>
+        <v>1.57</v>
       </c>
       <c r="M12">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="N12">
-        <v>1.96</v>
+        <v>4.75</v>
       </c>
       <c r="O12">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="P12">
-        <v>19</v>
+        <v>10.75</v>
       </c>
       <c r="Q12">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>13.8</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AA12">
-        <v>4.7</v>
+        <v>3.04</v>
       </c>
       <c r="AB12">
-        <v>1.53</v>
+        <v>2.11</v>
       </c>
       <c r="AC12">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD12">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="AE12">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="AH12">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AI12">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL12" s="3">
         <v>45851.35416666666</v>
@@ -2503,7 +2509,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>86</v>
@@ -2512,7 +2518,7 @@
         <v>98</v>
       </c>
       <c r="F13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2527,85 +2533,85 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L13">
+        <v>3.01</v>
+      </c>
+      <c r="M13">
+        <v>3.63</v>
+      </c>
+      <c r="N13">
+        <v>1.96</v>
+      </c>
+      <c r="O13">
+        <v>2.13</v>
+      </c>
+      <c r="P13">
+        <v>19</v>
+      </c>
+      <c r="Q13">
+        <v>1.68</v>
+      </c>
+      <c r="R13">
+        <v>1.23</v>
+      </c>
+      <c r="S13">
+        <v>3.6</v>
+      </c>
+      <c r="T13">
+        <v>2.15</v>
+      </c>
+      <c r="U13">
+        <v>1.72</v>
+      </c>
+      <c r="V13">
+        <v>4.6</v>
+      </c>
+      <c r="W13">
+        <v>1.18</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>17</v>
+      </c>
+      <c r="Z13">
+        <v>1.11</v>
+      </c>
+      <c r="AA13">
+        <v>5</v>
+      </c>
+      <c r="AB13">
+        <v>1.48</v>
+      </c>
+      <c r="AC13">
+        <v>2.47</v>
+      </c>
+      <c r="AD13">
+        <v>2.15</v>
+      </c>
+      <c r="AE13">
         <v>1.57</v>
       </c>
-      <c r="M13">
-        <v>3.75</v>
-      </c>
-      <c r="N13">
-        <v>4.75</v>
-      </c>
-      <c r="O13">
-        <v>1.4</v>
-      </c>
-      <c r="P13">
-        <v>10.75</v>
-      </c>
-      <c r="Q13">
-        <v>3.4</v>
-      </c>
-      <c r="R13">
-        <v>1.44</v>
-      </c>
-      <c r="S13">
-        <v>2.62</v>
-      </c>
-      <c r="T13">
-        <v>3.1</v>
-      </c>
-      <c r="U13">
-        <v>1.33</v>
-      </c>
-      <c r="V13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W13">
-        <v>1.07</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z13">
-        <v>1.37</v>
-      </c>
-      <c r="AA13">
-        <v>2.95</v>
-      </c>
-      <c r="AB13">
-        <v>1.78</v>
-      </c>
-      <c r="AC13">
-        <v>1.9</v>
-      </c>
-      <c r="AD13">
-        <v>2.95</v>
-      </c>
-      <c r="AE13">
-        <v>1.33</v>
-      </c>
       <c r="AF13">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AH13">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="AI13">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AJ13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL13" s="3">
         <v>45851.35416666666</v>
@@ -2628,7 +2634,7 @@
         <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2643,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L14">
         <v>1.76</v>
@@ -2718,10 +2724,10 @@
         <v>1.17</v>
       </c>
       <c r="AJ14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL14" s="3">
         <v>45851.375</v>
@@ -2744,7 +2750,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2759,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L15">
         <v>2.63</v>
@@ -2834,10 +2840,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL15" s="3">
         <v>45851.375</v>
@@ -2860,7 +2866,7 @@
         <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2875,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L16">
         <v>2.3</v>
@@ -2950,10 +2956,10 @@
         <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK16" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL16" s="3">
         <v>45851.39583333334</v>
@@ -2976,7 +2982,7 @@
         <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2991,85 +2997,85 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L17">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="M17">
-        <v>3.59</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>2.59</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="P17">
-        <v>12.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q17">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="R17">
+        <v>1.35</v>
+      </c>
+      <c r="S17">
+        <v>2.88</v>
+      </c>
+      <c r="T17">
+        <v>2.65</v>
+      </c>
+      <c r="U17">
+        <v>1.4</v>
+      </c>
+      <c r="V17">
+        <v>6.5</v>
+      </c>
+      <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z17">
+        <v>1.29</v>
+      </c>
+      <c r="AA17">
+        <v>3.22</v>
+      </c>
+      <c r="AB17">
+        <v>1.83</v>
+      </c>
+      <c r="AC17">
+        <v>1.93</v>
+      </c>
+      <c r="AD17">
+        <v>3.2</v>
+      </c>
+      <c r="AE17">
         <v>1.28</v>
       </c>
-      <c r="S17">
-        <v>3.3</v>
-      </c>
-      <c r="T17">
-        <v>2.3</v>
-      </c>
-      <c r="U17">
-        <v>1.55</v>
-      </c>
-      <c r="V17">
-        <v>5.6</v>
-      </c>
-      <c r="W17">
-        <v>1.12</v>
-      </c>
-      <c r="X17">
-        <v>1.03</v>
-      </c>
-      <c r="Y17">
-        <v>10</v>
-      </c>
-      <c r="Z17">
-        <v>1.18</v>
-      </c>
-      <c r="AA17">
-        <v>4.33</v>
-      </c>
-      <c r="AB17">
-        <v>1.57</v>
-      </c>
-      <c r="AC17">
-        <v>2.15</v>
-      </c>
-      <c r="AD17">
-        <v>2.5</v>
-      </c>
-      <c r="AE17">
-        <v>1.5</v>
-      </c>
       <c r="AF17">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AH17">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="AI17">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL17" s="3">
         <v>45851.41666666666</v>
@@ -3083,7 +3089,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
         <v>86</v>
@@ -3092,7 +3098,7 @@
         <v>103</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3107,85 +3113,85 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L18">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="P18">
-        <v>9.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Q18">
-        <v>3.28</v>
+        <v>2.61</v>
       </c>
       <c r="R18">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>7</v>
+      </c>
+      <c r="Z18">
+        <v>1.37</v>
+      </c>
+      <c r="AA18">
+        <v>2.66</v>
+      </c>
+      <c r="AB18">
+        <v>2.25</v>
+      </c>
+      <c r="AC18">
+        <v>1.53</v>
+      </c>
+      <c r="AD18">
+        <v>4.4</v>
+      </c>
+      <c r="AE18">
+        <v>1.16</v>
+      </c>
+      <c r="AF18">
+        <v>2.2</v>
+      </c>
+      <c r="AG18">
+        <v>1.55</v>
+      </c>
+      <c r="AH18">
+        <v>9.1</v>
+      </c>
+      <c r="AI18">
         <v>1</v>
       </c>
-      <c r="Y18">
-        <v>10</v>
-      </c>
-      <c r="Z18">
-        <v>1.25</v>
-      </c>
-      <c r="AA18">
-        <v>3.6</v>
-      </c>
-      <c r="AB18">
-        <v>1.83</v>
-      </c>
-      <c r="AC18">
-        <v>1.93</v>
-      </c>
-      <c r="AD18">
-        <v>2.92</v>
-      </c>
-      <c r="AE18">
-        <v>1.31</v>
-      </c>
-      <c r="AF18">
-        <v>1.91</v>
-      </c>
-      <c r="AG18">
-        <v>1.8</v>
-      </c>
-      <c r="AH18">
-        <v>5.5</v>
-      </c>
-      <c r="AI18">
-        <v>1.11</v>
-      </c>
       <c r="AJ18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK18" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL18" s="3">
         <v>45851.41666666666</v>
@@ -3196,10 +3202,10 @@
         <v>45851</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>86</v>
@@ -3208,7 +3214,7 @@
         <v>104</v>
       </c>
       <c r="F19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3223,88 +3229,88 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L19">
-        <v>3.82</v>
+        <v>2.2</v>
       </c>
       <c r="M19">
-        <v>3.37</v>
+        <v>3.59</v>
       </c>
       <c r="N19">
-        <v>1.78</v>
+        <v>2.59</v>
       </c>
       <c r="O19">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="P19">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="Q19">
+        <v>2.2</v>
+      </c>
+      <c r="R19">
+        <v>1.28</v>
+      </c>
+      <c r="S19">
+        <v>3.3</v>
+      </c>
+      <c r="T19">
+        <v>2.25</v>
+      </c>
+      <c r="U19">
+        <v>1.57</v>
+      </c>
+      <c r="V19">
+        <v>5</v>
+      </c>
+      <c r="W19">
+        <v>1.15</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>12</v>
+      </c>
+      <c r="Z19">
+        <v>1.2</v>
+      </c>
+      <c r="AA19">
+        <v>4.33</v>
+      </c>
+      <c r="AB19">
+        <v>1.61</v>
+      </c>
+      <c r="AC19">
+        <v>2.17</v>
+      </c>
+      <c r="AD19">
+        <v>2.52</v>
+      </c>
+      <c r="AE19">
+        <v>1.5</v>
+      </c>
+      <c r="AF19">
         <v>1.53</v>
       </c>
-      <c r="R19">
-        <v>1.36</v>
-      </c>
-      <c r="S19">
-        <v>3</v>
-      </c>
-      <c r="T19">
-        <v>2.75</v>
-      </c>
-      <c r="U19">
-        <v>1.4</v>
-      </c>
-      <c r="V19">
-        <v>8</v>
-      </c>
-      <c r="W19">
-        <v>1.08</v>
-      </c>
-      <c r="X19">
-        <v>1.06</v>
-      </c>
-      <c r="Y19">
-        <v>9</v>
-      </c>
-      <c r="Z19">
-        <v>1.3</v>
-      </c>
-      <c r="AA19">
-        <v>3.45</v>
-      </c>
-      <c r="AB19">
-        <v>1.91</v>
-      </c>
-      <c r="AC19">
-        <v>1.79</v>
-      </c>
-      <c r="AD19">
-        <v>3.45</v>
-      </c>
-      <c r="AE19">
-        <v>1.3</v>
-      </c>
-      <c r="AF19">
-        <v>1.8</v>
-      </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AH19">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="AI19">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL19" s="3">
-        <v>45851.47916666666</v>
+        <v>45851.41666666666</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3324,7 +3330,7 @@
         <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3339,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L20">
         <v>1.51</v>
@@ -3414,10 +3420,10 @@
         <v>1.12</v>
       </c>
       <c r="AJ20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL20" s="3">
         <v>45851.47916666666</v>
@@ -3428,10 +3434,10 @@
         <v>45851</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
         <v>86</v>
@@ -3440,7 +3446,7 @@
         <v>106</v>
       </c>
       <c r="F21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3455,88 +3461,88 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL21" s="3">
-        <v>45851.5</v>
+        <v>45851.47916666666</v>
       </c>
     </row>
     <row r="22" spans="1:38">
@@ -3556,7 +3562,7 @@
         <v>107</v>
       </c>
       <c r="F22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3571,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3646,10 +3652,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL22" s="3">
         <v>45851.5</v>
@@ -3663,7 +3669,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -3672,7 +3678,7 @@
         <v>108</v>
       </c>
       <c r="F23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3687,85 +3693,85 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L23">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL23" s="3">
         <v>45851.5</v>
@@ -3779,7 +3785,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>86</v>
@@ -3788,7 +3794,7 @@
         <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3803,85 +3809,85 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L24">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK24" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL24" s="3">
         <v>45851.5</v>
@@ -3895,7 +3901,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
         <v>86</v>
@@ -3904,7 +3910,7 @@
         <v>110</v>
       </c>
       <c r="F25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3919,85 +3925,85 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L25">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL25" s="3">
         <v>45851.5</v>
@@ -4011,7 +4017,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
         <v>86</v>
@@ -4020,7 +4026,7 @@
         <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4035,85 +4041,85 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L26">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL26" s="3">
         <v>45851.5</v>
@@ -4136,7 +4142,7 @@
         <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4151,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -4226,10 +4232,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK27" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL27" s="3">
         <v>45851.5</v>
@@ -4252,7 +4258,7 @@
         <v>113</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4267,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -4342,10 +4348,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK28" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL28" s="3">
         <v>45851.5</v>
@@ -4368,7 +4374,7 @@
         <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4383,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4458,10 +4464,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK29" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL29" s="3">
         <v>45851.5</v>
@@ -4484,7 +4490,7 @@
         <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4499,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4574,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK30" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL30" s="3">
         <v>45851.5</v>
@@ -4600,7 +4606,7 @@
         <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4615,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -4690,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK31" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL31" s="3">
         <v>45851.5</v>
@@ -4707,7 +4713,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
         <v>86</v>
@@ -4716,7 +4722,7 @@
         <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4731,85 +4737,85 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ32" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK32" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL32" s="3">
         <v>45851.5</v>
@@ -4823,7 +4829,7 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
         <v>86</v>
@@ -4832,7 +4838,7 @@
         <v>118</v>
       </c>
       <c r="F33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4847,85 +4853,85 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ33" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK33" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL33" s="3">
         <v>45851.5</v>
@@ -4939,7 +4945,7 @@
         <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
         <v>86</v>
@@ -4948,7 +4954,7 @@
         <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4963,85 +4969,85 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK34" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL34" s="3">
         <v>45851.5</v>
@@ -5055,7 +5061,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
         <v>86</v>
@@ -5064,7 +5070,7 @@
         <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5079,85 +5085,85 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L35">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK35" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL35" s="3">
         <v>45851.5</v>
@@ -5180,7 +5186,7 @@
         <v>121</v>
       </c>
       <c r="F36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5195,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -5270,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK36" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL36" s="3">
         <v>45851.5</v>
@@ -5296,7 +5302,7 @@
         <v>122</v>
       </c>
       <c r="F37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5311,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -5386,10 +5392,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK37" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL37" s="3">
         <v>45851.5</v>
@@ -5403,7 +5409,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D38" t="s">
         <v>86</v>
@@ -5412,7 +5418,7 @@
         <v>123</v>
       </c>
       <c r="F38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5427,85 +5433,85 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ38" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK38" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL38" s="3">
         <v>45851.5</v>
@@ -5528,7 +5534,7 @@
         <v>124</v>
       </c>
       <c r="F39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5543,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -5618,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK39" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL39" s="3">
         <v>45851.5</v>
@@ -5632,10 +5638,10 @@
         <v>45851</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D40" t="s">
         <v>86</v>
@@ -5644,7 +5650,7 @@
         <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5659,88 +5665,88 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L40">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="M40">
-        <v>3.57</v>
+        <v>4.1</v>
       </c>
       <c r="N40">
-        <v>3.23</v>
+        <v>5.8</v>
       </c>
       <c r="O40">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="P40">
         <v>11.5</v>
       </c>
       <c r="Q40">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R40">
         <v>1.3</v>
       </c>
       <c r="S40">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T40">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U40">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V40">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA40">
         <v>4.2</v>
       </c>
       <c r="AB40">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC40">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AD40">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AE40">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF40">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH40">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AI40">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ40" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK40" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL40" s="3">
-        <v>45851.52083333334</v>
+        <v>45851.5</v>
       </c>
     </row>
     <row r="41" spans="1:38">
@@ -5748,10 +5754,10 @@
         <v>45851</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
         <v>86</v>
@@ -5760,7 +5766,7 @@
         <v>126</v>
       </c>
       <c r="F41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5775,88 +5781,88 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L41">
-        <v>3.03</v>
+        <v>1.89</v>
       </c>
       <c r="M41">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="N41">
-        <v>2.11</v>
+        <v>3.23</v>
       </c>
       <c r="O41">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="P41">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="Q41">
-        <v>1.81</v>
+        <v>2.63</v>
       </c>
       <c r="R41">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S41">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="U41">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="Z41">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AA41">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AC41">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="AD41">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AF41">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH41">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AI41">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AJ41" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK41" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL41" s="3">
-        <v>45851.5625</v>
+        <v>45851.52083333334</v>
       </c>
     </row>
     <row r="42" spans="1:38">
@@ -5867,7 +5873,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
         <v>86</v>
@@ -5876,7 +5882,7 @@
         <v>127</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5891,85 +5897,85 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L42">
-        <v>1.56</v>
+        <v>3.03</v>
       </c>
       <c r="M42">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="N42">
-        <v>4.3</v>
+        <v>2.11</v>
       </c>
       <c r="O42">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="P42">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="Q42">
+        <v>1.81</v>
+      </c>
+      <c r="R42">
+        <v>1.4</v>
+      </c>
+      <c r="S42">
+        <v>2.5</v>
+      </c>
+      <c r="T42">
+        <v>2.9</v>
+      </c>
+      <c r="U42">
+        <v>1.36</v>
+      </c>
+      <c r="V42">
+        <v>7.5</v>
+      </c>
+      <c r="W42">
+        <v>1.06</v>
+      </c>
+      <c r="X42">
+        <v>1.06</v>
+      </c>
+      <c r="Y42">
+        <v>8.5</v>
+      </c>
+      <c r="Z42">
+        <v>1.32</v>
+      </c>
+      <c r="AA42">
         <v>2.88</v>
       </c>
-      <c r="R42">
-        <v>1.3</v>
-      </c>
-      <c r="S42">
-        <v>3.4</v>
-      </c>
-      <c r="T42">
-        <v>2.5</v>
-      </c>
-      <c r="U42">
-        <v>1.5</v>
-      </c>
-      <c r="V42">
-        <v>6</v>
-      </c>
-      <c r="W42">
-        <v>1.13</v>
-      </c>
-      <c r="X42">
-        <v>1.04</v>
-      </c>
-      <c r="Y42">
-        <v>11</v>
-      </c>
-      <c r="Z42">
-        <v>1.22</v>
-      </c>
-      <c r="AA42">
-        <v>4.33</v>
-      </c>
       <c r="AB42">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="AD42">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="AE42">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI42">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL42" s="3">
         <v>45851.5625</v>
@@ -5992,7 +5998,7 @@
         <v>128</v>
       </c>
       <c r="F43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -6007,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L43">
         <v>2.16</v>
@@ -6028,34 +6034,34 @@
         <v>2.61</v>
       </c>
       <c r="R43">
+        <v>1.35</v>
+      </c>
+      <c r="S43">
+        <v>2.89</v>
+      </c>
+      <c r="T43">
+        <v>2.62</v>
+      </c>
+      <c r="U43">
         <v>1.44</v>
       </c>
-      <c r="S43">
-        <v>2.6</v>
-      </c>
-      <c r="T43">
-        <v>3</v>
-      </c>
-      <c r="U43">
-        <v>1.33</v>
-      </c>
       <c r="V43">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
         <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="Z43">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AA43">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="AB43">
         <v>1.96</v>
@@ -6064,28 +6070,28 @@
         <v>1.74</v>
       </c>
       <c r="AD43">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF43">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG43">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AH43">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="AI43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AJ43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL43" s="3">
         <v>45851.5625</v>
@@ -6096,10 +6102,10 @@
         <v>45851</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
         <v>86</v>
@@ -6108,7 +6114,7 @@
         <v>129</v>
       </c>
       <c r="F44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -6123,88 +6129,88 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L44">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="M44">
-        <v>3.17</v>
+        <v>4.1</v>
       </c>
       <c r="N44">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O44">
+        <v>1.44</v>
+      </c>
+      <c r="P44">
+        <v>11</v>
+      </c>
+      <c r="Q44">
+        <v>2.88</v>
+      </c>
+      <c r="R44">
+        <v>1.3</v>
+      </c>
+      <c r="S44">
+        <v>3.4</v>
+      </c>
+      <c r="T44">
+        <v>2.5</v>
+      </c>
+      <c r="U44">
         <v>1.5</v>
       </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>3.6</v>
-      </c>
-      <c r="R44">
-        <v>1.52</v>
-      </c>
-      <c r="S44">
-        <v>2.38</v>
-      </c>
-      <c r="T44">
-        <v>3.7</v>
-      </c>
-      <c r="U44">
-        <v>1.29</v>
-      </c>
       <c r="V44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="Z44">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AA44">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB44">
-        <v>2.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC44">
-        <v>1.4</v>
+        <v>2.13</v>
       </c>
       <c r="AD44">
+        <v>2.65</v>
+      </c>
+      <c r="AE44">
+        <v>1.48</v>
+      </c>
+      <c r="AF44">
+        <v>1.7</v>
+      </c>
+      <c r="AG44">
+        <v>2.05</v>
+      </c>
+      <c r="AH44">
         <v>5</v>
       </c>
-      <c r="AE44">
-        <v>1.12</v>
-      </c>
-      <c r="AF44">
-        <v>2.27</v>
-      </c>
-      <c r="AG44">
-        <v>1.6</v>
-      </c>
-      <c r="AH44">
-        <v>11</v>
-      </c>
       <c r="AI44">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AJ44" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK44" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL44" s="3">
-        <v>45851.56944444445</v>
+        <v>45851.5625</v>
       </c>
     </row>
     <row r="45" spans="1:38">
@@ -6212,7 +6218,7 @@
         <v>45851</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
         <v>79</v>
@@ -6224,7 +6230,7 @@
         <v>130</v>
       </c>
       <c r="F45" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6239,88 +6245,88 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L45">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="M45">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="O45">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R45">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S45">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="T45">
         <v>3.4</v>
       </c>
       <c r="U45">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V45">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="W45">
+        <v>1.05</v>
+      </c>
+      <c r="X45">
+        <v>1.07</v>
+      </c>
+      <c r="Y45">
+        <v>6.5</v>
+      </c>
+      <c r="Z45">
+        <v>1.53</v>
+      </c>
+      <c r="AA45">
+        <v>2.25</v>
+      </c>
+      <c r="AB45">
+        <v>2.65</v>
+      </c>
+      <c r="AC45">
+        <v>1.42</v>
+      </c>
+      <c r="AD45">
+        <v>5</v>
+      </c>
+      <c r="AE45">
+        <v>1.14</v>
+      </c>
+      <c r="AF45">
+        <v>2.4</v>
+      </c>
+      <c r="AG45">
+        <v>1.54</v>
+      </c>
+      <c r="AH45">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AI45">
         <v>1.04</v>
       </c>
-      <c r="X45">
-        <v>1.1</v>
-      </c>
-      <c r="Y45">
-        <v>6</v>
-      </c>
-      <c r="Z45">
-        <v>1.57</v>
-      </c>
-      <c r="AA45">
-        <v>2.2</v>
-      </c>
-      <c r="AB45">
-        <v>2.49</v>
-      </c>
-      <c r="AC45">
-        <v>1.48</v>
-      </c>
-      <c r="AD45">
-        <v>4.7</v>
-      </c>
-      <c r="AE45">
-        <v>1.15</v>
-      </c>
-      <c r="AF45">
-        <v>2.5</v>
-      </c>
-      <c r="AG45">
-        <v>1.48</v>
-      </c>
-      <c r="AH45">
-        <v>10</v>
-      </c>
-      <c r="AI45">
-        <v>1.02</v>
-      </c>
       <c r="AJ45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL45" s="3">
-        <v>45851.58333333334</v>
+        <v>45851.56944444445</v>
       </c>
     </row>
     <row r="46" spans="1:38">
@@ -6328,19 +6334,19 @@
         <v>45851</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
         <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F46" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6355,88 +6361,88 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L46">
-        <v>4</v>
+        <v>1.54</v>
       </c>
       <c r="M46">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="N46">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="O46">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="P46">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="R46">
+        <v>1.5</v>
+      </c>
+      <c r="S46">
+        <v>2.5</v>
+      </c>
+      <c r="T46">
+        <v>3.4</v>
+      </c>
+      <c r="U46">
+        <v>1.3</v>
+      </c>
+      <c r="V46">
+        <v>7.8</v>
+      </c>
+      <c r="W46">
+        <v>1.05</v>
+      </c>
+      <c r="X46">
+        <v>1.1</v>
+      </c>
+      <c r="Y46">
+        <v>6.5</v>
+      </c>
+      <c r="Z46">
         <v>1.57</v>
       </c>
-      <c r="S46">
-        <v>2.25</v>
-      </c>
-      <c r="T46">
-        <v>3.75</v>
-      </c>
-      <c r="U46">
-        <v>1.25</v>
-      </c>
-      <c r="V46">
-        <v>13</v>
-      </c>
-      <c r="W46">
-        <v>1.04</v>
-      </c>
-      <c r="X46">
-        <v>1.11</v>
-      </c>
-      <c r="Y46">
-        <v>6.25</v>
-      </c>
-      <c r="Z46">
-        <v>1.53</v>
-      </c>
       <c r="AA46">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AC46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD46">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="AE46">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AG46">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH46">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AI46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK46" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL46" s="3">
-        <v>45851.59375</v>
+        <v>45851.58333333334</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -6447,16 +6453,16 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
         <v>86</v>
       </c>
       <c r="E47" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6471,85 +6477,85 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L47">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N47">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="P47">
-        <v>14.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="R47">
+        <v>1.57</v>
+      </c>
+      <c r="S47">
+        <v>2.25</v>
+      </c>
+      <c r="T47">
+        <v>3.75</v>
+      </c>
+      <c r="U47">
         <v>1.25</v>
       </c>
-      <c r="S47">
-        <v>3.75</v>
-      </c>
-      <c r="T47">
-        <v>2.1</v>
-      </c>
-      <c r="U47">
-        <v>1.67</v>
-      </c>
       <c r="V47">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="W47">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
+        <v>1.11</v>
+      </c>
+      <c r="Y47">
+        <v>6.25</v>
+      </c>
+      <c r="Z47">
+        <v>1.53</v>
+      </c>
+      <c r="AA47">
+        <v>2.3</v>
+      </c>
+      <c r="AB47">
+        <v>2.7</v>
+      </c>
+      <c r="AC47">
+        <v>1.44</v>
+      </c>
+      <c r="AD47">
+        <v>5.25</v>
+      </c>
+      <c r="AE47">
+        <v>1.15</v>
+      </c>
+      <c r="AF47">
+        <v>2.25</v>
+      </c>
+      <c r="AG47">
+        <v>1.57</v>
+      </c>
+      <c r="AH47">
+        <v>10</v>
+      </c>
+      <c r="AI47">
         <v>1.04</v>
       </c>
-      <c r="Y47">
-        <v>10</v>
-      </c>
-      <c r="Z47">
-        <v>1.17</v>
-      </c>
-      <c r="AA47">
-        <v>5</v>
-      </c>
-      <c r="AB47">
-        <v>1.57</v>
-      </c>
-      <c r="AC47">
-        <v>2.15</v>
-      </c>
-      <c r="AD47">
-        <v>2.27</v>
-      </c>
-      <c r="AE47">
-        <v>1.56</v>
-      </c>
-      <c r="AF47">
-        <v>1.4</v>
-      </c>
-      <c r="AG47">
-        <v>2.75</v>
-      </c>
-      <c r="AH47">
-        <v>3.7</v>
-      </c>
-      <c r="AI47">
-        <v>1.25</v>
-      </c>
       <c r="AJ47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL47" s="3">
         <v>45851.59375</v>
@@ -6560,10 +6566,10 @@
         <v>45851</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D48" t="s">
         <v>86</v>
@@ -6572,7 +6578,7 @@
         <v>132</v>
       </c>
       <c r="F48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6587,88 +6593,88 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L48">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="M48">
-        <v>2.61</v>
+        <v>3.38</v>
       </c>
       <c r="N48">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O48">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q48">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="S48">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="T48">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="U48">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="V48">
+        <v>4.5</v>
+      </c>
+      <c r="W48">
+        <v>1.18</v>
+      </c>
+      <c r="X48">
+        <v>1.04</v>
+      </c>
+      <c r="Y48">
         <v>10</v>
       </c>
-      <c r="W48">
-        <v>1.02</v>
-      </c>
-      <c r="X48">
-        <v>1.11</v>
-      </c>
-      <c r="Y48">
-        <v>5.5</v>
-      </c>
       <c r="Z48">
+        <v>1.17</v>
+      </c>
+      <c r="AA48">
+        <v>5</v>
+      </c>
+      <c r="AB48">
         <v>1.57</v>
       </c>
-      <c r="AA48">
+      <c r="AC48">
         <v>2.15</v>
       </c>
-      <c r="AB48">
+      <c r="AD48">
+        <v>2.27</v>
+      </c>
+      <c r="AE48">
+        <v>1.56</v>
+      </c>
+      <c r="AF48">
+        <v>1.4</v>
+      </c>
+      <c r="AG48">
         <v>2.75</v>
       </c>
-      <c r="AC48">
-        <v>1.4</v>
-      </c>
-      <c r="AD48">
-        <v>5.25</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>2.25</v>
-      </c>
-      <c r="AG48">
-        <v>1.57</v>
-      </c>
       <c r="AH48">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="AI48">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AJ48" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK48" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL48" s="3">
-        <v>45851.625</v>
+        <v>45851.59375</v>
       </c>
     </row>
     <row r="49" spans="1:38">
@@ -6688,7 +6694,7 @@
         <v>133</v>
       </c>
       <c r="F49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -6703,85 +6709,85 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L49">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="M49">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="N49">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="O49">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R49">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S49">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V49">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="W49">
         <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Y49">
+        <v>4.6</v>
+      </c>
+      <c r="Z49">
+        <v>1.57</v>
+      </c>
+      <c r="AA49">
+        <v>2.15</v>
+      </c>
+      <c r="AB49">
+        <v>2.99</v>
+      </c>
+      <c r="AC49">
+        <v>1.34</v>
+      </c>
+      <c r="AD49">
         <v>5.5</v>
       </c>
-      <c r="Z49">
-        <v>1.58</v>
-      </c>
-      <c r="AA49">
-        <v>2.2</v>
-      </c>
-      <c r="AB49">
-        <v>2.37</v>
-      </c>
-      <c r="AC49">
-        <v>1.48</v>
-      </c>
-      <c r="AD49">
-        <v>5</v>
-      </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AG49">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH49">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AI49">
         <v>1.02</v>
       </c>
       <c r="AJ49" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK49" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL49" s="3">
         <v>45851.625</v>
@@ -6804,7 +6810,7 @@
         <v>134</v>
       </c>
       <c r="F50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -6819,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L50">
         <v>1.88</v>
@@ -6840,25 +6846,25 @@
         <v>2.88</v>
       </c>
       <c r="R50">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S50">
         <v>2.2</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V50">
         <v>10</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X50">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y50">
         <v>5.5</v>
@@ -6870,34 +6876,34 @@
         <v>2.25</v>
       </c>
       <c r="AB50">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AC50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD50">
         <v>5.5</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AG50">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH50">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AI50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ50" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK50" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL50" s="3">
         <v>45851.625</v>
@@ -6911,7 +6917,7 @@
         <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
         <v>86</v>
@@ -6920,7 +6926,7 @@
         <v>135</v>
       </c>
       <c r="F51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -6935,85 +6941,85 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L51">
-        <v>1.95</v>
+        <v>2.71</v>
       </c>
       <c r="M51">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="O51">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="P51">
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB51">
+        <v>2.37</v>
+      </c>
+      <c r="AC51">
+        <v>1.48</v>
+      </c>
+      <c r="AD51">
+        <v>5.75</v>
+      </c>
+      <c r="AE51">
+        <v>1.09</v>
+      </c>
+      <c r="AF51">
+        <v>2.2</v>
+      </c>
+      <c r="AG51">
         <v>1.53</v>
       </c>
-      <c r="AC51">
-        <v>2.38</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
-      <c r="AG51">
-        <v>0</v>
-      </c>
       <c r="AH51">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AI51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL51" s="3">
         <v>45851.625</v>
@@ -7024,10 +7030,10 @@
         <v>45851</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
         <v>86</v>
@@ -7036,7 +7042,7 @@
         <v>136</v>
       </c>
       <c r="F52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -7051,88 +7057,88 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L52">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="M52">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="N52">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="O52">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC52">
-        <v>1.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD52">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH52">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI52">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK52" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL52" s="3">
-        <v>45851.64583333334</v>
+        <v>45851.625</v>
       </c>
     </row>
     <row r="53" spans="1:38">
@@ -7140,7 +7146,7 @@
         <v>45851</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
         <v>79</v>
@@ -7152,7 +7158,7 @@
         <v>137</v>
       </c>
       <c r="F53" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7167,88 +7173,88 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L53">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="M53">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="N53">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="O53">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P53">
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S53">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="T53">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="U53">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V53">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W53">
         <v>1.02</v>
       </c>
       <c r="X53">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y53">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Z53">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AA53">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB53">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="AC53">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD53">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AG53">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH53">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AI53">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL53" s="3">
-        <v>45851.65625</v>
+        <v>45851.64583333334</v>
       </c>
     </row>
     <row r="54" spans="1:38">
@@ -7256,10 +7262,10 @@
         <v>45851</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
         <v>86</v>
@@ -7268,7 +7274,7 @@
         <v>138</v>
       </c>
       <c r="F54" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7283,88 +7289,88 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L54">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="M54">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="N54">
-        <v>3.37</v>
+        <v>3.61</v>
       </c>
       <c r="O54">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P54">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="R54">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="S54">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T54">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="U54">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V54">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y54">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="Z54">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AA54">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB54">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="AC54">
+        <v>1.39</v>
+      </c>
+      <c r="AD54">
+        <v>5.5</v>
+      </c>
+      <c r="AE54">
+        <v>1.12</v>
+      </c>
+      <c r="AF54">
+        <v>2.4</v>
+      </c>
+      <c r="AG54">
         <v>1.62</v>
       </c>
-      <c r="AD54">
-        <v>3.8</v>
-      </c>
-      <c r="AE54">
-        <v>1.22</v>
-      </c>
-      <c r="AF54">
-        <v>1.91</v>
-      </c>
-      <c r="AG54">
-        <v>1.8</v>
-      </c>
       <c r="AH54">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AI54">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL54" s="3">
-        <v>45851.66666666666</v>
+        <v>45851.65625</v>
       </c>
     </row>
     <row r="55" spans="1:38">
@@ -7384,7 +7390,7 @@
         <v>139</v>
       </c>
       <c r="F55" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7399,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L55">
         <v>1.78</v>
@@ -7420,10 +7426,10 @@
         <v>3.4</v>
       </c>
       <c r="R55">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T55">
         <v>3.4</v>
@@ -7435,13 +7441,13 @@
         <v>10</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X55">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z55">
         <v>1.52</v>
@@ -7468,16 +7474,16 @@
         <v>1.57</v>
       </c>
       <c r="AH55">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AI55">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ55" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK55" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL55" s="3">
         <v>45851.66666666666</v>
@@ -7491,7 +7497,7 @@
         <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D56" t="s">
         <v>86</v>
@@ -7500,7 +7506,7 @@
         <v>140</v>
       </c>
       <c r="F56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7515,85 +7521,85 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L56">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="M56">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="N56">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="O56">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q56">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R56">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="S56">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="T56">
-        <v>1.99</v>
+        <v>2.9</v>
       </c>
       <c r="U56">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="V56">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="W56">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Z56">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AA56">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AB56">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AC56">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="AD56">
+        <v>3.6</v>
+      </c>
+      <c r="AE56">
+        <v>1.25</v>
+      </c>
+      <c r="AF56">
+        <v>1.75</v>
+      </c>
+      <c r="AG56">
         <v>1.95</v>
       </c>
-      <c r="AE56">
-        <v>1.82</v>
-      </c>
-      <c r="AF56">
-        <v>1.56</v>
-      </c>
-      <c r="AG56">
-        <v>2.25</v>
-      </c>
       <c r="AH56">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="AI56">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AJ56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL56" s="3">
         <v>45851.66666666666</v>
@@ -7604,10 +7610,10 @@
         <v>45851</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
         <v>86</v>
@@ -7616,7 +7622,7 @@
         <v>141</v>
       </c>
       <c r="F57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7631,88 +7637,88 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L57">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="M57">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="N57">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="O57">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="P57">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R57">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="S57">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="T57">
-        <v>3.5</v>
+        <v>2.01</v>
       </c>
       <c r="U57">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="V57">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="X57">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Z57">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="AA57">
+        <v>4.3</v>
+      </c>
+      <c r="AB57">
+        <v>1.4</v>
+      </c>
+      <c r="AC57">
         <v>2.4</v>
       </c>
-      <c r="AB57">
-        <v>2.37</v>
-      </c>
-      <c r="AC57">
-        <v>1.48</v>
-      </c>
       <c r="AD57">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="AE57">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="AF57">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AG57">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH57">
-        <v>10</v>
+        <v>3.04</v>
       </c>
       <c r="AI57">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="AJ57" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK57" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL57" s="3">
-        <v>45851.6875</v>
+        <v>45851.66666666666</v>
       </c>
     </row>
     <row r="58" spans="1:38">
@@ -7723,16 +7729,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D58" t="s">
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="F58" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7747,85 +7753,85 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L58">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N58">
+        <v>4.75</v>
+      </c>
+      <c r="O58">
+        <v>1.5</v>
+      </c>
+      <c r="P58">
+        <v>6.5</v>
+      </c>
+      <c r="Q58">
         <v>3.25</v>
       </c>
-      <c r="O58">
-        <v>1.91</v>
-      </c>
-      <c r="P58">
-        <v>7.4</v>
-      </c>
-      <c r="Q58">
-        <v>2.25</v>
-      </c>
       <c r="R58">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S58">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="T58">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U58">
         <v>1.29</v>
       </c>
       <c r="V58">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y58">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Z58">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AA58">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AB58">
+        <v>2.5</v>
+      </c>
+      <c r="AC58">
+        <v>1.5</v>
+      </c>
+      <c r="AD58">
+        <v>4.75</v>
+      </c>
+      <c r="AE58">
+        <v>1.18</v>
+      </c>
+      <c r="AF58">
         <v>2.25</v>
       </c>
-      <c r="AC58">
-        <v>1.53</v>
-      </c>
-      <c r="AD58">
-        <v>4</v>
-      </c>
-      <c r="AE58">
-        <v>1.19</v>
-      </c>
-      <c r="AF58">
-        <v>1.98</v>
-      </c>
       <c r="AG58">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH58">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="AI58">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ58" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK58" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL58" s="3">
         <v>45851.6875</v>
@@ -7845,7 +7851,7 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F59" t="s">
         <v>190</v>
@@ -7863,37 +7869,37 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L59">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M59">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="O59">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P59">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q59">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="R59">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S59">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T59">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U59">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V59">
         <v>11</v>
@@ -7902,34 +7908,34 @@
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y59">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Z59">
+        <v>1.5</v>
+      </c>
+      <c r="AA59">
+        <v>2.38</v>
+      </c>
+      <c r="AB59">
+        <v>2.6</v>
+      </c>
+      <c r="AC59">
         <v>1.48</v>
       </c>
-      <c r="AA59">
-        <v>2.6</v>
-      </c>
-      <c r="AB59">
-        <v>2.5</v>
-      </c>
-      <c r="AC59">
-        <v>1.5</v>
-      </c>
       <c r="AD59">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE59">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF59">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG59">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH59">
         <v>9.5</v>
@@ -7938,10 +7944,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ59" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK59" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL59" s="3">
         <v>45851.6875</v>
@@ -7955,16 +7961,16 @@
         <v>57</v>
       </c>
       <c r="C60" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D60" t="s">
         <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7979,40 +7985,40 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L60">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="M60">
+        <v>2.86</v>
+      </c>
+      <c r="N60">
+        <v>4.1</v>
+      </c>
+      <c r="O60">
+        <v>1.62</v>
+      </c>
+      <c r="P60">
+        <v>7.5</v>
+      </c>
+      <c r="Q60">
         <v>3</v>
       </c>
-      <c r="N60">
-        <v>3.25</v>
-      </c>
-      <c r="O60">
-        <v>1.83</v>
-      </c>
-      <c r="P60">
-        <v>6</v>
-      </c>
-      <c r="Q60">
-        <v>2.4</v>
-      </c>
       <c r="R60">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S60">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="T60">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="U60">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V60">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W60">
         <v>1.05</v>
@@ -8021,25 +8027,25 @@
         <v>1.11</v>
       </c>
       <c r="Y60">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Z60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA60">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB60">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AC60">
         <v>1.48</v>
       </c>
       <c r="AD60">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF60">
         <v>2.1</v>
@@ -8048,16 +8054,16 @@
         <v>1.67</v>
       </c>
       <c r="AH60">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI60">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ60" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK60" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL60" s="3">
         <v>45851.6875</v>
@@ -8068,10 +8074,10 @@
         <v>45851</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D61" t="s">
         <v>86</v>
@@ -8080,7 +8086,7 @@
         <v>143</v>
       </c>
       <c r="F61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8095,88 +8101,88 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L61">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="M61">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="N61">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="O61">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q61">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="S61">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="T61">
-        <v>2.11</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="V61">
-        <v>4.5</v>
+        <v>9.25</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z61">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AA61">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="AB61">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="AC61">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="AD61">
-        <v>2.13</v>
+        <v>3.8</v>
       </c>
       <c r="AE61">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AG61">
-        <v>2.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH61">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="AI61">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="AJ61" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK61" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL61" s="3">
-        <v>45851.70833333334</v>
+        <v>45851.6875</v>
       </c>
     </row>
     <row r="62" spans="1:38">
@@ -8184,10 +8190,10 @@
         <v>45851</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D62" t="s">
         <v>86</v>
@@ -8196,7 +8202,7 @@
         <v>144</v>
       </c>
       <c r="F62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8211,88 +8217,88 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L62">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="M62">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N62">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O62">
+        <v>2</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>1.8</v>
+      </c>
+      <c r="R62">
+        <v>1.22</v>
+      </c>
+      <c r="S62">
+        <v>3.8</v>
+      </c>
+      <c r="T62">
+        <v>2.05</v>
+      </c>
+      <c r="U62">
+        <v>1.62</v>
+      </c>
+      <c r="V62">
+        <v>4.33</v>
+      </c>
+      <c r="W62">
+        <v>1.18</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>1.11</v>
+      </c>
+      <c r="AA62">
+        <v>5.5</v>
+      </c>
+      <c r="AB62">
+        <v>1.5</v>
+      </c>
+      <c r="AC62">
+        <v>2.5</v>
+      </c>
+      <c r="AD62">
+        <v>2.07</v>
+      </c>
+      <c r="AE62">
         <v>1.67</v>
       </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>2.6</v>
-      </c>
-      <c r="R62">
-        <v>1.48</v>
-      </c>
-      <c r="S62">
-        <v>2.5</v>
-      </c>
-      <c r="T62">
-        <v>3</v>
-      </c>
-      <c r="U62">
-        <v>1.33</v>
-      </c>
-      <c r="V62">
-        <v>9</v>
-      </c>
-      <c r="W62">
-        <v>1.05</v>
-      </c>
-      <c r="X62">
-        <v>1.07</v>
-      </c>
-      <c r="Y62">
-        <v>7</v>
-      </c>
-      <c r="Z62">
-        <v>1.33</v>
-      </c>
-      <c r="AA62">
+      <c r="AF62">
+        <v>1.38</v>
+      </c>
+      <c r="AG62">
         <v>2.8</v>
       </c>
-      <c r="AB62">
-        <v>2</v>
-      </c>
-      <c r="AC62">
-        <v>1.71</v>
-      </c>
-      <c r="AD62">
-        <v>3.8</v>
-      </c>
-      <c r="AE62">
-        <v>1.22</v>
-      </c>
-      <c r="AF62">
-        <v>1.91</v>
-      </c>
-      <c r="AG62">
-        <v>1.75</v>
-      </c>
       <c r="AH62">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="AI62">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AJ62" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK62" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL62" s="3">
-        <v>45851.75</v>
+        <v>45851.70833333334</v>
       </c>
     </row>
     <row r="63" spans="1:38">
@@ -8300,10 +8306,10 @@
         <v>45851</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D63" t="s">
         <v>86</v>
@@ -8312,7 +8318,7 @@
         <v>145</v>
       </c>
       <c r="F63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8327,88 +8333,88 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L63">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="M63">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N63">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="O63">
         <v>1.67</v>
       </c>
       <c r="P63">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
       </c>
       <c r="R63">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S63">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T63">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U63">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V63">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
         <v>7</v>
       </c>
       <c r="Z63">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AA63">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AB63">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC63">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AD63">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AE63">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG63">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH63">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AI63">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL63" s="3">
-        <v>45851.77083333334</v>
+        <v>45851.75</v>
       </c>
     </row>
     <row r="64" spans="1:38">
@@ -8428,7 +8434,7 @@
         <v>146</v>
       </c>
       <c r="F64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8443,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L64">
         <v>2.37</v>
@@ -8464,64 +8470,64 @@
         <v>2.11</v>
       </c>
       <c r="R64">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S64">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T64">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="U64">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V64">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W64">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y64">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z64">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA64">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AB64">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC64">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD64">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AE64">
         <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH64">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AI64">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ64" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK64" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL64" s="3">
         <v>45851.77083333334</v>
@@ -8532,19 +8538,19 @@
         <v>45851</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
         <v>86</v>
       </c>
       <c r="E65" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="F65" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -8559,88 +8565,88 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L65">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="M65">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N65">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="O65">
+        <v>1.67</v>
+      </c>
+      <c r="P65">
+        <v>6.75</v>
+      </c>
+      <c r="Q65">
+        <v>2.6</v>
+      </c>
+      <c r="R65">
+        <v>1.44</v>
+      </c>
+      <c r="S65">
+        <v>2.63</v>
+      </c>
+      <c r="T65">
+        <v>3.1</v>
+      </c>
+      <c r="U65">
+        <v>1.3</v>
+      </c>
+      <c r="V65">
+        <v>9.5</v>
+      </c>
+      <c r="W65">
+        <v>1.06</v>
+      </c>
+      <c r="X65">
+        <v>1.1</v>
+      </c>
+      <c r="Y65">
+        <v>7</v>
+      </c>
+      <c r="Z65">
+        <v>1.45</v>
+      </c>
+      <c r="AA65">
+        <v>2.7</v>
+      </c>
+      <c r="AB65">
+        <v>2.25</v>
+      </c>
+      <c r="AC65">
+        <v>1.53</v>
+      </c>
+      <c r="AD65">
+        <v>4.5</v>
+      </c>
+      <c r="AE65">
+        <v>1.16</v>
+      </c>
+      <c r="AF65">
+        <v>2</v>
+      </c>
+      <c r="AG65">
         <v>1.73</v>
       </c>
-      <c r="P65">
-        <v>5.5</v>
-      </c>
-      <c r="Q65">
-        <v>2.75</v>
-      </c>
-      <c r="R65">
-        <v>1.62</v>
-      </c>
-      <c r="S65">
-        <v>2.2</v>
-      </c>
-      <c r="T65">
-        <v>4</v>
-      </c>
-      <c r="U65">
-        <v>1.22</v>
-      </c>
-      <c r="V65">
-        <v>13</v>
-      </c>
-      <c r="W65">
-        <v>1.04</v>
-      </c>
-      <c r="X65">
-        <v>1.12</v>
-      </c>
-      <c r="Y65">
-        <v>5.75</v>
-      </c>
-      <c r="Z65">
-        <v>1.58</v>
-      </c>
-      <c r="AA65">
-        <v>2.2</v>
-      </c>
-      <c r="AB65">
-        <v>2.88</v>
-      </c>
-      <c r="AC65">
-        <v>1.4</v>
-      </c>
-      <c r="AD65">
-        <v>5.75</v>
-      </c>
-      <c r="AE65">
-        <v>1.12</v>
-      </c>
-      <c r="AF65">
-        <v>2.38</v>
-      </c>
-      <c r="AG65">
-        <v>1.53</v>
-      </c>
       <c r="AH65">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI65">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ65" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK65" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL65" s="3">
-        <v>45851.78125</v>
+        <v>45851.77083333334</v>
       </c>
     </row>
     <row r="66" spans="1:38">
@@ -8648,19 +8654,19 @@
         <v>45851</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D66" t="s">
         <v>86</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="F66" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -8675,88 +8681,88 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L66">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="M66">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N66">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O66">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q66">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R66">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="S66">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T66">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U66">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V66">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y66">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="Z66">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AA66">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB66">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AC66">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AD66">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AE66">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG66">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AH66">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI66">
         <v>1.03</v>
       </c>
       <c r="AJ66" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK66" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL66" s="3">
-        <v>45851.79166666666</v>
+        <v>45851.78125</v>
       </c>
     </row>
     <row r="67" spans="1:38">
@@ -8776,7 +8782,7 @@
         <v>148</v>
       </c>
       <c r="F67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -8791,16 +8797,16 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L67">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M67">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="N67">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O67">
         <v>1.36</v>
@@ -8815,61 +8821,61 @@
         <v>1.51</v>
       </c>
       <c r="S67">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="T67">
         <v>3.3</v>
       </c>
       <c r="U67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V67">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="W67">
         <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z67">
         <v>1.41</v>
       </c>
       <c r="AA67">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AB67">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AC67">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD67">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AE67">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AG67">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH67">
         <v>10</v>
       </c>
       <c r="AI67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ67" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK67" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL67" s="3">
         <v>45851.79166666666</v>
@@ -8883,7 +8889,7 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D68" t="s">
         <v>86</v>
@@ -8892,7 +8898,7 @@
         <v>149</v>
       </c>
       <c r="F68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -8907,85 +8913,85 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L68">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="M68">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N68">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="O68">
         <v>1.67</v>
       </c>
       <c r="P68">
+        <v>6.75</v>
+      </c>
+      <c r="Q68">
+        <v>2.63</v>
+      </c>
+      <c r="R68">
+        <v>1.44</v>
+      </c>
+      <c r="S68">
+        <v>2.5</v>
+      </c>
+      <c r="T68">
+        <v>3.3</v>
+      </c>
+      <c r="U68">
+        <v>1.3</v>
+      </c>
+      <c r="V68">
+        <v>8.9</v>
+      </c>
+      <c r="W68">
+        <v>1.05</v>
+      </c>
+      <c r="X68">
+        <v>1.08</v>
+      </c>
+      <c r="Y68">
         <v>6.5</v>
       </c>
-      <c r="Q68">
-        <v>2.75</v>
-      </c>
-      <c r="R68">
-        <v>1.53</v>
-      </c>
-      <c r="S68">
-        <v>2.33</v>
-      </c>
-      <c r="T68">
-        <v>3.4</v>
-      </c>
-      <c r="U68">
-        <v>1.25</v>
-      </c>
-      <c r="V68">
-        <v>9.75</v>
-      </c>
-      <c r="W68">
-        <v>1.03</v>
-      </c>
-      <c r="X68">
-        <v>1.12</v>
-      </c>
-      <c r="Y68">
-        <v>6</v>
-      </c>
       <c r="Z68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA68">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AB68">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC68">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD68">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AG68">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH68">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI68">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ68" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK68" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL68" s="3">
         <v>45851.79166666666</v>
@@ -8999,7 +9005,7 @@
         <v>62</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D69" t="s">
         <v>86</v>
@@ -9008,7 +9014,7 @@
         <v>150</v>
       </c>
       <c r="F69" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9023,85 +9029,85 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L69">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="M69">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N69">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O69">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="P69">
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S69">
         <v>3.4</v>
       </c>
       <c r="T69">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U69">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V69">
         <v>5</v>
       </c>
       <c r="W69">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC69">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AD69">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG69">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AH69">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI69">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK69" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL69" s="3">
         <v>45851.79166666666</v>
@@ -9115,7 +9121,7 @@
         <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D70" t="s">
         <v>86</v>
@@ -9124,7 +9130,7 @@
         <v>151</v>
       </c>
       <c r="F70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9139,85 +9145,85 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L70">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="M70">
+        <v>3.8</v>
+      </c>
+      <c r="N70">
         <v>3.6</v>
       </c>
-      <c r="N70">
-        <v>4.2</v>
-      </c>
       <c r="O70">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P70">
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R70">
         <v>1.3</v>
       </c>
       <c r="S70">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T70">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U70">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V70">
         <v>5</v>
       </c>
       <c r="W70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB70">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC70">
         <v>2.2</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF70">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL70" s="3">
         <v>45851.79166666666</v>
@@ -9228,10 +9234,10 @@
         <v>45851</v>
       </c>
       <c r="B71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D71" t="s">
         <v>86</v>
@@ -9240,7 +9246,7 @@
         <v>152</v>
       </c>
       <c r="F71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -9255,88 +9261,88 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L71">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M71">
-        <v>4.33</v>
+        <v>2.98</v>
       </c>
       <c r="N71">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O71">
         <v>1.67</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q71">
+        <v>2.75</v>
+      </c>
+      <c r="R71">
+        <v>1.44</v>
+      </c>
+      <c r="S71">
+        <v>2.5</v>
+      </c>
+      <c r="T71">
+        <v>3.3</v>
+      </c>
+      <c r="U71">
+        <v>1.3</v>
+      </c>
+      <c r="V71">
+        <v>9.25</v>
+      </c>
+      <c r="W71">
+        <v>1.05</v>
+      </c>
+      <c r="X71">
+        <v>1.1</v>
+      </c>
+      <c r="Y71">
+        <v>6</v>
+      </c>
+      <c r="Z71">
+        <v>1.44</v>
+      </c>
+      <c r="AA71">
+        <v>2.43</v>
+      </c>
+      <c r="AB71">
+        <v>2.37</v>
+      </c>
+      <c r="AC71">
+        <v>1.48</v>
+      </c>
+      <c r="AD71">
+        <v>4.5</v>
+      </c>
+      <c r="AE71">
+        <v>1.13</v>
+      </c>
+      <c r="AF71">
         <v>2.1</v>
       </c>
-      <c r="R71">
-        <v>1.22</v>
-      </c>
-      <c r="S71">
-        <v>3.8</v>
-      </c>
-      <c r="T71">
-        <v>2.05</v>
-      </c>
-      <c r="U71">
-        <v>1.68</v>
-      </c>
-      <c r="V71">
-        <v>4.33</v>
-      </c>
-      <c r="W71">
-        <v>1.18</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>1.11</v>
-      </c>
-      <c r="AA71">
-        <v>5.5</v>
-      </c>
-      <c r="AB71">
-        <v>1.42</v>
-      </c>
-      <c r="AC71">
-        <v>2.62</v>
-      </c>
-      <c r="AD71">
-        <v>2.05</v>
-      </c>
-      <c r="AE71">
-        <v>1.7</v>
-      </c>
-      <c r="AF71">
-        <v>1.36</v>
-      </c>
       <c r="AG71">
-        <v>2.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH71">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AI71">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="AJ71" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK71" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL71" s="3">
-        <v>45851.83333333334</v>
+        <v>45851.79166666666</v>
       </c>
     </row>
     <row r="72" spans="1:38">
@@ -9356,7 +9362,7 @@
         <v>153</v>
       </c>
       <c r="F72" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -9371,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L72">
         <v>2.06</v>
@@ -9446,10 +9452,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ72" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK72" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL72" s="3">
         <v>45851.83333333334</v>
@@ -9472,7 +9478,7 @@
         <v>154</v>
       </c>
       <c r="F73" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -9487,85 +9493,85 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L73">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="M73">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="N73">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="O73">
+        <v>1.67</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>2.1</v>
+      </c>
+      <c r="R73">
+        <v>1.22</v>
+      </c>
+      <c r="S73">
+        <v>3.6</v>
+      </c>
+      <c r="T73">
+        <v>2.05</v>
+      </c>
+      <c r="U73">
         <v>1.62</v>
       </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>2.38</v>
-      </c>
-      <c r="R73">
-        <v>1.3</v>
-      </c>
-      <c r="S73">
-        <v>3.5</v>
-      </c>
-      <c r="T73">
-        <v>2.4</v>
-      </c>
-      <c r="U73">
-        <v>1.53</v>
-      </c>
       <c r="V73">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="W73">
+        <v>1.18</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
         <v>1.11</v>
       </c>
-      <c r="X73">
-        <v>1.01</v>
-      </c>
-      <c r="Y73">
-        <v>11</v>
-      </c>
-      <c r="Z73">
-        <v>1.14</v>
-      </c>
       <c r="AA73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB73">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AC73">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="AD73">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AE73">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AF73">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG73">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH73">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AI73">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AJ73" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK73" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL73" s="3">
         <v>45851.83333333334</v>
@@ -9576,10 +9582,10 @@
         <v>45851</v>
       </c>
       <c r="B74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D74" t="s">
         <v>86</v>
@@ -9588,7 +9594,7 @@
         <v>155</v>
       </c>
       <c r="F74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -9603,88 +9609,88 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L74">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="M74">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="N74">
-        <v>3.57</v>
+        <v>2.05</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P74">
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R74">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S74">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T74">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="U74">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V74">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="W74">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z74">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AA74">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="AB74">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="AC74">
+        <v>2.1</v>
+      </c>
+      <c r="AD74">
+        <v>2.57</v>
+      </c>
+      <c r="AE74">
+        <v>1.45</v>
+      </c>
+      <c r="AF74">
         <v>1.57</v>
       </c>
-      <c r="AD74">
-        <v>4.6</v>
-      </c>
-      <c r="AE74">
-        <v>1.18</v>
-      </c>
-      <c r="AF74">
-        <v>2</v>
-      </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AH74">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AI74">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AJ74" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK74" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL74" s="3">
-        <v>45851.85416666666</v>
+        <v>45851.83333333334</v>
       </c>
     </row>
     <row r="75" spans="1:38">
@@ -9704,7 +9710,7 @@
         <v>156</v>
       </c>
       <c r="F75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -9719,13 +9725,13 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L75">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="M75">
-        <v>3.95</v>
+        <v>3.81</v>
       </c>
       <c r="N75">
         <v>3.68</v>
@@ -9740,22 +9746,22 @@
         <v>2.05</v>
       </c>
       <c r="R75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S75">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T75">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="U75">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V75">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="W75">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -9764,40 +9770,40 @@
         <v>11</v>
       </c>
       <c r="Z75">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AA75">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="AB75">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC75">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD75">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AE75">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF75">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG75">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AH75">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI75">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AJ75" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK75" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL75" s="3">
         <v>45851.85416666666</v>
@@ -9820,7 +9826,7 @@
         <v>157</v>
       </c>
       <c r="F76" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -9835,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L76">
         <v>1.67</v>
@@ -9850,52 +9856,52 @@
         <v>1.44</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Q76">
         <v>3.25</v>
       </c>
       <c r="R76">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S76">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T76">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V76">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z76">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AA76">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AB76">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC76">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD76">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AE76">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
         <v>2.1</v>
@@ -9904,16 +9910,16 @@
         <v>1.7</v>
       </c>
       <c r="AH76">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AI76">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL76" s="3">
         <v>45851.85416666666</v>
@@ -9924,10 +9930,10 @@
         <v>45851</v>
       </c>
       <c r="B77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D77" t="s">
         <v>86</v>
@@ -9936,7 +9942,7 @@
         <v>158</v>
       </c>
       <c r="F77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -9951,88 +9957,88 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L77">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="M77">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="N77">
+        <v>3.57</v>
+      </c>
+      <c r="O77">
+        <v>1.87</v>
+      </c>
+      <c r="P77">
         <v>7</v>
       </c>
-      <c r="O77">
-        <v>1.29</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
       <c r="Q77">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R77">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="S77">
-        <v>3.28</v>
+        <v>2.42</v>
       </c>
       <c r="T77">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="U77">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z77">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AA77">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB77">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="AC77">
-        <v>2.56</v>
+        <v>1.53</v>
       </c>
       <c r="AD77">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="AE77">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AG77">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH77">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI77">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ77" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK77" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL77" s="3">
-        <v>45851.875</v>
+        <v>45851.85416666666</v>
       </c>
     </row>
     <row r="78" spans="1:38">
@@ -10043,16 +10049,16 @@
         <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D78" t="s">
         <v>86</v>
       </c>
       <c r="E78" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="F78" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10067,85 +10073,85 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L78">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="M78">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N78">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O78">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P78">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R78">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="S78">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="T78">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="U78">
+        <v>1.62</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>1.12</v>
+      </c>
+      <c r="AA78">
+        <v>4.8</v>
+      </c>
+      <c r="AB78">
+        <v>1.45</v>
+      </c>
+      <c r="AC78">
+        <v>2.45</v>
+      </c>
+      <c r="AD78">
+        <v>2.1</v>
+      </c>
+      <c r="AE78">
+        <v>1.6</v>
+      </c>
+      <c r="AF78">
+        <v>1.87</v>
+      </c>
+      <c r="AG78">
+        <v>1.83</v>
+      </c>
+      <c r="AH78">
+        <v>3.5</v>
+      </c>
+      <c r="AI78">
         <v>1.25</v>
       </c>
-      <c r="V78">
-        <v>11</v>
-      </c>
-      <c r="W78">
-        <v>1.05</v>
-      </c>
-      <c r="X78">
-        <v>1.1</v>
-      </c>
-      <c r="Y78">
-        <v>6.5</v>
-      </c>
-      <c r="Z78">
-        <v>1.45</v>
-      </c>
-      <c r="AA78">
-        <v>2.5</v>
-      </c>
-      <c r="AB78">
-        <v>2.6</v>
-      </c>
-      <c r="AC78">
-        <v>1.48</v>
-      </c>
-      <c r="AD78">
-        <v>5.25</v>
-      </c>
-      <c r="AE78">
-        <v>1.15</v>
-      </c>
-      <c r="AF78">
-        <v>2.75</v>
-      </c>
-      <c r="AG78">
-        <v>1.4</v>
-      </c>
-      <c r="AH78">
-        <v>10</v>
-      </c>
-      <c r="AI78">
-        <v>1.04</v>
-      </c>
       <c r="AJ78" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK78" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL78" s="3">
         <v>45851.875</v>
@@ -10165,10 +10171,10 @@
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10183,43 +10189,43 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L79">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M79">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N79">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P79">
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S79">
         <v>3.6</v>
       </c>
       <c r="T79">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="U79">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V79">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="W79">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X79">
         <v>0</v>
@@ -10228,40 +10234,40 @@
         <v>0</v>
       </c>
       <c r="Z79">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AA79">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AB79">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC79">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AD79">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE79">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF79">
         <v>1.42</v>
       </c>
       <c r="AG79">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AH79">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI79">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ79" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK79" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL79" s="3">
         <v>45851.875</v>
@@ -10275,16 +10281,16 @@
         <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D80" t="s">
         <v>86</v>
       </c>
       <c r="E80" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="F80" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10299,85 +10305,85 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R80">
+        <v>1.57</v>
+      </c>
+      <c r="S80">
+        <v>2.25</v>
+      </c>
+      <c r="T80">
+        <v>3.75</v>
+      </c>
+      <c r="U80">
         <v>1.25</v>
       </c>
-      <c r="S80">
-        <v>3.6</v>
-      </c>
-      <c r="T80">
-        <v>2.1</v>
-      </c>
-      <c r="U80">
-        <v>1.67</v>
-      </c>
       <c r="V80">
-        <v>4.33</v>
+        <v>11</v>
       </c>
       <c r="W80">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z80">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="AA80">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="AB80">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="AC80">
-        <v>2.6</v>
+        <v>1.48</v>
       </c>
       <c r="AD80">
-        <v>2.06</v>
+        <v>5.25</v>
       </c>
       <c r="AE80">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AF80">
-        <v>1.42</v>
+        <v>2.75</v>
       </c>
       <c r="AG80">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="AH80">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="AI80">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AJ80" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK80" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL80" s="3">
         <v>45851.875</v>
@@ -10388,10 +10394,10 @@
         <v>45851</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
         <v>86</v>
@@ -10400,7 +10406,7 @@
         <v>161</v>
       </c>
       <c r="F81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10415,88 +10421,88 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L81">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="M81">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N81">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="O81">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="P81">
         <v>0</v>
       </c>
       <c r="Q81">
+        <v>2.05</v>
+      </c>
+      <c r="R81">
+        <v>1.25</v>
+      </c>
+      <c r="S81">
+        <v>3.6</v>
+      </c>
+      <c r="T81">
+        <v>2.16</v>
+      </c>
+      <c r="U81">
+        <v>1.62</v>
+      </c>
+      <c r="V81">
+        <v>4.75</v>
+      </c>
+      <c r="W81">
+        <v>1.15</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>1.14</v>
+      </c>
+      <c r="AA81">
+        <v>5</v>
+      </c>
+      <c r="AB81">
+        <v>1.48</v>
+      </c>
+      <c r="AC81">
+        <v>2.43</v>
+      </c>
+      <c r="AD81">
+        <v>2.19</v>
+      </c>
+      <c r="AE81">
+        <v>1.55</v>
+      </c>
+      <c r="AF81">
         <v>1.44</v>
       </c>
-      <c r="R81">
-        <v>1.33</v>
-      </c>
-      <c r="S81">
-        <v>3.25</v>
-      </c>
-      <c r="T81">
-        <v>2.5</v>
-      </c>
-      <c r="U81">
-        <v>1.5</v>
-      </c>
-      <c r="V81">
-        <v>5</v>
-      </c>
-      <c r="W81">
-        <v>1.14</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
-      </c>
-      <c r="Z81">
-        <v>0</v>
-      </c>
-      <c r="AA81">
-        <v>0</v>
-      </c>
-      <c r="AB81">
-        <v>1.65</v>
-      </c>
-      <c r="AC81">
-        <v>2.1</v>
-      </c>
-      <c r="AD81">
-        <v>0</v>
-      </c>
-      <c r="AE81">
-        <v>0</v>
-      </c>
-      <c r="AF81">
-        <v>1.8</v>
-      </c>
       <c r="AG81">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AK81" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL81" s="3">
-        <v>45851.91666666666</v>
+        <v>45851.875</v>
       </c>
     </row>
     <row r="82" spans="1:38">
@@ -10504,10 +10510,10 @@
         <v>45851</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D82" t="s">
         <v>86</v>
@@ -10516,7 +10522,7 @@
         <v>162</v>
       </c>
       <c r="F82" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -10531,87 +10537,203 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L82">
+        <v>4.3</v>
+      </c>
+      <c r="M82">
+        <v>3.65</v>
+      </c>
+      <c r="N82">
+        <v>1.68</v>
+      </c>
+      <c r="O82">
+        <v>2.88</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>1.44</v>
+      </c>
+      <c r="R82">
+        <v>1.33</v>
+      </c>
+      <c r="S82">
+        <v>3.25</v>
+      </c>
+      <c r="T82">
+        <v>2.5</v>
+      </c>
+      <c r="U82">
+        <v>1.5</v>
+      </c>
+      <c r="V82">
+        <v>5</v>
+      </c>
+      <c r="W82">
+        <v>1.14</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+      <c r="AB82">
+        <v>1.75</v>
+      </c>
+      <c r="AC82">
+        <v>1.85</v>
+      </c>
+      <c r="AD82">
+        <v>0</v>
+      </c>
+      <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>1.8</v>
+      </c>
+      <c r="AG82">
+        <v>1.91</v>
+      </c>
+      <c r="AH82">
+        <v>0</v>
+      </c>
+      <c r="AI82">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="s">
+        <v>242</v>
+      </c>
+      <c r="AK82" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL82" s="3">
+        <v>45851.91666666666</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38">
+      <c r="A83" s="2">
+        <v>45851</v>
+      </c>
+      <c r="B83" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" t="s">
+        <v>80</v>
+      </c>
+      <c r="D83" t="s">
+        <v>86</v>
+      </c>
+      <c r="E83" t="s">
+        <v>163</v>
+      </c>
+      <c r="F83" t="s">
+        <v>240</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83" t="s">
+        <v>241</v>
+      </c>
+      <c r="L83">
         <v>1.95</v>
       </c>
-      <c r="M82">
+      <c r="M83">
         <v>4.2</v>
       </c>
-      <c r="N82">
+      <c r="N83">
         <v>2.75</v>
       </c>
-      <c r="O82">
+      <c r="O83">
         <v>1.62</v>
       </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
         <v>2.2</v>
       </c>
-      <c r="R82">
+      <c r="R83">
         <v>1.22</v>
       </c>
-      <c r="S82">
+      <c r="S83">
         <v>3.8</v>
       </c>
-      <c r="T82">
-        <v>2.02</v>
-      </c>
-      <c r="U82">
-        <v>1.73</v>
-      </c>
-      <c r="V82">
-        <v>4</v>
-      </c>
-      <c r="W82">
+      <c r="T83">
+        <v>2.01</v>
+      </c>
+      <c r="U83">
+        <v>1.72</v>
+      </c>
+      <c r="V83">
+        <v>3.8</v>
+      </c>
+      <c r="W83">
         <v>1.2</v>
       </c>
-      <c r="X82">
-        <v>0</v>
-      </c>
-      <c r="Y82">
-        <v>0</v>
-      </c>
-      <c r="Z82">
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
         <v>1.1</v>
       </c>
-      <c r="AA82">
-        <v>5.75</v>
-      </c>
-      <c r="AB82">
+      <c r="AA83">
+        <v>6</v>
+      </c>
+      <c r="AB83">
         <v>1.4</v>
       </c>
-      <c r="AC82">
+      <c r="AC83">
         <v>2.75</v>
       </c>
-      <c r="AD82">
-        <v>1.95</v>
-      </c>
-      <c r="AE82">
-        <v>1.75</v>
-      </c>
-      <c r="AF82">
+      <c r="AD83">
+        <v>1.93</v>
+      </c>
+      <c r="AE83">
+        <v>1.72</v>
+      </c>
+      <c r="AF83">
         <v>1.36</v>
       </c>
-      <c r="AG82">
-        <v>2.88</v>
-      </c>
-      <c r="AH82">
-        <v>2.97</v>
-      </c>
-      <c r="AI82">
+      <c r="AG83">
+        <v>2.79</v>
+      </c>
+      <c r="AH83">
+        <v>3.2</v>
+      </c>
+      <c r="AI83">
         <v>1.3</v>
       </c>
-      <c r="AJ82" t="s">
-        <v>240</v>
-      </c>
-      <c r="AK82" t="s">
-        <v>240</v>
-      </c>
-      <c r="AL82" s="3">
+      <c r="AJ83" t="s">
+        <v>242</v>
+      </c>
+      <c r="AK83" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL83" s="3">
         <v>45851.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -280,132 +280,132 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Sydney United</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
-    <t>Rockdale City Suns</t>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
   </si>
   <si>
     <t>Ansan Greeners</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
+    <t>Tallinna Kalev</t>
+  </si>
+  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
+    <t>GAIS</t>
   </si>
   <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>Bryne</t>
   </si>
   <si>
+    <t>Zhenys</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Zhenys</t>
-  </si>
-  <si>
     <t>Gnistan</t>
   </si>
   <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
     <t>AIK</t>
   </si>
   <si>
-    <t>Värnamo</t>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
   </si>
   <si>
     <t>Atlético Tucumán</t>
   </si>
   <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
     <t>Talleres Córdoba</t>
   </si>
   <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
+    <t>Häcken</t>
+  </si>
+  <si>
     <t>Santiago Morning</t>
   </si>
   <si>
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Häcken</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
@@ -421,69 +421,69 @@
     <t>Deportivo Maipú</t>
   </si>
   <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
+    <t>Philadelphia Union II</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Philadelphia Union II</t>
+    <t>Botafogo PB</t>
   </si>
   <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>Chapecoense</t>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>FC Cincinnati II</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
   </si>
   <si>
     <t>Caxias</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
-    <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>Orlando City II</t>
+  </si>
+  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
@@ -493,15 +493,15 @@
     <t>Fortaleza</t>
   </si>
   <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -511,132 +511,132 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Sydney Olympic</t>
+  </si>
+  <si>
+    <t>APIA Leichhardt Tigers</t>
+  </si>
+  <si>
+    <t>St George City FA</t>
+  </si>
+  <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>St George City FA</t>
-  </si>
-  <si>
-    <t>Sydney Olympic</t>
-  </si>
-  <si>
-    <t>APIA Leichhardt Tigers</t>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
   </si>
   <si>
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
     <t>Nanjing City</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
+    <t>Hammarby</t>
   </si>
   <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
     <t>Haka</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
     <t>Degerfors</t>
   </si>
   <si>
-    <t>Djurgården</t>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
   </si>
   <si>
     <t>San Martín San Juan</t>
   </si>
   <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
     <t>Copiapó</t>
   </si>
   <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
@@ -652,69 +652,69 @@
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
+    <t>New England II</t>
+  </si>
+  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Chattanooga FC</t>
+    <t>Londrina</t>
   </si>
   <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>Londrina</t>
-  </si>
-  <si>
     <t>Real Monarchs</t>
   </si>
   <si>
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Concepción</t>
   </si>
   <si>
-    <t>Remo</t>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
+    <t>Náutico</t>
   </si>
   <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
-    <t>Náutico</t>
-  </si>
-  <si>
     <t>Portland Timbers</t>
   </si>
   <si>
+    <t>Carolina Core</t>
+  </si>
+  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -724,13 +724,13 @@
     <t>Ceará</t>
   </si>
   <si>
+    <t>North Texas</t>
+  </si>
+  <si>
     <t>Sporting KC II</t>
   </si>
   <si>
     <t>Whitecaps II</t>
-  </si>
-  <si>
-    <t>North Texas</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1260,13 +1260,13 @@
         <v>241</v>
       </c>
       <c r="L2">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="M2">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.71</v>
@@ -1278,43 +1278,43 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S2">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
         <v>1.3</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z2">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AA2">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AC2">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AD2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -1323,13 +1323,13 @@
         <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH2">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>242</v>
@@ -1376,76 +1376,76 @@
         <v>241</v>
       </c>
       <c r="L3">
-        <v>1.82</v>
+        <v>5.38</v>
       </c>
       <c r="M3">
-        <v>3.6</v>
+        <v>4.72</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
         <v>1.5</v>
       </c>
-      <c r="V3">
-        <v>5.5</v>
-      </c>
-      <c r="W3">
-        <v>1.13</v>
-      </c>
-      <c r="X3">
-        <v>1.01</v>
-      </c>
-      <c r="Y3">
-        <v>13</v>
-      </c>
-      <c r="Z3">
-        <v>1.2</v>
-      </c>
-      <c r="AA3">
-        <v>4.2</v>
-      </c>
-      <c r="AB3">
-        <v>1.65</v>
-      </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AD3">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE3">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
         <v>242</v>
@@ -1492,76 +1492,76 @@
         <v>241</v>
       </c>
       <c r="L4">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="M4">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N4">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB4">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="AC4">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="s">
         <v>242</v>
@@ -1608,22 +1608,22 @@
         <v>241</v>
       </c>
       <c r="L5">
-        <v>5.75</v>
+        <v>2.65</v>
       </c>
       <c r="M5">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="N5">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AC5">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1724,76 +1724,76 @@
         <v>241</v>
       </c>
       <c r="L6">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="M6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N6">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="P6">
-        <v>20</v>
+        <v>16.75</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="U6">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
+        <v>5.5</v>
+      </c>
+      <c r="W6">
+        <v>1.12</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>11</v>
+      </c>
+      <c r="Z6">
+        <v>1.15</v>
+      </c>
+      <c r="AA6">
+        <v>4.25</v>
+      </c>
+      <c r="AB6">
+        <v>1.6</v>
+      </c>
+      <c r="AC6">
+        <v>2.25</v>
+      </c>
+      <c r="AD6">
+        <v>2.55</v>
+      </c>
+      <c r="AE6">
+        <v>1.44</v>
+      </c>
+      <c r="AF6">
+        <v>1.57</v>
+      </c>
+      <c r="AG6">
+        <v>2.3</v>
+      </c>
+      <c r="AH6">
         <v>4.33</v>
       </c>
-      <c r="W6">
+      <c r="AI6">
         <v>1.18</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>21</v>
-      </c>
-      <c r="Z6">
-        <v>1.1</v>
-      </c>
-      <c r="AA6">
-        <v>5.5</v>
-      </c>
-      <c r="AB6">
-        <v>1.42</v>
-      </c>
-      <c r="AC6">
-        <v>2.7</v>
-      </c>
-      <c r="AD6">
-        <v>2.06</v>
-      </c>
-      <c r="AE6">
-        <v>1.67</v>
-      </c>
-      <c r="AF6">
-        <v>1.36</v>
-      </c>
-      <c r="AG6">
-        <v>2.75</v>
-      </c>
-      <c r="AH6">
-        <v>3.5</v>
-      </c>
-      <c r="AI6">
-        <v>1.25</v>
       </c>
       <c r="AJ6" t="s">
         <v>242</v>
@@ -1840,22 +1840,22 @@
         <v>241</v>
       </c>
       <c r="L7">
-        <v>3.84</v>
+        <v>1.74</v>
       </c>
       <c r="M7">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="N7">
-        <v>1.8</v>
+        <v>4.63</v>
       </c>
       <c r="O7">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="P7">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q7">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="R7">
         <v>1.44</v>
@@ -1864,10 +1864,10 @@
         <v>2.63</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1879,37 +1879,37 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC7">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD7">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH7">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ7" t="s">
         <v>242</v>
@@ -1956,22 +1956,22 @@
         <v>241</v>
       </c>
       <c r="L8">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="M8">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="N8">
-        <v>4.63</v>
+        <v>3.09</v>
       </c>
       <c r="O8">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="P8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>1.44</v>
@@ -1980,10 +1980,10 @@
         <v>2.63</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1995,37 +1995,37 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Z8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AA8">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB8">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD8">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AE8">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG8">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH8">
-        <v>6.95</v>
+        <v>7.7</v>
       </c>
       <c r="AI8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ8" t="s">
         <v>242</v>
@@ -2072,22 +2072,22 @@
         <v>241</v>
       </c>
       <c r="L9">
-        <v>2.09</v>
+        <v>3.84</v>
       </c>
       <c r="M9">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N9">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2111,37 +2111,37 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AA9">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD9">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AE9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH9">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
         <v>242</v>
@@ -2206,58 +2206,58 @@
         <v>2.3</v>
       </c>
       <c r="R10">
+        <v>1.44</v>
+      </c>
+      <c r="S10">
+        <v>2.5</v>
+      </c>
+      <c r="T10">
+        <v>3.3</v>
+      </c>
+      <c r="U10">
+        <v>1.27</v>
+      </c>
+      <c r="V10">
+        <v>8.1</v>
+      </c>
+      <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>7.3</v>
+      </c>
+      <c r="Z10">
+        <v>1.4</v>
+      </c>
+      <c r="AA10">
+        <v>2.7</v>
+      </c>
+      <c r="AB10">
+        <v>2.25</v>
+      </c>
+      <c r="AC10">
         <v>1.5</v>
       </c>
-      <c r="S10">
-        <v>2.4</v>
-      </c>
-      <c r="T10">
-        <v>3.28</v>
-      </c>
-      <c r="U10">
-        <v>1.32</v>
-      </c>
-      <c r="V10">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W10">
-        <v>1.03</v>
-      </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>6.5</v>
-      </c>
-      <c r="Z10">
-        <v>1.46</v>
-      </c>
-      <c r="AA10">
-        <v>2.56</v>
-      </c>
-      <c r="AB10">
-        <v>2.32</v>
-      </c>
-      <c r="AC10">
-        <v>1.54</v>
-      </c>
       <c r="AD10">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG10">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AH10">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AI10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
         <v>242</v>
@@ -2304,13 +2304,13 @@
         <v>241</v>
       </c>
       <c r="L11">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="M11">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N11">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O11">
         <v>1.62</v>
@@ -2322,28 +2322,28 @@
         <v>2.75</v>
       </c>
       <c r="R11">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T11">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V11">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>1.27</v>
@@ -2352,28 +2352,28 @@
         <v>3.4</v>
       </c>
       <c r="AB11">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD11">
         <v>3</v>
       </c>
       <c r="AE11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AH11">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AI11">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="s">
         <v>242</v>
@@ -2393,7 +2393,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>86</v>
@@ -2420,76 +2420,76 @@
         <v>241</v>
       </c>
       <c r="L12">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="M12">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="N12">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
+        <v>2.13</v>
+      </c>
+      <c r="P12">
+        <v>19</v>
+      </c>
+      <c r="Q12">
+        <v>1.68</v>
+      </c>
+      <c r="R12">
+        <v>1.22</v>
+      </c>
+      <c r="S12">
+        <v>3.4</v>
+      </c>
+      <c r="T12">
+        <v>2.1</v>
+      </c>
+      <c r="U12">
+        <v>1.67</v>
+      </c>
+      <c r="V12">
+        <v>4.8</v>
+      </c>
+      <c r="W12">
+        <v>1.14</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>17</v>
+      </c>
+      <c r="Z12">
+        <v>1.14</v>
+      </c>
+      <c r="AA12">
+        <v>5</v>
+      </c>
+      <c r="AB12">
+        <v>1.5</v>
+      </c>
+      <c r="AC12">
+        <v>2.5</v>
+      </c>
+      <c r="AD12">
+        <v>2.1</v>
+      </c>
+      <c r="AE12">
+        <v>1.62</v>
+      </c>
+      <c r="AF12">
         <v>1.4</v>
       </c>
-      <c r="P12">
-        <v>10.75</v>
-      </c>
-      <c r="Q12">
-        <v>3.4</v>
-      </c>
-      <c r="R12">
-        <v>1.42</v>
-      </c>
-      <c r="S12">
-        <v>2.6</v>
-      </c>
-      <c r="T12">
-        <v>3</v>
-      </c>
-      <c r="U12">
-        <v>1.33</v>
-      </c>
-      <c r="V12">
-        <v>7.5</v>
-      </c>
-      <c r="W12">
-        <v>1.06</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>8</v>
-      </c>
-      <c r="Z12">
-        <v>1.36</v>
-      </c>
-      <c r="AA12">
-        <v>3.04</v>
-      </c>
-      <c r="AB12">
-        <v>2.11</v>
-      </c>
-      <c r="AC12">
-        <v>1.7</v>
-      </c>
-      <c r="AD12">
-        <v>2.95</v>
-      </c>
-      <c r="AE12">
-        <v>1.27</v>
-      </c>
-      <c r="AF12">
-        <v>2.1</v>
-      </c>
       <c r="AG12">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="AH12">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI12">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="s">
         <v>242</v>
@@ -2509,7 +2509,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>86</v>
@@ -2536,76 +2536,76 @@
         <v>241</v>
       </c>
       <c r="L13">
-        <v>3.01</v>
+        <v>1.57</v>
       </c>
       <c r="M13">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="N13">
-        <v>1.96</v>
+        <v>4.75</v>
       </c>
       <c r="O13">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="P13">
-        <v>19</v>
+        <v>10.75</v>
       </c>
       <c r="Q13">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="R13">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T13">
-        <v>2.15</v>
+        <v>3.08</v>
       </c>
       <c r="U13">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="V13">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="W13">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z13">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AB13">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="AD13">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AE13">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AH13">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AI13">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AJ13" t="s">
         <v>242</v>
@@ -2652,76 +2652,76 @@
         <v>241</v>
       </c>
       <c r="L14">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="M14">
+        <v>3.19</v>
+      </c>
+      <c r="N14">
+        <v>2.35</v>
+      </c>
+      <c r="O14">
+        <v>2.1</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>1.83</v>
+      </c>
+      <c r="R14">
+        <v>1.4</v>
+      </c>
+      <c r="S14">
+        <v>2.75</v>
+      </c>
+      <c r="T14">
+        <v>2.75</v>
+      </c>
+      <c r="U14">
+        <v>1.4</v>
+      </c>
+      <c r="V14">
+        <v>8</v>
+      </c>
+      <c r="W14">
+        <v>1.08</v>
+      </c>
+      <c r="X14">
+        <v>1.06</v>
+      </c>
+      <c r="Y14">
+        <v>9</v>
+      </c>
+      <c r="Z14">
+        <v>1.3</v>
+      </c>
+      <c r="AA14">
         <v>3.5</v>
       </c>
-      <c r="N14">
-        <v>3.77</v>
-      </c>
-      <c r="O14">
-        <v>1.44</v>
-      </c>
-      <c r="P14">
-        <v>11</v>
-      </c>
-      <c r="Q14">
-        <v>2.75</v>
-      </c>
-      <c r="R14">
-        <v>1.3</v>
-      </c>
-      <c r="S14">
-        <v>3.4</v>
-      </c>
-      <c r="T14">
-        <v>2.5</v>
-      </c>
-      <c r="U14">
-        <v>1.5</v>
-      </c>
-      <c r="V14">
-        <v>6</v>
-      </c>
-      <c r="W14">
-        <v>1.13</v>
-      </c>
-      <c r="X14">
-        <v>1.04</v>
-      </c>
-      <c r="Y14">
-        <v>11</v>
-      </c>
-      <c r="Z14">
-        <v>1.22</v>
-      </c>
-      <c r="AA14">
-        <v>4.2</v>
-      </c>
       <c r="AB14">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AC14">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AD14">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="AE14">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH14">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI14">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="s">
         <v>242</v>
@@ -2768,76 +2768,76 @@
         <v>241</v>
       </c>
       <c r="L15">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="M15">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N15">
-        <v>2.35</v>
+        <v>3.77</v>
       </c>
       <c r="O15">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="P15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R15">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z15">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA15">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB15">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AE15">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH15">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI15">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ15" t="s">
         <v>242</v>
@@ -3000,76 +3000,76 @@
         <v>241</v>
       </c>
       <c r="L17">
+        <v>1.77</v>
+      </c>
+      <c r="M17">
+        <v>3.2</v>
+      </c>
+      <c r="N17">
+        <v>4.4</v>
+      </c>
+      <c r="O17">
+        <v>1.64</v>
+      </c>
+      <c r="P17">
+        <v>8.1</v>
+      </c>
+      <c r="Q17">
+        <v>2.61</v>
+      </c>
+      <c r="R17">
         <v>1.47</v>
       </c>
-      <c r="M17">
-        <v>4</v>
-      </c>
-      <c r="N17">
-        <v>5.5</v>
-      </c>
-      <c r="O17">
-        <v>1.41</v>
-      </c>
-      <c r="P17">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q17">
-        <v>3.28</v>
-      </c>
-      <c r="R17">
-        <v>1.35</v>
-      </c>
       <c r="S17">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
+        <v>1.32</v>
+      </c>
+      <c r="V17">
+        <v>8.5</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1.08</v>
+      </c>
+      <c r="Y17">
+        <v>7.5</v>
+      </c>
+      <c r="Z17">
         <v>1.4</v>
       </c>
-      <c r="V17">
-        <v>6.5</v>
-      </c>
-      <c r="W17">
-        <v>1.08</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Z17">
-        <v>1.29</v>
-      </c>
       <c r="AA17">
-        <v>3.22</v>
+        <v>2.75</v>
       </c>
       <c r="AB17">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AD17">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AE17">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
         <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH17">
-        <v>5.75</v>
+        <v>9.5</v>
       </c>
       <c r="AI17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ17" t="s">
         <v>242</v>
@@ -3116,76 +3116,76 @@
         <v>241</v>
       </c>
       <c r="L18">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="M18">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N18">
-        <v>5.4</v>
+        <v>6.91</v>
       </c>
       <c r="O18">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="P18">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q18">
-        <v>2.61</v>
+        <v>3.28</v>
       </c>
       <c r="R18">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S18">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="T18">
+        <v>2.63</v>
+      </c>
+      <c r="U18">
+        <v>1.44</v>
+      </c>
+      <c r="V18">
+        <v>6.5</v>
+      </c>
+      <c r="W18">
+        <v>1.1</v>
+      </c>
+      <c r="X18">
+        <v>1.05</v>
+      </c>
+      <c r="Y18">
+        <v>10</v>
+      </c>
+      <c r="Z18">
+        <v>1.25</v>
+      </c>
+      <c r="AA18">
+        <v>3.4</v>
+      </c>
+      <c r="AB18">
+        <v>1.85</v>
+      </c>
+      <c r="AC18">
+        <v>1.83</v>
+      </c>
+      <c r="AD18">
         <v>3.2</v>
       </c>
-      <c r="U18">
-        <v>1.27</v>
-      </c>
-      <c r="V18">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W18">
-        <v>1</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>7</v>
-      </c>
-      <c r="Z18">
-        <v>1.37</v>
-      </c>
-      <c r="AA18">
-        <v>2.66</v>
-      </c>
-      <c r="AB18">
-        <v>2.25</v>
-      </c>
-      <c r="AC18">
-        <v>1.53</v>
-      </c>
-      <c r="AD18">
-        <v>4.4</v>
-      </c>
       <c r="AE18">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AF18">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH18">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="AI18">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ18" t="s">
         <v>242</v>
@@ -3232,13 +3232,13 @@
         <v>241</v>
       </c>
       <c r="L19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M19">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N19">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
         <v>1.67</v>
@@ -3250,19 +3250,19 @@
         <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="T19">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U19">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="W19">
         <v>1.15</v>
@@ -3274,31 +3274,31 @@
         <v>12</v>
       </c>
       <c r="Z19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AA19">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="AB19">
         <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AD19">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AE19">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF19">
         <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH19">
-        <v>4.47</v>
+        <v>4.35</v>
       </c>
       <c r="AI19">
         <v>1.18</v>
@@ -3348,22 +3348,22 @@
         <v>241</v>
       </c>
       <c r="L20">
-        <v>1.51</v>
+        <v>3.82</v>
       </c>
       <c r="M20">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="N20">
-        <v>5.3</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
         <v>1.36</v>
@@ -3378,46 +3378,46 @@
         <v>1.4</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>1.3</v>
       </c>
       <c r="AA20">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC20">
+        <v>1.79</v>
+      </c>
+      <c r="AD20">
+        <v>3.45</v>
+      </c>
+      <c r="AE20">
+        <v>1.3</v>
+      </c>
+      <c r="AF20">
         <v>1.8</v>
       </c>
-      <c r="AD20">
-        <v>3.25</v>
-      </c>
-      <c r="AE20">
-        <v>1.35</v>
-      </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>1.95</v>
       </c>
-      <c r="AG20">
-        <v>1.8</v>
-      </c>
       <c r="AH20">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI20">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
         <v>242</v>
@@ -3464,22 +3464,22 @@
         <v>241</v>
       </c>
       <c r="L21">
-        <v>3.82</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
-        <v>3.37</v>
+        <v>3.76</v>
       </c>
       <c r="N21">
-        <v>1.78</v>
+        <v>5.3</v>
       </c>
       <c r="O21">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="P21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="R21">
         <v>1.36</v>
@@ -3494,46 +3494,46 @@
         <v>1.4</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>1.3</v>
       </c>
       <c r="AA21">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AB21">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD21">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AE21">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF21">
+        <v>1.95</v>
+      </c>
+      <c r="AG21">
         <v>1.8</v>
       </c>
-      <c r="AG21">
-        <v>1.95</v>
-      </c>
       <c r="AH21">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ21" t="s">
         <v>242</v>
@@ -4597,7 +4597,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
         <v>86</v>
@@ -4624,76 +4624,76 @@
         <v>241</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ31" t="s">
         <v>242</v>
@@ -4713,7 +4713,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>86</v>
@@ -4740,76 +4740,76 @@
         <v>241</v>
       </c>
       <c r="L32">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="s">
         <v>242</v>
@@ -4856,76 +4856,76 @@
         <v>241</v>
       </c>
       <c r="L33">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="M33">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="N33">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="O33">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="P33">
-        <v>9.25</v>
+        <v>12.5</v>
       </c>
       <c r="Q33">
+        <v>1.73</v>
+      </c>
+      <c r="R33">
+        <v>1.25</v>
+      </c>
+      <c r="S33">
+        <v>3.75</v>
+      </c>
+      <c r="T33">
+        <v>2.25</v>
+      </c>
+      <c r="U33">
         <v>1.57</v>
       </c>
-      <c r="R33">
-        <v>1.36</v>
-      </c>
-      <c r="S33">
-        <v>3</v>
-      </c>
-      <c r="T33">
-        <v>2.75</v>
-      </c>
-      <c r="U33">
-        <v>1.4</v>
-      </c>
       <c r="V33">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AA33">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="AB33">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AC33">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AD33">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE33">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AH33">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="AI33">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AJ33" t="s">
         <v>242</v>
@@ -4972,76 +4972,76 @@
         <v>241</v>
       </c>
       <c r="L34">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="M34">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="N34">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O34">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="P34">
-        <v>10.5</v>
+        <v>9.25</v>
       </c>
       <c r="Q34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S34">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T34">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V34">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA34">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AB34">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AD34">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="AE34">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH34">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI34">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ34" t="s">
         <v>242</v>
@@ -5061,7 +5061,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
         <v>86</v>
@@ -5088,76 +5088,76 @@
         <v>241</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ35" t="s">
         <v>242</v>
@@ -5293,7 +5293,7 @@
         <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
         <v>86</v>
@@ -5320,76 +5320,76 @@
         <v>241</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ37" t="s">
         <v>242</v>
@@ -5409,7 +5409,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
         <v>86</v>
@@ -5436,76 +5436,76 @@
         <v>241</v>
       </c>
       <c r="L38">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="s">
         <v>242</v>
@@ -5641,7 +5641,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
         <v>86</v>
@@ -5668,76 +5668,76 @@
         <v>241</v>
       </c>
       <c r="L40">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="s">
         <v>242</v>
@@ -5784,13 +5784,13 @@
         <v>241</v>
       </c>
       <c r="L41">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="M41">
-        <v>3.57</v>
+        <v>3.9</v>
       </c>
       <c r="N41">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="O41">
         <v>1.5</v>
@@ -5802,46 +5802,46 @@
         <v>2.63</v>
       </c>
       <c r="R41">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S41">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T41">
         <v>2.38</v>
       </c>
       <c r="U41">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V41">
         <v>5.5</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z41">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AA41">
         <v>4.4</v>
       </c>
       <c r="AB41">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC41">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AD41">
         <v>2.5</v>
       </c>
       <c r="AE41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
@@ -5850,7 +5850,7 @@
         <v>2.2</v>
       </c>
       <c r="AH41">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AI41">
         <v>1.14</v>
@@ -5873,7 +5873,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
         <v>86</v>
@@ -5900,76 +5900,76 @@
         <v>241</v>
       </c>
       <c r="L42">
-        <v>3.03</v>
+        <v>1.56</v>
       </c>
       <c r="M42">
-        <v>3.17</v>
+        <v>4.1</v>
       </c>
       <c r="N42">
-        <v>2.11</v>
+        <v>4.3</v>
       </c>
       <c r="O42">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="P42">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="Q42">
-        <v>1.81</v>
+        <v>2.88</v>
       </c>
       <c r="R42">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S42">
+        <v>3.4</v>
+      </c>
+      <c r="T42">
         <v>2.5</v>
       </c>
-      <c r="T42">
-        <v>2.9</v>
-      </c>
       <c r="U42">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V42">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z42">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AA42">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AC42">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="AD42">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AH42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AI42">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AJ42" t="s">
         <v>242</v>
@@ -6016,76 +6016,76 @@
         <v>241</v>
       </c>
       <c r="L43">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="M43">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="N43">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="P43">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q43">
-        <v>2.61</v>
+        <v>1.81</v>
       </c>
       <c r="R43">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S43">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="T43">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V43">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z43">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA43">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="AB43">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC43">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AD43">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AE43">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH43">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI43">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ43" t="s">
         <v>242</v>
@@ -6105,7 +6105,7 @@
         <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
         <v>86</v>
@@ -6132,76 +6132,76 @@
         <v>241</v>
       </c>
       <c r="L44">
-        <v>1.56</v>
+        <v>2.32</v>
       </c>
       <c r="M44">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="N44">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O44">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="P44">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="Q44">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="R44">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S44">
+        <v>2.89</v>
+      </c>
+      <c r="T44">
+        <v>2.71</v>
+      </c>
+      <c r="U44">
+        <v>1.41</v>
+      </c>
+      <c r="V44">
+        <v>7</v>
+      </c>
+      <c r="W44">
+        <v>1.1</v>
+      </c>
+      <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z44">
+        <v>1.29</v>
+      </c>
+      <c r="AA44">
         <v>3.4</v>
       </c>
-      <c r="T44">
-        <v>2.5</v>
-      </c>
-      <c r="U44">
-        <v>1.5</v>
-      </c>
-      <c r="V44">
-        <v>6</v>
-      </c>
-      <c r="W44">
-        <v>1.13</v>
-      </c>
-      <c r="X44">
-        <v>1.04</v>
-      </c>
-      <c r="Y44">
-        <v>11</v>
-      </c>
-      <c r="Z44">
-        <v>1.22</v>
-      </c>
-      <c r="AA44">
-        <v>4.33</v>
-      </c>
       <c r="AB44">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC44">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AD44">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AE44">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF44">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG44">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH44">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AI44">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ44" t="s">
         <v>242</v>
@@ -6266,7 +6266,7 @@
         <v>3.6</v>
       </c>
       <c r="R45">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S45">
         <v>2.38</v>
@@ -6293,13 +6293,13 @@
         <v>1.53</v>
       </c>
       <c r="AA45">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB45">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AC45">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD45">
         <v>5</v>
@@ -6308,10 +6308,10 @@
         <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG45">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AH45">
         <v>9.800000000000001</v>
@@ -6364,13 +6364,13 @@
         <v>241</v>
       </c>
       <c r="L46">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="M46">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="O46">
         <v>1.36</v>
@@ -6388,52 +6388,52 @@
         <v>2.5</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U46">
         <v>1.3</v>
       </c>
       <c r="V46">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
         <v>1.1</v>
       </c>
       <c r="Y46">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="Z46">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AA46">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AB46">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AC46">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD46">
         <v>4.7</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AG46">
         <v>1.5</v>
       </c>
       <c r="AH46">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AI46">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ46" t="s">
         <v>242</v>
@@ -6453,16 +6453,16 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D47" t="s">
         <v>86</v>
       </c>
       <c r="E47" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="F47" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6480,76 +6480,76 @@
         <v>241</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M47">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N47">
+        <v>2.46</v>
+      </c>
+      <c r="O47">
+        <v>1.73</v>
+      </c>
+      <c r="P47">
+        <v>14.5</v>
+      </c>
+      <c r="Q47">
+        <v>2.05</v>
+      </c>
+      <c r="R47">
+        <v>1.25</v>
+      </c>
+      <c r="S47">
+        <v>3.75</v>
+      </c>
+      <c r="T47">
         <v>2.1</v>
       </c>
-      <c r="O47">
-        <v>2.88</v>
-      </c>
-      <c r="P47">
-        <v>5.75</v>
-      </c>
-      <c r="Q47">
+      <c r="U47">
         <v>1.67</v>
       </c>
-      <c r="R47">
+      <c r="V47">
+        <v>4.5</v>
+      </c>
+      <c r="W47">
+        <v>1.18</v>
+      </c>
+      <c r="X47">
+        <v>1.04</v>
+      </c>
+      <c r="Y47">
+        <v>10</v>
+      </c>
+      <c r="Z47">
+        <v>1.17</v>
+      </c>
+      <c r="AA47">
+        <v>5</v>
+      </c>
+      <c r="AB47">
         <v>1.57</v>
       </c>
-      <c r="S47">
-        <v>2.25</v>
-      </c>
-      <c r="T47">
-        <v>3.75</v>
-      </c>
-      <c r="U47">
+      <c r="AC47">
+        <v>2.15</v>
+      </c>
+      <c r="AD47">
+        <v>2.27</v>
+      </c>
+      <c r="AE47">
+        <v>1.56</v>
+      </c>
+      <c r="AF47">
+        <v>1.4</v>
+      </c>
+      <c r="AG47">
+        <v>2.75</v>
+      </c>
+      <c r="AH47">
+        <v>3.7</v>
+      </c>
+      <c r="AI47">
         <v>1.25</v>
-      </c>
-      <c r="V47">
-        <v>13</v>
-      </c>
-      <c r="W47">
-        <v>1.04</v>
-      </c>
-      <c r="X47">
-        <v>1.11</v>
-      </c>
-      <c r="Y47">
-        <v>6.25</v>
-      </c>
-      <c r="Z47">
-        <v>1.53</v>
-      </c>
-      <c r="AA47">
-        <v>2.3</v>
-      </c>
-      <c r="AB47">
-        <v>2.7</v>
-      </c>
-      <c r="AC47">
-        <v>1.44</v>
-      </c>
-      <c r="AD47">
-        <v>5.25</v>
-      </c>
-      <c r="AE47">
-        <v>1.15</v>
-      </c>
-      <c r="AF47">
-        <v>2.25</v>
-      </c>
-      <c r="AG47">
-        <v>1.57</v>
-      </c>
-      <c r="AH47">
-        <v>10</v>
-      </c>
-      <c r="AI47">
-        <v>1.04</v>
       </c>
       <c r="AJ47" t="s">
         <v>242</v>
@@ -6569,16 +6569,16 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D48" t="s">
         <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="F48" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6596,76 +6596,76 @@
         <v>241</v>
       </c>
       <c r="L48">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M48">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N48">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="P48">
-        <v>14.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="R48">
+        <v>1.57</v>
+      </c>
+      <c r="S48">
+        <v>2.25</v>
+      </c>
+      <c r="T48">
+        <v>3.75</v>
+      </c>
+      <c r="U48">
         <v>1.25</v>
       </c>
-      <c r="S48">
-        <v>3.75</v>
-      </c>
-      <c r="T48">
-        <v>2.1</v>
-      </c>
-      <c r="U48">
-        <v>1.67</v>
-      </c>
       <c r="V48">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="W48">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
+        <v>1.11</v>
+      </c>
+      <c r="Y48">
+        <v>6.25</v>
+      </c>
+      <c r="Z48">
+        <v>1.53</v>
+      </c>
+      <c r="AA48">
+        <v>2.3</v>
+      </c>
+      <c r="AB48">
+        <v>2.7</v>
+      </c>
+      <c r="AC48">
+        <v>1.44</v>
+      </c>
+      <c r="AD48">
+        <v>5.25</v>
+      </c>
+      <c r="AE48">
+        <v>1.15</v>
+      </c>
+      <c r="AF48">
+        <v>2.25</v>
+      </c>
+      <c r="AG48">
+        <v>1.57</v>
+      </c>
+      <c r="AH48">
+        <v>10</v>
+      </c>
+      <c r="AI48">
         <v>1.04</v>
-      </c>
-      <c r="Y48">
-        <v>10</v>
-      </c>
-      <c r="Z48">
-        <v>1.17</v>
-      </c>
-      <c r="AA48">
-        <v>5</v>
-      </c>
-      <c r="AB48">
-        <v>1.57</v>
-      </c>
-      <c r="AC48">
-        <v>2.15</v>
-      </c>
-      <c r="AD48">
-        <v>2.27</v>
-      </c>
-      <c r="AE48">
-        <v>1.56</v>
-      </c>
-      <c r="AF48">
-        <v>1.4</v>
-      </c>
-      <c r="AG48">
-        <v>2.75</v>
-      </c>
-      <c r="AH48">
-        <v>3.7</v>
-      </c>
-      <c r="AI48">
-        <v>1.25</v>
       </c>
       <c r="AJ48" t="s">
         <v>242</v>
@@ -6712,13 +6712,13 @@
         <v>241</v>
       </c>
       <c r="L49">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="M49">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="N49">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="O49">
         <v>2.6</v>
@@ -6730,58 +6730,58 @@
         <v>1.83</v>
       </c>
       <c r="R49">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S49">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U49">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V49">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Y49">
-        <v>4.6</v>
+        <v>5.55</v>
       </c>
       <c r="Z49">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AA49">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB49">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="AC49">
         <v>1.34</v>
       </c>
       <c r="AD49">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AG49">
         <v>1.53</v>
       </c>
       <c r="AH49">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI49">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ49" t="s">
         <v>242</v>
@@ -6828,13 +6828,13 @@
         <v>241</v>
       </c>
       <c r="L50">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="M50">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="N50">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="O50">
         <v>1.67</v>
@@ -6846,22 +6846,22 @@
         <v>2.88</v>
       </c>
       <c r="R50">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S50">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T50">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W50">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.14</v>
@@ -6870,34 +6870,34 @@
         <v>5.5</v>
       </c>
       <c r="Z50">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA50">
+        <v>2.2</v>
+      </c>
+      <c r="AB50">
+        <v>2.83</v>
+      </c>
+      <c r="AC50">
+        <v>1.33</v>
+      </c>
+      <c r="AD50">
+        <v>5.75</v>
+      </c>
+      <c r="AE50">
+        <v>1.11</v>
+      </c>
+      <c r="AF50">
         <v>2.25</v>
       </c>
-      <c r="AB50">
-        <v>2.89</v>
-      </c>
-      <c r="AC50">
-        <v>1.36</v>
-      </c>
-      <c r="AD50">
-        <v>5.5</v>
-      </c>
-      <c r="AE50">
-        <v>1.06</v>
-      </c>
-      <c r="AF50">
-        <v>2.45</v>
-      </c>
       <c r="AG50">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH50">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AI50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ50" t="s">
         <v>242</v>
@@ -6917,7 +6917,7 @@
         <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
         <v>86</v>
@@ -6944,76 +6944,76 @@
         <v>241</v>
       </c>
       <c r="L51">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="M51">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="N51">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="O51">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="P51">
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="AC51">
-        <v>1.48</v>
+        <v>2.38</v>
       </c>
       <c r="AD51">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH51">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AI51">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="s">
         <v>242</v>
@@ -7033,7 +7033,7 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
         <v>86</v>
@@ -7060,76 +7060,76 @@
         <v>241</v>
       </c>
       <c r="L52">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="M52">
-        <v>3.75</v>
+        <v>2.61</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="O52">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="AC52">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AI52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ52" t="s">
         <v>242</v>
@@ -7176,13 +7176,13 @@
         <v>241</v>
       </c>
       <c r="L53">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="M53">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="N53">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="O53">
         <v>2</v>
@@ -7194,10 +7194,10 @@
         <v>2.5</v>
       </c>
       <c r="R53">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S53">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T53">
         <v>4.33</v>
@@ -7206,43 +7206,43 @@
         <v>1.18</v>
       </c>
       <c r="V53">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W53">
         <v>1.02</v>
       </c>
       <c r="X53">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y53">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Z53">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AA53">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB53">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="AC53">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD53">
-        <v>7.2</v>
+        <v>5.75</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AG53">
         <v>1.53</v>
       </c>
       <c r="AH53">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AI53">
         <v>1.02</v>
@@ -7295,10 +7295,10 @@
         <v>2.14</v>
       </c>
       <c r="M54">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="N54">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="O54">
         <v>1.8</v>
@@ -7310,49 +7310,49 @@
         <v>2.75</v>
       </c>
       <c r="R54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S54">
         <v>2.2</v>
       </c>
       <c r="T54">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U54">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V54">
         <v>10</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y54">
         <v>5.5</v>
       </c>
       <c r="Z54">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AA54">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB54">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AC54">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AD54">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AE54">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AG54">
         <v>1.62</v>
@@ -7381,7 +7381,7 @@
         <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D55" t="s">
         <v>86</v>
@@ -7408,76 +7408,76 @@
         <v>241</v>
       </c>
       <c r="L55">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N55">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="O55">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="P55">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q55">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R55">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U55">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V55">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z55">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AA55">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB55">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC55">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AD55">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AE55">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AG55">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AH55">
-        <v>11.5</v>
+        <v>6.75</v>
       </c>
       <c r="AI55">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ55" t="s">
         <v>242</v>
@@ -7497,7 +7497,7 @@
         <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D56" t="s">
         <v>86</v>
@@ -7524,76 +7524,76 @@
         <v>241</v>
       </c>
       <c r="L56">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="M56">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="N56">
-        <v>3.37</v>
+        <v>4.75</v>
       </c>
       <c r="O56">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="P56">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R56">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S56">
+        <v>3.6</v>
+      </c>
+      <c r="T56">
+        <v>2.1</v>
+      </c>
+      <c r="U56">
+        <v>1.65</v>
+      </c>
+      <c r="V56">
+        <v>4.5</v>
+      </c>
+      <c r="W56">
+        <v>1.17</v>
+      </c>
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="Y56">
+        <v>12</v>
+      </c>
+      <c r="Z56">
+        <v>1.15</v>
+      </c>
+      <c r="AA56">
+        <v>5</v>
+      </c>
+      <c r="AB56">
+        <v>1.48</v>
+      </c>
+      <c r="AC56">
         <v>2.5</v>
       </c>
-      <c r="T56">
-        <v>2.9</v>
-      </c>
-      <c r="U56">
-        <v>1.36</v>
-      </c>
-      <c r="V56">
-        <v>8.5</v>
-      </c>
-      <c r="W56">
-        <v>1.07</v>
-      </c>
-      <c r="X56">
-        <v>1.05</v>
-      </c>
-      <c r="Y56">
-        <v>8</v>
-      </c>
-      <c r="Z56">
-        <v>1.33</v>
-      </c>
-      <c r="AA56">
-        <v>3</v>
-      </c>
-      <c r="AB56">
-        <v>2</v>
-      </c>
-      <c r="AC56">
-        <v>1.67</v>
-      </c>
       <c r="AD56">
+        <v>2.2</v>
+      </c>
+      <c r="AE56">
+        <v>1.62</v>
+      </c>
+      <c r="AF56">
+        <v>1.65</v>
+      </c>
+      <c r="AG56">
+        <v>2.1</v>
+      </c>
+      <c r="AH56">
         <v>3.6</v>
       </c>
-      <c r="AE56">
+      <c r="AI56">
         <v>1.25</v>
-      </c>
-      <c r="AF56">
-        <v>1.75</v>
-      </c>
-      <c r="AG56">
-        <v>1.95</v>
-      </c>
-      <c r="AH56">
-        <v>6.2</v>
-      </c>
-      <c r="AI56">
-        <v>1.08</v>
       </c>
       <c r="AJ56" t="s">
         <v>242</v>
@@ -7613,7 +7613,7 @@
         <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
         <v>86</v>
@@ -7640,76 +7640,76 @@
         <v>241</v>
       </c>
       <c r="L57">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="M57">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="N57">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="O57">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q57">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R57">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="S57">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="T57">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="U57">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="V57">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W57">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y57">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Z57">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="AA57">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB57">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC57">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD57">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="AE57">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AF57">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AG57">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AH57">
-        <v>3.04</v>
+        <v>11</v>
       </c>
       <c r="AI57">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AJ57" t="s">
         <v>242</v>
@@ -7729,16 +7729,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="F58" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7756,76 +7756,76 @@
         <v>241</v>
       </c>
       <c r="L58">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M58">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="N58">
-        <v>4.75</v>
+        <v>3.29</v>
       </c>
       <c r="O58">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="P58">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q58">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="R58">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S58">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T58">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V58">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y58">
         <v>7</v>
       </c>
       <c r="Z58">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AA58">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB58">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AC58">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD58">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AE58">
         <v>1.18</v>
       </c>
       <c r="AF58">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG58">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH58">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI58">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ58" t="s">
         <v>242</v>
@@ -7851,10 +7851,10 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="F59" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7872,34 +7872,34 @@
         <v>241</v>
       </c>
       <c r="L59">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N59">
+        <v>4.75</v>
+      </c>
+      <c r="O59">
+        <v>1.5</v>
+      </c>
+      <c r="P59">
+        <v>6.5</v>
+      </c>
+      <c r="Q59">
         <v>3.25</v>
       </c>
-      <c r="O59">
-        <v>1.83</v>
-      </c>
-      <c r="P59">
-        <v>6</v>
-      </c>
-      <c r="Q59">
-        <v>2.4</v>
-      </c>
       <c r="R59">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S59">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T59">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U59">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V59">
         <v>11</v>
@@ -7908,34 +7908,34 @@
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y59">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Z59">
+        <v>1.48</v>
+      </c>
+      <c r="AA59">
+        <v>2.6</v>
+      </c>
+      <c r="AB59">
+        <v>2.5</v>
+      </c>
+      <c r="AC59">
         <v>1.5</v>
       </c>
-      <c r="AA59">
-        <v>2.38</v>
-      </c>
-      <c r="AB59">
-        <v>2.6</v>
-      </c>
-      <c r="AC59">
-        <v>1.48</v>
-      </c>
       <c r="AD59">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE59">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF59">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG59">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH59">
         <v>9.5</v>
@@ -7967,10 +7967,10 @@
         <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F60" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7988,13 +7988,13 @@
         <v>241</v>
       </c>
       <c r="L60">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="M60">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="N60">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="O60">
         <v>1.62</v>
@@ -8006,13 +8006,13 @@
         <v>3</v>
       </c>
       <c r="R60">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S60">
         <v>2.45</v>
       </c>
       <c r="T60">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="U60">
         <v>1.29</v>
@@ -8024,10 +8024,10 @@
         <v>1.05</v>
       </c>
       <c r="X60">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Z60">
         <v>1.44</v>
@@ -8036,13 +8036,13 @@
         <v>2.45</v>
       </c>
       <c r="AB60">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC60">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD60">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AE60">
         <v>1.15</v>
@@ -8077,16 +8077,16 @@
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D61" t="s">
         <v>86</v>
       </c>
       <c r="E61" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F61" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8104,73 +8104,73 @@
         <v>241</v>
       </c>
       <c r="L61">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="M61">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="N61">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="O61">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P61">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="Q61">
+        <v>2.4</v>
+      </c>
+      <c r="R61">
+        <v>1.57</v>
+      </c>
+      <c r="S61">
         <v>2.25</v>
       </c>
-      <c r="R61">
-        <v>1.49</v>
-      </c>
-      <c r="S61">
-        <v>2.4</v>
-      </c>
       <c r="T61">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U61">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V61">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="W61">
         <v>1.05</v>
       </c>
       <c r="X61">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y61">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Z61">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AA61">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AB61">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AC61">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AD61">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG61">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH61">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="AI61">
         <v>1.05</v>
@@ -8220,13 +8220,13 @@
         <v>241</v>
       </c>
       <c r="L62">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="M62">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N62">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O62">
         <v>2</v>
@@ -8244,10 +8244,10 @@
         <v>3.8</v>
       </c>
       <c r="T62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U62">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V62">
         <v>4.33</v>
@@ -8268,16 +8268,16 @@
         <v>5.5</v>
       </c>
       <c r="AB62">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AC62">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AD62">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE62">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF62">
         <v>1.38</v>
@@ -8286,7 +8286,7 @@
         <v>2.8</v>
       </c>
       <c r="AH62">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AI62">
         <v>1.25</v>
@@ -8336,13 +8336,13 @@
         <v>241</v>
       </c>
       <c r="L63">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="M63">
+        <v>3</v>
+      </c>
+      <c r="N63">
         <v>3.25</v>
-      </c>
-      <c r="N63">
-        <v>2.75</v>
       </c>
       <c r="O63">
         <v>1.67</v>
@@ -8354,58 +8354,58 @@
         <v>2.6</v>
       </c>
       <c r="R63">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S63">
         <v>2.5</v>
       </c>
       <c r="T63">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V63">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="W63">
         <v>1.05</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y63">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Z63">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AA63">
         <v>2.8</v>
       </c>
       <c r="AB63">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC63">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AD63">
         <v>4.2</v>
       </c>
       <c r="AE63">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF63">
         <v>1.95</v>
       </c>
       <c r="AG63">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH63">
         <v>9</v>
       </c>
       <c r="AI63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ63" t="s">
         <v>242</v>
@@ -8425,7 +8425,7 @@
         <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D64" t="s">
         <v>86</v>
@@ -8452,76 +8452,76 @@
         <v>241</v>
       </c>
       <c r="L64">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="M64">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="N64">
-        <v>2.8</v>
+        <v>4.02</v>
       </c>
       <c r="O64">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="P64">
-        <v>8.9</v>
+        <v>6.75</v>
       </c>
       <c r="Q64">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S64">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="T64">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U64">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V64">
+        <v>9.5</v>
+      </c>
+      <c r="W64">
+        <v>1.06</v>
+      </c>
+      <c r="X64">
+        <v>1.07</v>
+      </c>
+      <c r="Y64">
         <v>7</v>
       </c>
-      <c r="W64">
-        <v>1.08</v>
-      </c>
-      <c r="X64">
-        <v>1.06</v>
-      </c>
-      <c r="Y64">
-        <v>9</v>
-      </c>
       <c r="Z64">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA64">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB64">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AC64">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AD64">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE64">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG64">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH64">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AI64">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AJ64" t="s">
         <v>242</v>
@@ -8541,7 +8541,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D65" t="s">
         <v>86</v>
@@ -8568,76 +8568,76 @@
         <v>241</v>
       </c>
       <c r="L65">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="M65">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N65">
-        <v>3.23</v>
+        <v>2.7</v>
       </c>
       <c r="O65">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="P65">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="Q65">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="R65">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S65">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="T65">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U65">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V65">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="W65">
+        <v>1.08</v>
+      </c>
+      <c r="X65">
         <v>1.06</v>
       </c>
-      <c r="X65">
-        <v>1.1</v>
-      </c>
       <c r="Y65">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z65">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AA65">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AB65">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AC65">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AD65">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE65">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG65">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AH65">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AI65">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ65" t="s">
         <v>242</v>
@@ -8663,10 +8663,10 @@
         <v>86</v>
       </c>
       <c r="E66" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F66" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
         <v>86</v>
@@ -8800,28 +8800,28 @@
         <v>241</v>
       </c>
       <c r="L67">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="M67">
-        <v>3.56</v>
+        <v>3.12</v>
       </c>
       <c r="N67">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="O67">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="P67">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q67">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S67">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="T67">
         <v>3.3</v>
@@ -8830,46 +8830,46 @@
         <v>1.3</v>
       </c>
       <c r="V67">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y67">
         <v>6.5</v>
       </c>
       <c r="Z67">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AA67">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB67">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AC67">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AD67">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE67">
         <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AG67">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH67">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="AI67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ67" t="s">
         <v>242</v>
@@ -8889,7 +8889,7 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
         <v>86</v>
@@ -8916,76 +8916,76 @@
         <v>241</v>
       </c>
       <c r="L68">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="M68">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N68">
         <v>3.6</v>
       </c>
       <c r="O68">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P68">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R68">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S68">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="T68">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="U68">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V68">
-        <v>8.9</v>
+        <v>4.5</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="Z68">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AA68">
-        <v>2.62</v>
+        <v>4.75</v>
       </c>
       <c r="AB68">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC68">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AD68">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="AE68">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="AF68">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AG68">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH68">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI68">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ68" t="s">
         <v>242</v>
@@ -9005,7 +9005,7 @@
         <v>62</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D69" t="s">
         <v>86</v>
@@ -9032,76 +9032,76 @@
         <v>241</v>
       </c>
       <c r="L69">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="M69">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="N69">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O69">
+        <v>1.67</v>
+      </c>
+      <c r="P69">
+        <v>6.5</v>
+      </c>
+      <c r="Q69">
+        <v>2.75</v>
+      </c>
+      <c r="R69">
+        <v>1.51</v>
+      </c>
+      <c r="S69">
+        <v>2.5</v>
+      </c>
+      <c r="T69">
+        <v>3.3</v>
+      </c>
+      <c r="U69">
+        <v>1.3</v>
+      </c>
+      <c r="V69">
+        <v>9.25</v>
+      </c>
+      <c r="W69">
+        <v>1.05</v>
+      </c>
+      <c r="X69">
+        <v>1.1</v>
+      </c>
+      <c r="Y69">
+        <v>6</v>
+      </c>
+      <c r="Z69">
         <v>1.44</v>
       </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>2.88</v>
-      </c>
-      <c r="R69">
-        <v>1.3</v>
-      </c>
-      <c r="S69">
-        <v>3.4</v>
-      </c>
-      <c r="T69">
-        <v>2.38</v>
-      </c>
-      <c r="U69">
-        <v>1.53</v>
-      </c>
-      <c r="V69">
-        <v>5</v>
-      </c>
-      <c r="W69">
-        <v>1.14</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB69">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC69">
+        <v>1.5</v>
+      </c>
+      <c r="AD69">
+        <v>4.5</v>
+      </c>
+      <c r="AE69">
+        <v>1.13</v>
+      </c>
+      <c r="AF69">
         <v>2.1</v>
       </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>1.73</v>
-      </c>
       <c r="AG69">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ69" t="s">
         <v>242</v>
@@ -9121,7 +9121,7 @@
         <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D70" t="s">
         <v>86</v>
@@ -9148,76 +9148,76 @@
         <v>241</v>
       </c>
       <c r="L70">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="M70">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N70">
-        <v>3.6</v>
+        <v>6.17</v>
       </c>
       <c r="O70">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q70">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="R70">
+        <v>1.48</v>
+      </c>
+      <c r="S70">
+        <v>2.63</v>
+      </c>
+      <c r="T70">
+        <v>3.2</v>
+      </c>
+      <c r="U70">
         <v>1.3</v>
       </c>
-      <c r="S70">
-        <v>3</v>
-      </c>
-      <c r="T70">
-        <v>2.3</v>
-      </c>
-      <c r="U70">
+      <c r="V70">
+        <v>8.5</v>
+      </c>
+      <c r="W70">
+        <v>1.06</v>
+      </c>
+      <c r="X70">
+        <v>1.08</v>
+      </c>
+      <c r="Y70">
+        <v>7.8</v>
+      </c>
+      <c r="Z70">
+        <v>1.4</v>
+      </c>
+      <c r="AA70">
+        <v>2.75</v>
+      </c>
+      <c r="AB70">
+        <v>2.25</v>
+      </c>
+      <c r="AC70">
+        <v>1.57</v>
+      </c>
+      <c r="AD70">
+        <v>4.2</v>
+      </c>
+      <c r="AE70">
+        <v>1.18</v>
+      </c>
+      <c r="AF70">
+        <v>2.42</v>
+      </c>
+      <c r="AG70">
         <v>1.5</v>
       </c>
-      <c r="V70">
-        <v>5</v>
-      </c>
-      <c r="W70">
-        <v>1.13</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="Y70">
-        <v>12</v>
-      </c>
-      <c r="Z70">
-        <v>1.18</v>
-      </c>
-      <c r="AA70">
-        <v>4.1</v>
-      </c>
-      <c r="AB70">
-        <v>1.55</v>
-      </c>
-      <c r="AC70">
-        <v>2.2</v>
-      </c>
-      <c r="AD70">
-        <v>2.52</v>
-      </c>
-      <c r="AE70">
-        <v>1.45</v>
-      </c>
-      <c r="AF70">
-        <v>1.5</v>
-      </c>
-      <c r="AG70">
-        <v>2.3</v>
-      </c>
       <c r="AH70">
-        <v>4.33</v>
+        <v>8.9</v>
       </c>
       <c r="AI70">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AJ70" t="s">
         <v>242</v>
@@ -9237,7 +9237,7 @@
         <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
         <v>86</v>
@@ -9264,76 +9264,76 @@
         <v>241</v>
       </c>
       <c r="L71">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="M71">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="N71">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O71">
+        <v>1.44</v>
+      </c>
+      <c r="P71">
+        <v>12</v>
+      </c>
+      <c r="Q71">
+        <v>2.88</v>
+      </c>
+      <c r="R71">
+        <v>1.28</v>
+      </c>
+      <c r="S71">
+        <v>3.18</v>
+      </c>
+      <c r="T71">
+        <v>2.4</v>
+      </c>
+      <c r="U71">
+        <v>1.48</v>
+      </c>
+      <c r="V71">
+        <v>6.1</v>
+      </c>
+      <c r="W71">
+        <v>1.13</v>
+      </c>
+      <c r="X71">
+        <v>1.04</v>
+      </c>
+      <c r="Y71">
+        <v>11</v>
+      </c>
+      <c r="Z71">
+        <v>1.15</v>
+      </c>
+      <c r="AA71">
+        <v>4.2</v>
+      </c>
+      <c r="AB71">
         <v>1.67</v>
       </c>
-      <c r="P71">
-        <v>6.5</v>
-      </c>
-      <c r="Q71">
-        <v>2.75</v>
-      </c>
-      <c r="R71">
-        <v>1.44</v>
-      </c>
-      <c r="S71">
-        <v>2.5</v>
-      </c>
-      <c r="T71">
-        <v>3.3</v>
-      </c>
-      <c r="U71">
-        <v>1.3</v>
-      </c>
-      <c r="V71">
-        <v>9.25</v>
-      </c>
-      <c r="W71">
-        <v>1.05</v>
-      </c>
-      <c r="X71">
-        <v>1.1</v>
-      </c>
-      <c r="Y71">
-        <v>6</v>
-      </c>
-      <c r="Z71">
-        <v>1.44</v>
-      </c>
-      <c r="AA71">
-        <v>2.43</v>
-      </c>
-      <c r="AB71">
-        <v>2.37</v>
-      </c>
       <c r="AC71">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="AD71">
-        <v>4.5</v>
+        <v>2.63</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AF71">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AH71">
-        <v>9</v>
+        <v>4.65</v>
       </c>
       <c r="AI71">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ71" t="s">
         <v>242</v>
@@ -9496,76 +9496,76 @@
         <v>241</v>
       </c>
       <c r="L73">
+        <v>1.96</v>
+      </c>
+      <c r="M73">
+        <v>3.81</v>
+      </c>
+      <c r="N73">
         <v>2.05</v>
       </c>
-      <c r="M73">
+      <c r="O73">
+        <v>1.62</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>2.38</v>
+      </c>
+      <c r="R73">
+        <v>1.3</v>
+      </c>
+      <c r="S73">
+        <v>3.2</v>
+      </c>
+      <c r="T73">
+        <v>2.3</v>
+      </c>
+      <c r="U73">
+        <v>1.5</v>
+      </c>
+      <c r="V73">
+        <v>5.5</v>
+      </c>
+      <c r="W73">
+        <v>1.11</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>11</v>
+      </c>
+      <c r="Z73">
+        <v>1.14</v>
+      </c>
+      <c r="AA73">
+        <v>4.4</v>
+      </c>
+      <c r="AB73">
+        <v>1.63</v>
+      </c>
+      <c r="AC73">
+        <v>2.16</v>
+      </c>
+      <c r="AD73">
+        <v>2.57</v>
+      </c>
+      <c r="AE73">
+        <v>1.46</v>
+      </c>
+      <c r="AF73">
+        <v>1.57</v>
+      </c>
+      <c r="AG73">
+        <v>2.28</v>
+      </c>
+      <c r="AH73">
         <v>4.33</v>
       </c>
-      <c r="N73">
-        <v>2.55</v>
-      </c>
-      <c r="O73">
-        <v>1.67</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>2.1</v>
-      </c>
-      <c r="R73">
-        <v>1.22</v>
-      </c>
-      <c r="S73">
-        <v>3.6</v>
-      </c>
-      <c r="T73">
-        <v>2.05</v>
-      </c>
-      <c r="U73">
-        <v>1.62</v>
-      </c>
-      <c r="V73">
-        <v>4.33</v>
-      </c>
-      <c r="W73">
-        <v>1.18</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
-      </c>
-      <c r="Z73">
+      <c r="AI73">
         <v>1.11</v>
-      </c>
-      <c r="AA73">
-        <v>5</v>
-      </c>
-      <c r="AB73">
-        <v>1.42</v>
-      </c>
-      <c r="AC73">
-        <v>2.61</v>
-      </c>
-      <c r="AD73">
-        <v>2.05</v>
-      </c>
-      <c r="AE73">
-        <v>1.67</v>
-      </c>
-      <c r="AF73">
-        <v>1.38</v>
-      </c>
-      <c r="AG73">
-        <v>2.75</v>
-      </c>
-      <c r="AH73">
-        <v>3.2</v>
-      </c>
-      <c r="AI73">
-        <v>1.27</v>
       </c>
       <c r="AJ73" t="s">
         <v>242</v>
@@ -9612,76 +9612,76 @@
         <v>241</v>
       </c>
       <c r="L74">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="M74">
+        <v>4.33</v>
+      </c>
+      <c r="N74">
+        <v>2.55</v>
+      </c>
+      <c r="O74">
+        <v>1.67</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>2.1</v>
+      </c>
+      <c r="R74">
+        <v>1.22</v>
+      </c>
+      <c r="S74">
         <v>3.6</v>
       </c>
-      <c r="N74">
+      <c r="T74">
         <v>2.05</v>
       </c>
-      <c r="O74">
+      <c r="U74">
         <v>1.62</v>
       </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>2.38</v>
-      </c>
-      <c r="R74">
+      <c r="V74">
+        <v>4.33</v>
+      </c>
+      <c r="W74">
+        <v>1.18</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>1.11</v>
+      </c>
+      <c r="AA74">
+        <v>5</v>
+      </c>
+      <c r="AB74">
+        <v>1.38</v>
+      </c>
+      <c r="AC74">
+        <v>2.6</v>
+      </c>
+      <c r="AD74">
+        <v>2.05</v>
+      </c>
+      <c r="AE74">
+        <v>1.67</v>
+      </c>
+      <c r="AF74">
+        <v>1.37</v>
+      </c>
+      <c r="AG74">
+        <v>2.7</v>
+      </c>
+      <c r="AH74">
+        <v>3.2</v>
+      </c>
+      <c r="AI74">
         <v>1.3</v>
-      </c>
-      <c r="S74">
-        <v>3.2</v>
-      </c>
-      <c r="T74">
-        <v>2.4</v>
-      </c>
-      <c r="U74">
-        <v>1.5</v>
-      </c>
-      <c r="V74">
-        <v>5.5</v>
-      </c>
-      <c r="W74">
-        <v>1.11</v>
-      </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>11</v>
-      </c>
-      <c r="Z74">
-        <v>1.18</v>
-      </c>
-      <c r="AA74">
-        <v>4</v>
-      </c>
-      <c r="AB74">
-        <v>1.63</v>
-      </c>
-      <c r="AC74">
-        <v>2.1</v>
-      </c>
-      <c r="AD74">
-        <v>2.57</v>
-      </c>
-      <c r="AE74">
-        <v>1.45</v>
-      </c>
-      <c r="AF74">
-        <v>1.57</v>
-      </c>
-      <c r="AG74">
-        <v>2.28</v>
-      </c>
-      <c r="AH74">
-        <v>4.1</v>
-      </c>
-      <c r="AI74">
-        <v>1.17</v>
       </c>
       <c r="AJ74" t="s">
         <v>242</v>
@@ -9728,13 +9728,13 @@
         <v>241</v>
       </c>
       <c r="L75">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="M75">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="N75">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="O75">
         <v>1.8</v>
@@ -9749,7 +9749,7 @@
         <v>1.22</v>
       </c>
       <c r="S75">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="T75">
         <v>2.05</v>
@@ -9770,13 +9770,13 @@
         <v>11</v>
       </c>
       <c r="Z75">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AA75">
         <v>4.7</v>
       </c>
       <c r="AB75">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AC75">
         <v>2.45</v>
@@ -9788,10 +9788,10 @@
         <v>1.6</v>
       </c>
       <c r="AF75">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG75">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH75">
         <v>3.5</v>
@@ -9844,13 +9844,13 @@
         <v>241</v>
       </c>
       <c r="L76">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M76">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N76">
-        <v>5.5</v>
+        <v>5.82</v>
       </c>
       <c r="O76">
         <v>1.44</v>
@@ -9862,46 +9862,46 @@
         <v>3.25</v>
       </c>
       <c r="R76">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S76">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T76">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U76">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V76">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W76">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y76">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="Z76">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AA76">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB76">
         <v>2.25</v>
       </c>
       <c r="AC76">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AD76">
         <v>4.15</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
         <v>2.1</v>
@@ -9910,10 +9910,10 @@
         <v>1.7</v>
       </c>
       <c r="AH76">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="AI76">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ76" t="s">
         <v>242</v>
@@ -9978,46 +9978,46 @@
         <v>2.3</v>
       </c>
       <c r="R77">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S77">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="T77">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U77">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V77">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y77">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Z77">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA77">
         <v>2.63</v>
       </c>
       <c r="AB77">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AC77">
         <v>1.53</v>
       </c>
       <c r="AD77">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF77">
         <v>1.93</v>
@@ -10026,7 +10026,7 @@
         <v>1.79</v>
       </c>
       <c r="AH77">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="AI77">
         <v>1.05</v>
@@ -10049,16 +10049,16 @@
         <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D78" t="s">
         <v>86</v>
       </c>
       <c r="E78" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F78" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10076,76 +10076,76 @@
         <v>241</v>
       </c>
       <c r="L78">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="M78">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N78">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O78">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q78">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R78">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="S78">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="T78">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="U78">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z78">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="AA78">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB78">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="AC78">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="AD78">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="AE78">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AG78">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AH78">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AI78">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ78" t="s">
         <v>242</v>
@@ -10171,10 +10171,10 @@
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F79" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10192,76 +10192,76 @@
         <v>241</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P79">
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R79">
         <v>1.22</v>
       </c>
       <c r="S79">
+        <v>3.5</v>
+      </c>
+      <c r="T79">
+        <v>2.1</v>
+      </c>
+      <c r="U79">
+        <v>1.6</v>
+      </c>
+      <c r="V79">
+        <v>4.75</v>
+      </c>
+      <c r="W79">
+        <v>1.15</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>1.14</v>
+      </c>
+      <c r="AA79">
+        <v>4.5</v>
+      </c>
+      <c r="AB79">
+        <v>1.5</v>
+      </c>
+      <c r="AC79">
+        <v>2.3</v>
+      </c>
+      <c r="AD79">
+        <v>2.2</v>
+      </c>
+      <c r="AE79">
+        <v>1.55</v>
+      </c>
+      <c r="AF79">
+        <v>1.44</v>
+      </c>
+      <c r="AG79">
+        <v>2.6</v>
+      </c>
+      <c r="AH79">
         <v>3.6</v>
       </c>
-      <c r="T79">
-        <v>2.05</v>
-      </c>
-      <c r="U79">
-        <v>1.62</v>
-      </c>
-      <c r="V79">
-        <v>4.33</v>
-      </c>
-      <c r="W79">
-        <v>1.18</v>
-      </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>0</v>
-      </c>
-      <c r="Z79">
-        <v>1.11</v>
-      </c>
-      <c r="AA79">
-        <v>5.5</v>
-      </c>
-      <c r="AB79">
-        <v>1.45</v>
-      </c>
-      <c r="AC79">
-        <v>2.62</v>
-      </c>
-      <c r="AD79">
-        <v>2</v>
-      </c>
-      <c r="AE79">
-        <v>1.73</v>
-      </c>
-      <c r="AF79">
-        <v>1.42</v>
-      </c>
-      <c r="AG79">
-        <v>2.45</v>
-      </c>
-      <c r="AH79">
-        <v>3.2</v>
-      </c>
       <c r="AI79">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AJ79" t="s">
         <v>242</v>
@@ -10281,16 +10281,16 @@
         <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D80" t="s">
         <v>86</v>
       </c>
       <c r="E80" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="F80" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10308,76 +10308,76 @@
         <v>241</v>
       </c>
       <c r="L80">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="M80">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N80">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O80">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="P80">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R80">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="S80">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="T80">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="U80">
+        <v>1.62</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>1.12</v>
+      </c>
+      <c r="AA80">
+        <v>4.8</v>
+      </c>
+      <c r="AB80">
+        <v>1.45</v>
+      </c>
+      <c r="AC80">
+        <v>2.45</v>
+      </c>
+      <c r="AD80">
+        <v>2.1</v>
+      </c>
+      <c r="AE80">
+        <v>1.6</v>
+      </c>
+      <c r="AF80">
+        <v>1.87</v>
+      </c>
+      <c r="AG80">
+        <v>1.83</v>
+      </c>
+      <c r="AH80">
+        <v>3.5</v>
+      </c>
+      <c r="AI80">
         <v>1.25</v>
-      </c>
-      <c r="V80">
-        <v>11</v>
-      </c>
-      <c r="W80">
-        <v>1.05</v>
-      </c>
-      <c r="X80">
-        <v>1.1</v>
-      </c>
-      <c r="Y80">
-        <v>6.5</v>
-      </c>
-      <c r="Z80">
-        <v>1.45</v>
-      </c>
-      <c r="AA80">
-        <v>2.5</v>
-      </c>
-      <c r="AB80">
-        <v>2.6</v>
-      </c>
-      <c r="AC80">
-        <v>1.48</v>
-      </c>
-      <c r="AD80">
-        <v>5.25</v>
-      </c>
-      <c r="AE80">
-        <v>1.15</v>
-      </c>
-      <c r="AF80">
-        <v>2.75</v>
-      </c>
-      <c r="AG80">
-        <v>1.4</v>
-      </c>
-      <c r="AH80">
-        <v>10</v>
-      </c>
-      <c r="AI80">
-        <v>1.04</v>
       </c>
       <c r="AJ80" t="s">
         <v>242</v>
@@ -10424,40 +10424,40 @@
         <v>241</v>
       </c>
       <c r="L81">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P81">
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S81">
         <v>3.6</v>
       </c>
       <c r="T81">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U81">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V81">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="W81">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -10466,34 +10466,34 @@
         <v>0</v>
       </c>
       <c r="Z81">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AA81">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AB81">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC81">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AD81">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AE81">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF81">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG81">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AH81">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AI81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ81" t="s">
         <v>242</v>
@@ -10588,10 +10588,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC82">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -10674,19 +10674,19 @@
         <v>2.2</v>
       </c>
       <c r="R83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S83">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T83">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="U83">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V83">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="W83">
         <v>1.2</v>
@@ -10701,13 +10701,13 @@
         <v>1.1</v>
       </c>
       <c r="AA83">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AB83">
         <v>1.4</v>
       </c>
       <c r="AC83">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD83">
         <v>1.93</v>
@@ -10716,10 +10716,10 @@
         <v>1.72</v>
       </c>
       <c r="AF83">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG83">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AH83">
         <v>3.2</v>

--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -265,12 +265,12 @@
     <t>Brazil Serie C</t>
   </si>
   <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>USA MLS</t>
   </si>
   <si>
@@ -280,33 +280,33 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Rockdale City Suns</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
-    <t>Rockdale City Suns</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Ansan Greeners</t>
+    <t>Dalian Huayi</t>
   </si>
   <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
-  </si>
-  <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
@@ -337,75 +337,75 @@
     <t>AIK</t>
   </si>
   <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
     <t>Racing Club</t>
   </si>
   <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
+    <t>Antofagasta</t>
+  </si>
+  <si>
     <t>Santiago Morning</t>
   </si>
   <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
@@ -415,12 +415,12 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Alvarado</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
@@ -442,55 +442,58 @@
     <t>Criciúma</t>
   </si>
   <si>
+    <t>Guarani</t>
+  </si>
+  <si>
     <t>Botafogo PB</t>
   </si>
   <si>
-    <t>Guarani</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
+    <t>Caxias</t>
+  </si>
+  <si>
+    <t>York9 FC</t>
+  </si>
+  <si>
+    <t>FC Cincinnati II</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>FC Cincinnati II</t>
-  </si>
-  <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Caxias</t>
-  </si>
-  <si>
-    <t>York9 FC</t>
+    <t>Inter Miami II</t>
+  </si>
+  <si>
+    <t>Orlando City II</t>
   </si>
   <si>
     <t>St. Louis City</t>
   </si>
   <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
-    <t>Inter Miami II</t>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
   </si>
   <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
+    <t>Colorado Rapids II</t>
   </si>
   <si>
     <t>Houston Dynamo FC II</t>
@@ -499,9 +502,6 @@
     <t>San Jose Earthquakes II</t>
   </si>
   <si>
-    <t>Colorado Rapids II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -511,33 +511,33 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>APIA Leichhardt Tigers</t>
+  </si>
+  <si>
+    <t>St George City FA</t>
+  </si>
+  <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
-    <t>APIA Leichhardt Tigers</t>
-  </si>
-  <si>
-    <t>St George City FA</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Seoul E-Land</t>
+    <t>Nanjing City</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
@@ -568,75 +568,75 @@
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
     <t>Tigre</t>
   </si>
   <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
     <t>Barracas Central</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
     <t>Halmstad</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Copiapó</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
@@ -646,12 +646,12 @@
     <t>Viking</t>
   </si>
   <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
     <t>San Miguel</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
@@ -673,64 +673,64 @@
     <t>Ferroviária</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
     <t>Londrina</t>
   </si>
   <si>
-    <t>Ituano</t>
-  </si>
-  <si>
     <t>Real Monarchs</t>
   </si>
   <si>
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Concepción</t>
+  </si>
+  <si>
     <t>Remo</t>
   </si>
   <si>
-    <t>Concepción</t>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
   </si>
   <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Huntsville City</t>
-  </si>
-  <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>Anápolis</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
+    <t>Crown Legacy</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
   </si>
   <si>
     <t>Portland Timbers</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Crown Legacy</t>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
-    <t>Ceará</t>
+    <t>Whitecaps II</t>
   </si>
   <si>
     <t>North Texas</t>
   </si>
   <si>
     <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Whitecaps II</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1376,76 +1376,76 @@
         <v>241</v>
       </c>
       <c r="L3">
-        <v>5.38</v>
+        <v>2.1</v>
       </c>
       <c r="M3">
-        <v>4.72</v>
+        <v>3.6</v>
       </c>
       <c r="N3">
-        <v>1.47</v>
+        <v>2.75</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB3">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AC3">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE3">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ3" t="s">
         <v>242</v>
@@ -1492,76 +1492,76 @@
         <v>241</v>
       </c>
       <c r="L4">
+        <v>2.65</v>
+      </c>
+      <c r="M4">
+        <v>3.5</v>
+      </c>
+      <c r="N4">
+        <v>2.3</v>
+      </c>
+      <c r="O4">
+        <v>1.8</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
         <v>2.1</v>
       </c>
-      <c r="M4">
-        <v>3.6</v>
-      </c>
-      <c r="N4">
-        <v>2.75</v>
-      </c>
-      <c r="O4">
-        <v>1.67</v>
-      </c>
-      <c r="P4">
-        <v>20</v>
-      </c>
-      <c r="Q4">
-        <v>2.2</v>
-      </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AD4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>242</v>
@@ -1608,76 +1608,76 @@
         <v>241</v>
       </c>
       <c r="L5">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="M5">
+        <v>3.6</v>
+      </c>
+      <c r="N5">
         <v>3.5</v>
       </c>
-      <c r="N5">
+      <c r="O5">
+        <v>1.64</v>
+      </c>
+      <c r="P5">
+        <v>16.75</v>
+      </c>
+      <c r="Q5">
+        <v>2.24</v>
+      </c>
+      <c r="R5">
+        <v>1.3</v>
+      </c>
+      <c r="S5">
+        <v>3.2</v>
+      </c>
+      <c r="T5">
+        <v>2.35</v>
+      </c>
+      <c r="U5">
+        <v>1.5</v>
+      </c>
+      <c r="V5">
+        <v>5.5</v>
+      </c>
+      <c r="W5">
+        <v>1.12</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>11</v>
+      </c>
+      <c r="Z5">
+        <v>1.15</v>
+      </c>
+      <c r="AA5">
+        <v>4.25</v>
+      </c>
+      <c r="AB5">
+        <v>1.6</v>
+      </c>
+      <c r="AC5">
+        <v>2.25</v>
+      </c>
+      <c r="AD5">
+        <v>2.55</v>
+      </c>
+      <c r="AE5">
+        <v>1.44</v>
+      </c>
+      <c r="AF5">
+        <v>1.57</v>
+      </c>
+      <c r="AG5">
         <v>2.3</v>
       </c>
-      <c r="O5">
-        <v>1.8</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>2.1</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>1.72</v>
-      </c>
-      <c r="AC5">
-        <v>2.07</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
       <c r="AH5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>242</v>
@@ -1724,76 +1724,76 @@
         <v>241</v>
       </c>
       <c r="L6">
-        <v>1.82</v>
+        <v>5.38</v>
       </c>
       <c r="M6">
-        <v>3.6</v>
+        <v>4.72</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="O6">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
         <v>1.5</v>
       </c>
-      <c r="V6">
-        <v>5.5</v>
-      </c>
-      <c r="W6">
-        <v>1.12</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>11</v>
-      </c>
-      <c r="Z6">
-        <v>1.15</v>
-      </c>
-      <c r="AA6">
-        <v>4.25</v>
-      </c>
-      <c r="AB6">
+      <c r="AC6">
+        <v>2.5</v>
+      </c>
+      <c r="AD6">
+        <v>2.2</v>
+      </c>
+      <c r="AE6">
         <v>1.6</v>
       </c>
-      <c r="AC6">
-        <v>2.25</v>
-      </c>
-      <c r="AD6">
-        <v>2.55</v>
-      </c>
-      <c r="AE6">
-        <v>1.44</v>
-      </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>242</v>
@@ -1956,22 +1956,22 @@
         <v>241</v>
       </c>
       <c r="L8">
-        <v>2.09</v>
+        <v>3.84</v>
       </c>
       <c r="M8">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N8">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P8">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="R8">
         <v>1.44</v>
@@ -1995,37 +1995,37 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AA8">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD8">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AE8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH8">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AI8">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
         <v>242</v>
@@ -2072,22 +2072,22 @@
         <v>241</v>
       </c>
       <c r="L9">
-        <v>3.84</v>
+        <v>2.09</v>
       </c>
       <c r="M9">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>3.09</v>
       </c>
       <c r="O9">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2111,37 +2111,37 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Z9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AA9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AB9">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD9">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH9">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AI9">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>242</v>
@@ -2188,76 +2188,76 @@
         <v>241</v>
       </c>
       <c r="L10">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="M10">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N10">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P10">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S10">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U10">
+        <v>1.45</v>
+      </c>
+      <c r="V10">
+        <v>6.9</v>
+      </c>
+      <c r="W10">
+        <v>1.09</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>10</v>
+      </c>
+      <c r="Z10">
         <v>1.27</v>
       </c>
-      <c r="V10">
-        <v>8.1</v>
-      </c>
-      <c r="W10">
-        <v>1.02</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>7.3</v>
-      </c>
-      <c r="Z10">
-        <v>1.4</v>
-      </c>
       <c r="AA10">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB10">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC10">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="AH10">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="AI10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
         <v>242</v>
@@ -2304,76 +2304,76 @@
         <v>241</v>
       </c>
       <c r="L11">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="M11">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N11">
+        <v>2.95</v>
+      </c>
+      <c r="O11">
+        <v>1.8</v>
+      </c>
+      <c r="P11">
+        <v>7.6</v>
+      </c>
+      <c r="Q11">
+        <v>2.3</v>
+      </c>
+      <c r="R11">
+        <v>1.44</v>
+      </c>
+      <c r="S11">
+        <v>2.5</v>
+      </c>
+      <c r="T11">
+        <v>3.3</v>
+      </c>
+      <c r="U11">
+        <v>1.27</v>
+      </c>
+      <c r="V11">
+        <v>8.1</v>
+      </c>
+      <c r="W11">
+        <v>1.02</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>7.3</v>
+      </c>
+      <c r="Z11">
+        <v>1.4</v>
+      </c>
+      <c r="AA11">
+        <v>2.7</v>
+      </c>
+      <c r="AB11">
+        <v>2.25</v>
+      </c>
+      <c r="AC11">
+        <v>1.5</v>
+      </c>
+      <c r="AD11">
         <v>4</v>
       </c>
-      <c r="O11">
-        <v>1.62</v>
-      </c>
-      <c r="P11">
-        <v>9.1</v>
-      </c>
-      <c r="Q11">
-        <v>2.75</v>
-      </c>
-      <c r="R11">
-        <v>1.35</v>
-      </c>
-      <c r="S11">
-        <v>2.8</v>
-      </c>
-      <c r="T11">
-        <v>2.69</v>
-      </c>
-      <c r="U11">
-        <v>1.45</v>
-      </c>
-      <c r="V11">
-        <v>6.9</v>
-      </c>
-      <c r="W11">
-        <v>1.09</v>
-      </c>
-      <c r="X11">
+      <c r="AE11">
+        <v>1.15</v>
+      </c>
+      <c r="AF11">
+        <v>1.93</v>
+      </c>
+      <c r="AG11">
+        <v>1.66</v>
+      </c>
+      <c r="AH11">
+        <v>8.1</v>
+      </c>
+      <c r="AI11">
         <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>10</v>
-      </c>
-      <c r="Z11">
-        <v>1.27</v>
-      </c>
-      <c r="AA11">
-        <v>3.4</v>
-      </c>
-      <c r="AB11">
-        <v>1.87</v>
-      </c>
-      <c r="AC11">
-        <v>1.85</v>
-      </c>
-      <c r="AD11">
-        <v>3</v>
-      </c>
-      <c r="AE11">
-        <v>1.33</v>
-      </c>
-      <c r="AF11">
-        <v>1.7</v>
-      </c>
-      <c r="AG11">
-        <v>1.97</v>
-      </c>
-      <c r="AH11">
-        <v>6</v>
-      </c>
-      <c r="AI11">
-        <v>1.06</v>
       </c>
       <c r="AJ11" t="s">
         <v>242</v>
@@ -3669,7 +3669,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -3696,76 +3696,76 @@
         <v>241</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ23" t="s">
         <v>242</v>
@@ -4597,7 +4597,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
         <v>86</v>
@@ -4624,76 +4624,76 @@
         <v>241</v>
       </c>
       <c r="L31">
-        <v>4</v>
+        <v>1.42</v>
       </c>
       <c r="M31">
-        <v>3.13</v>
+        <v>4.1</v>
       </c>
       <c r="N31">
-        <v>1.86</v>
+        <v>5.8</v>
       </c>
       <c r="O31">
-        <v>2.52</v>
+        <v>1.33</v>
       </c>
       <c r="P31">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="Q31">
-        <v>1.68</v>
+        <v>3.5</v>
       </c>
       <c r="R31">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S31">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AA31">
+        <v>4.2</v>
+      </c>
+      <c r="AB31">
+        <v>1.63</v>
+      </c>
+      <c r="AC31">
+        <v>2.13</v>
+      </c>
+      <c r="AD31">
         <v>2.8</v>
       </c>
-      <c r="AB31">
-        <v>2.25</v>
-      </c>
-      <c r="AC31">
-        <v>1.62</v>
-      </c>
-      <c r="AD31">
-        <v>4.2</v>
-      </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AF31">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH31">
-        <v>9</v>
+        <v>5.25</v>
       </c>
       <c r="AI31">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ31" t="s">
         <v>242</v>
@@ -4829,7 +4829,7 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>86</v>
@@ -4856,76 +4856,76 @@
         <v>241</v>
       </c>
       <c r="L33">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="s">
         <v>242</v>
@@ -4972,76 +4972,76 @@
         <v>241</v>
       </c>
       <c r="L34">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="M34">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N34">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O34">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="P34">
-        <v>9.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q34">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S34">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U34">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA34">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AB34">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="AC34">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
-        <v>3.3</v>
+        <v>2.31</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH34">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AI34">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ34" t="s">
         <v>242</v>
@@ -5088,76 +5088,76 @@
         <v>241</v>
       </c>
       <c r="L35">
-        <v>1.42</v>
+        <v>3.5</v>
       </c>
       <c r="M35">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N35">
-        <v>5.8</v>
+        <v>1.87</v>
       </c>
       <c r="O35">
+        <v>2.6</v>
+      </c>
+      <c r="P35">
+        <v>9.25</v>
+      </c>
+      <c r="Q35">
+        <v>1.57</v>
+      </c>
+      <c r="R35">
+        <v>1.36</v>
+      </c>
+      <c r="S35">
+        <v>3</v>
+      </c>
+      <c r="T35">
+        <v>2.75</v>
+      </c>
+      <c r="U35">
+        <v>1.4</v>
+      </c>
+      <c r="V35">
+        <v>7</v>
+      </c>
+      <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.05</v>
+      </c>
+      <c r="Y35">
+        <v>9</v>
+      </c>
+      <c r="Z35">
+        <v>1.3</v>
+      </c>
+      <c r="AA35">
+        <v>3.45</v>
+      </c>
+      <c r="AB35">
+        <v>1.82</v>
+      </c>
+      <c r="AC35">
+        <v>1.88</v>
+      </c>
+      <c r="AD35">
+        <v>3.3</v>
+      </c>
+      <c r="AE35">
         <v>1.33</v>
       </c>
-      <c r="P35">
-        <v>11.5</v>
-      </c>
-      <c r="Q35">
-        <v>3.5</v>
-      </c>
-      <c r="R35">
-        <v>1.3</v>
-      </c>
-      <c r="S35">
-        <v>3.4</v>
-      </c>
-      <c r="T35">
-        <v>2.5</v>
-      </c>
-      <c r="U35">
-        <v>1.5</v>
-      </c>
-      <c r="V35">
-        <v>6</v>
-      </c>
-      <c r="W35">
-        <v>1.13</v>
-      </c>
-      <c r="X35">
-        <v>1.04</v>
-      </c>
-      <c r="Y35">
-        <v>10</v>
-      </c>
-      <c r="Z35">
-        <v>1.22</v>
-      </c>
-      <c r="AA35">
-        <v>4.2</v>
-      </c>
-      <c r="AB35">
-        <v>1.63</v>
-      </c>
-      <c r="AC35">
-        <v>2.13</v>
-      </c>
-      <c r="AD35">
-        <v>2.8</v>
-      </c>
-      <c r="AE35">
-        <v>1.42</v>
-      </c>
       <c r="AF35">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH35">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI35">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ35" t="s">
         <v>242</v>
@@ -5177,7 +5177,7 @@
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
         <v>86</v>
@@ -5204,76 +5204,76 @@
         <v>241</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ36" t="s">
         <v>242</v>
@@ -5293,7 +5293,7 @@
         <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
         <v>86</v>
@@ -5320,76 +5320,76 @@
         <v>241</v>
       </c>
       <c r="L37">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="s">
         <v>242</v>
@@ -6016,76 +6016,76 @@
         <v>241</v>
       </c>
       <c r="L43">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="M43">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="O43">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="P43">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="Q43">
-        <v>1.81</v>
+        <v>2.61</v>
       </c>
       <c r="R43">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S43">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="T43">
+        <v>2.71</v>
+      </c>
+      <c r="U43">
+        <v>1.41</v>
+      </c>
+      <c r="V43">
+        <v>7</v>
+      </c>
+      <c r="W43">
+        <v>1.1</v>
+      </c>
+      <c r="X43">
+        <v>1.02</v>
+      </c>
+      <c r="Y43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z43">
+        <v>1.29</v>
+      </c>
+      <c r="AA43">
+        <v>3.4</v>
+      </c>
+      <c r="AB43">
+        <v>1.85</v>
+      </c>
+      <c r="AC43">
+        <v>1.85</v>
+      </c>
+      <c r="AD43">
         <v>3</v>
       </c>
-      <c r="U43">
-        <v>1.34</v>
-      </c>
-      <c r="V43">
-        <v>8</v>
-      </c>
-      <c r="W43">
-        <v>1.06</v>
-      </c>
-      <c r="X43">
-        <v>1.05</v>
-      </c>
-      <c r="Y43">
-        <v>8</v>
-      </c>
-      <c r="Z43">
+      <c r="AE43">
         <v>1.33</v>
       </c>
-      <c r="AA43">
-        <v>2.83</v>
-      </c>
-      <c r="AB43">
+      <c r="AF43">
+        <v>1.77</v>
+      </c>
+      <c r="AG43">
         <v>2.1</v>
       </c>
-      <c r="AC43">
-        <v>1.65</v>
-      </c>
-      <c r="AD43">
-        <v>3.8</v>
-      </c>
-      <c r="AE43">
-        <v>1.19</v>
-      </c>
-      <c r="AF43">
-        <v>1.91</v>
-      </c>
-      <c r="AG43">
-        <v>1.8</v>
-      </c>
       <c r="AH43">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AI43">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AJ43" t="s">
         <v>242</v>
@@ -6132,76 +6132,76 @@
         <v>241</v>
       </c>
       <c r="L44">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="M44">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N44">
+        <v>1.95</v>
+      </c>
+      <c r="O44">
+        <v>2.3</v>
+      </c>
+      <c r="P44">
+        <v>7.8</v>
+      </c>
+      <c r="Q44">
+        <v>1.81</v>
+      </c>
+      <c r="R44">
+        <v>1.44</v>
+      </c>
+      <c r="S44">
         <v>2.75</v>
       </c>
-      <c r="O44">
-        <v>1.61</v>
-      </c>
-      <c r="P44">
-        <v>8.9</v>
-      </c>
-      <c r="Q44">
-        <v>2.61</v>
-      </c>
-      <c r="R44">
-        <v>1.36</v>
-      </c>
-      <c r="S44">
-        <v>2.89</v>
-      </c>
       <c r="T44">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="V44">
+        <v>8</v>
+      </c>
+      <c r="W44">
+        <v>1.06</v>
+      </c>
+      <c r="X44">
+        <v>1.05</v>
+      </c>
+      <c r="Y44">
+        <v>8</v>
+      </c>
+      <c r="Z44">
+        <v>1.33</v>
+      </c>
+      <c r="AA44">
+        <v>2.83</v>
+      </c>
+      <c r="AB44">
+        <v>2.1</v>
+      </c>
+      <c r="AC44">
+        <v>1.65</v>
+      </c>
+      <c r="AD44">
+        <v>3.8</v>
+      </c>
+      <c r="AE44">
+        <v>1.19</v>
+      </c>
+      <c r="AF44">
+        <v>1.91</v>
+      </c>
+      <c r="AG44">
+        <v>1.8</v>
+      </c>
+      <c r="AH44">
         <v>7</v>
       </c>
-      <c r="W44">
-        <v>1.1</v>
-      </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z44">
-        <v>1.29</v>
-      </c>
-      <c r="AA44">
-        <v>3.4</v>
-      </c>
-      <c r="AB44">
-        <v>1.85</v>
-      </c>
-      <c r="AC44">
-        <v>1.85</v>
-      </c>
-      <c r="AD44">
-        <v>3</v>
-      </c>
-      <c r="AE44">
-        <v>1.33</v>
-      </c>
-      <c r="AF44">
-        <v>1.77</v>
-      </c>
-      <c r="AG44">
-        <v>2.1</v>
-      </c>
-      <c r="AH44">
-        <v>5.8</v>
-      </c>
       <c r="AI44">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AJ44" t="s">
         <v>242</v>
@@ -6575,10 +6575,10 @@
         <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F48" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6712,76 +6712,76 @@
         <v>241</v>
       </c>
       <c r="L49">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M49">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="O49">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R49">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="S49">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="T49">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="U49">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V49">
         <v>11</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y49">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="Z49">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA49">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB49">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AC49">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD49">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG49">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH49">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AI49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ49" t="s">
         <v>242</v>
@@ -6828,76 +6828,76 @@
         <v>241</v>
       </c>
       <c r="L50">
+        <v>4.2</v>
+      </c>
+      <c r="M50">
+        <v>2.8</v>
+      </c>
+      <c r="N50">
         <v>2</v>
       </c>
-      <c r="M50">
-        <v>2.87</v>
-      </c>
-      <c r="N50">
-        <v>3.7</v>
-      </c>
       <c r="O50">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="P50">
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="R50">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S50">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="T50">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U50">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V50">
         <v>11</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y50">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="Z50">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA50">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB50">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AC50">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD50">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF50">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG50">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH50">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI50">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AJ50" t="s">
         <v>242</v>
@@ -7729,16 +7729,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D58" t="s">
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="F58" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7756,76 +7756,76 @@
         <v>241</v>
       </c>
       <c r="L58">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="M58">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N58">
-        <v>3.29</v>
+        <v>4.75</v>
       </c>
       <c r="O58">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="P58">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q58">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="R58">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="S58">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U58">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V58">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y58">
         <v>7</v>
       </c>
       <c r="Z58">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AA58">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB58">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AC58">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD58">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AE58">
         <v>1.18</v>
       </c>
       <c r="AF58">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG58">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH58">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ58" t="s">
         <v>242</v>
@@ -7845,16 +7845,16 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F59" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7872,76 +7872,76 @@
         <v>241</v>
       </c>
       <c r="L59">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="M59">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="N59">
-        <v>4.75</v>
+        <v>4.27</v>
       </c>
       <c r="O59">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P59">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q59">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R59">
         <v>1.53</v>
       </c>
       <c r="S59">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T59">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U59">
         <v>1.29</v>
       </c>
       <c r="V59">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W59">
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="Z59">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA59">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AB59">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC59">
         <v>1.5</v>
       </c>
       <c r="AD59">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE59">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF59">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG59">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH59">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI59">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ59" t="s">
         <v>242</v>
@@ -7988,76 +7988,76 @@
         <v>241</v>
       </c>
       <c r="L60">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="M60">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N60">
-        <v>4.27</v>
+        <v>3.29</v>
       </c>
       <c r="O60">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="P60">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q60">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R60">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S60">
         <v>2.45</v>
       </c>
       <c r="T60">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="U60">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V60">
         <v>9</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y60">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="Z60">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AA60">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AB60">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC60">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD60">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AE60">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF60">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG60">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH60">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI60">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ60" t="s">
         <v>242</v>
@@ -8425,7 +8425,7 @@
         <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
         <v>86</v>
@@ -8452,76 +8452,76 @@
         <v>241</v>
       </c>
       <c r="L64">
+        <v>2.3</v>
+      </c>
+      <c r="M64">
+        <v>3.1</v>
+      </c>
+      <c r="N64">
+        <v>2.7</v>
+      </c>
+      <c r="O64">
+        <v>1.89</v>
+      </c>
+      <c r="P64">
+        <v>8.9</v>
+      </c>
+      <c r="Q64">
+        <v>2.11</v>
+      </c>
+      <c r="R64">
+        <v>1.45</v>
+      </c>
+      <c r="S64">
+        <v>2.88</v>
+      </c>
+      <c r="T64">
+        <v>2.9</v>
+      </c>
+      <c r="U64">
+        <v>1.36</v>
+      </c>
+      <c r="V64">
+        <v>7</v>
+      </c>
+      <c r="W64">
+        <v>1.08</v>
+      </c>
+      <c r="X64">
+        <v>1.06</v>
+      </c>
+      <c r="Y64">
+        <v>9</v>
+      </c>
+      <c r="Z64">
+        <v>1.33</v>
+      </c>
+      <c r="AA64">
+        <v>3.2</v>
+      </c>
+      <c r="AB64">
+        <v>2.07</v>
+      </c>
+      <c r="AC64">
+        <v>1.75</v>
+      </c>
+      <c r="AD64">
+        <v>3.5</v>
+      </c>
+      <c r="AE64">
+        <v>1.25</v>
+      </c>
+      <c r="AF64">
+        <v>1.75</v>
+      </c>
+      <c r="AG64">
         <v>1.95</v>
       </c>
-      <c r="M64">
-        <v>3.35</v>
-      </c>
-      <c r="N64">
-        <v>4.02</v>
-      </c>
-      <c r="O64">
-        <v>1.67</v>
-      </c>
-      <c r="P64">
-        <v>6.75</v>
-      </c>
-      <c r="Q64">
-        <v>2.6</v>
-      </c>
-      <c r="R64">
-        <v>1.44</v>
-      </c>
-      <c r="S64">
-        <v>2.63</v>
-      </c>
-      <c r="T64">
-        <v>3.1</v>
-      </c>
-      <c r="U64">
-        <v>1.3</v>
-      </c>
-      <c r="V64">
-        <v>9.5</v>
-      </c>
-      <c r="W64">
-        <v>1.06</v>
-      </c>
-      <c r="X64">
-        <v>1.07</v>
-      </c>
-      <c r="Y64">
-        <v>7</v>
-      </c>
-      <c r="Z64">
-        <v>1.44</v>
-      </c>
-      <c r="AA64">
-        <v>2.7</v>
-      </c>
-      <c r="AB64">
-        <v>2.26</v>
-      </c>
-      <c r="AC64">
-        <v>1.64</v>
-      </c>
-      <c r="AD64">
-        <v>4.33</v>
-      </c>
-      <c r="AE64">
-        <v>1.17</v>
-      </c>
-      <c r="AF64">
-        <v>2</v>
-      </c>
-      <c r="AG64">
-        <v>1.73</v>
-      </c>
       <c r="AH64">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI64">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AJ64" t="s">
         <v>242</v>
@@ -8541,7 +8541,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
         <v>86</v>
@@ -8568,76 +8568,76 @@
         <v>241</v>
       </c>
       <c r="L65">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="M65">
+        <v>3.35</v>
+      </c>
+      <c r="N65">
+        <v>4.02</v>
+      </c>
+      <c r="O65">
+        <v>1.67</v>
+      </c>
+      <c r="P65">
+        <v>6.75</v>
+      </c>
+      <c r="Q65">
+        <v>2.6</v>
+      </c>
+      <c r="R65">
+        <v>1.44</v>
+      </c>
+      <c r="S65">
+        <v>2.63</v>
+      </c>
+      <c r="T65">
         <v>3.1</v>
       </c>
-      <c r="N65">
+      <c r="U65">
+        <v>1.3</v>
+      </c>
+      <c r="V65">
+        <v>9.5</v>
+      </c>
+      <c r="W65">
+        <v>1.06</v>
+      </c>
+      <c r="X65">
+        <v>1.07</v>
+      </c>
+      <c r="Y65">
+        <v>7</v>
+      </c>
+      <c r="Z65">
+        <v>1.44</v>
+      </c>
+      <c r="AA65">
         <v>2.7</v>
       </c>
-      <c r="O65">
-        <v>1.89</v>
-      </c>
-      <c r="P65">
-        <v>8.9</v>
-      </c>
-      <c r="Q65">
-        <v>2.11</v>
-      </c>
-      <c r="R65">
-        <v>1.45</v>
-      </c>
-      <c r="S65">
-        <v>2.88</v>
-      </c>
-      <c r="T65">
-        <v>2.9</v>
-      </c>
-      <c r="U65">
-        <v>1.36</v>
-      </c>
-      <c r="V65">
-        <v>7</v>
-      </c>
-      <c r="W65">
-        <v>1.08</v>
-      </c>
-      <c r="X65">
-        <v>1.06</v>
-      </c>
-      <c r="Y65">
-        <v>9</v>
-      </c>
-      <c r="Z65">
-        <v>1.33</v>
-      </c>
-      <c r="AA65">
-        <v>3.2</v>
-      </c>
       <c r="AB65">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="AC65">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AD65">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF65">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH65">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI65">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AJ65" t="s">
         <v>242</v>
@@ -8663,10 +8663,10 @@
         <v>86</v>
       </c>
       <c r="E66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F66" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
         <v>86</v>
@@ -8800,31 +8800,31 @@
         <v>241</v>
       </c>
       <c r="L67">
-        <v>2.09</v>
+        <v>1.51</v>
       </c>
       <c r="M67">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="N67">
-        <v>3.75</v>
+        <v>6.17</v>
       </c>
       <c r="O67">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="P67">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q67">
+        <v>4</v>
+      </c>
+      <c r="R67">
+        <v>1.48</v>
+      </c>
+      <c r="S67">
         <v>2.63</v>
       </c>
-      <c r="R67">
-        <v>1.44</v>
-      </c>
-      <c r="S67">
-        <v>2.5</v>
-      </c>
       <c r="T67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U67">
         <v>1.3</v>
@@ -8833,40 +8833,40 @@
         <v>8.5</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.08</v>
       </c>
       <c r="Y67">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z67">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA67">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB67">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
         <v>1.57</v>
       </c>
       <c r="AD67">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AE67">
         <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AG67">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AH67">
-        <v>8.75</v>
+        <v>8.9</v>
       </c>
       <c r="AI67">
         <v>1.04</v>
@@ -8889,7 +8889,7 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D68" t="s">
         <v>86</v>
@@ -8916,76 +8916,76 @@
         <v>241</v>
       </c>
       <c r="L68">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="M68">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N68">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="O68">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q68">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R68">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S68">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="T68">
+        <v>2.4</v>
+      </c>
+      <c r="U68">
+        <v>1.48</v>
+      </c>
+      <c r="V68">
+        <v>6.1</v>
+      </c>
+      <c r="W68">
+        <v>1.13</v>
+      </c>
+      <c r="X68">
+        <v>1.04</v>
+      </c>
+      <c r="Y68">
+        <v>11</v>
+      </c>
+      <c r="Z68">
+        <v>1.15</v>
+      </c>
+      <c r="AA68">
+        <v>4.2</v>
+      </c>
+      <c r="AB68">
+        <v>1.67</v>
+      </c>
+      <c r="AC68">
         <v>2.1</v>
       </c>
-      <c r="U68">
-        <v>1.6</v>
-      </c>
-      <c r="V68">
-        <v>4.5</v>
-      </c>
-      <c r="W68">
-        <v>1.17</v>
-      </c>
-      <c r="X68">
-        <v>1</v>
-      </c>
-      <c r="Y68">
-        <v>12</v>
-      </c>
-      <c r="Z68">
-        <v>1.14</v>
-      </c>
-      <c r="AA68">
-        <v>4.75</v>
-      </c>
-      <c r="AB68">
-        <v>1.5</v>
-      </c>
-      <c r="AC68">
-        <v>2.3</v>
-      </c>
       <c r="AD68">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AE68">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AF68">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AH68">
-        <v>3.6</v>
+        <v>4.65</v>
       </c>
       <c r="AI68">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AJ68" t="s">
         <v>242</v>
@@ -9005,7 +9005,7 @@
         <v>62</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D69" t="s">
         <v>86</v>
@@ -9032,76 +9032,76 @@
         <v>241</v>
       </c>
       <c r="L69">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M69">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="N69">
+        <v>3.6</v>
+      </c>
+      <c r="O69">
+        <v>1.53</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>2.5</v>
+      </c>
+      <c r="R69">
+        <v>1.22</v>
+      </c>
+      <c r="S69">
+        <v>3.5</v>
+      </c>
+      <c r="T69">
+        <v>2.1</v>
+      </c>
+      <c r="U69">
+        <v>1.6</v>
+      </c>
+      <c r="V69">
         <v>4.5</v>
       </c>
-      <c r="O69">
-        <v>1.67</v>
-      </c>
-      <c r="P69">
-        <v>6.5</v>
-      </c>
-      <c r="Q69">
-        <v>2.75</v>
-      </c>
-      <c r="R69">
-        <v>1.51</v>
-      </c>
-      <c r="S69">
-        <v>2.5</v>
-      </c>
-      <c r="T69">
-        <v>3.3</v>
-      </c>
-      <c r="U69">
-        <v>1.3</v>
-      </c>
-      <c r="V69">
-        <v>9.25</v>
-      </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X69">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Z69">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AA69">
-        <v>2.43</v>
+        <v>4.75</v>
       </c>
       <c r="AB69">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC69">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD69">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AF69">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AG69">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AH69">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AI69">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AJ69" t="s">
         <v>242</v>
@@ -9121,7 +9121,7 @@
         <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
         <v>86</v>
@@ -9148,31 +9148,31 @@
         <v>241</v>
       </c>
       <c r="L70">
-        <v>1.51</v>
+        <v>2.09</v>
       </c>
       <c r="M70">
+        <v>3.12</v>
+      </c>
+      <c r="N70">
         <v>3.75</v>
       </c>
-      <c r="N70">
-        <v>6.17</v>
-      </c>
       <c r="O70">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="P70">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q70">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R70">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S70">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T70">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U70">
         <v>1.3</v>
@@ -9181,40 +9181,40 @@
         <v>8.5</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
         <v>1.08</v>
       </c>
       <c r="Y70">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z70">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AA70">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AB70">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC70">
         <v>1.57</v>
       </c>
       <c r="AD70">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE70">
         <v>1.18</v>
       </c>
       <c r="AF70">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="AG70">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH70">
-        <v>8.9</v>
+        <v>8.75</v>
       </c>
       <c r="AI70">
         <v>1.04</v>
@@ -9237,7 +9237,7 @@
         <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D71" t="s">
         <v>86</v>
@@ -9264,76 +9264,76 @@
         <v>241</v>
       </c>
       <c r="L71">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="M71">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O71">
+        <v>1.67</v>
+      </c>
+      <c r="P71">
+        <v>6.5</v>
+      </c>
+      <c r="Q71">
+        <v>2.75</v>
+      </c>
+      <c r="R71">
+        <v>1.51</v>
+      </c>
+      <c r="S71">
+        <v>2.5</v>
+      </c>
+      <c r="T71">
+        <v>3.3</v>
+      </c>
+      <c r="U71">
+        <v>1.3</v>
+      </c>
+      <c r="V71">
+        <v>9.25</v>
+      </c>
+      <c r="W71">
+        <v>1.05</v>
+      </c>
+      <c r="X71">
+        <v>1.1</v>
+      </c>
+      <c r="Y71">
+        <v>6</v>
+      </c>
+      <c r="Z71">
         <v>1.44</v>
       </c>
-      <c r="P71">
-        <v>12</v>
-      </c>
-      <c r="Q71">
-        <v>2.88</v>
-      </c>
-      <c r="R71">
-        <v>1.28</v>
-      </c>
-      <c r="S71">
-        <v>3.18</v>
-      </c>
-      <c r="T71">
+      <c r="AA71">
+        <v>2.43</v>
+      </c>
+      <c r="AB71">
         <v>2.4</v>
       </c>
-      <c r="U71">
-        <v>1.48</v>
-      </c>
-      <c r="V71">
-        <v>6.1</v>
-      </c>
-      <c r="W71">
+      <c r="AC71">
+        <v>1.5</v>
+      </c>
+      <c r="AD71">
+        <v>4.5</v>
+      </c>
+      <c r="AE71">
         <v>1.13</v>
       </c>
-      <c r="X71">
-        <v>1.04</v>
-      </c>
-      <c r="Y71">
-        <v>11</v>
-      </c>
-      <c r="Z71">
-        <v>1.15</v>
-      </c>
-      <c r="AA71">
-        <v>4.2</v>
-      </c>
-      <c r="AB71">
+      <c r="AF71">
+        <v>2.1</v>
+      </c>
+      <c r="AG71">
         <v>1.67</v>
       </c>
-      <c r="AC71">
-        <v>2.1</v>
-      </c>
-      <c r="AD71">
-        <v>2.63</v>
-      </c>
-      <c r="AE71">
-        <v>1.4</v>
-      </c>
-      <c r="AF71">
-        <v>1.65</v>
-      </c>
-      <c r="AG71">
-        <v>2.05</v>
-      </c>
       <c r="AH71">
-        <v>4.65</v>
+        <v>9</v>
       </c>
       <c r="AI71">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ71" t="s">
         <v>242</v>
@@ -9353,7 +9353,7 @@
         <v>63</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D72" t="s">
         <v>86</v>
@@ -9380,76 +9380,76 @@
         <v>241</v>
       </c>
       <c r="L72">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M72">
-        <v>3.53</v>
+        <v>4.33</v>
       </c>
       <c r="N72">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O72">
         <v>1.67</v>
       </c>
       <c r="P72">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S72">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T72">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U72">
         <v>1.62</v>
       </c>
       <c r="V72">
+        <v>4.33</v>
+      </c>
+      <c r="W72">
+        <v>1.18</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>1.11</v>
+      </c>
+      <c r="AA72">
         <v>5</v>
       </c>
-      <c r="W72">
-        <v>1.17</v>
-      </c>
-      <c r="X72">
-        <v>1.02</v>
-      </c>
-      <c r="Y72">
-        <v>13.5</v>
-      </c>
-      <c r="Z72">
-        <v>1.15</v>
-      </c>
-      <c r="AA72">
-        <v>5.36</v>
-      </c>
       <c r="AB72">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AC72">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AD72">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE72">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF72">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AG72">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH72">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AI72">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AJ72" t="s">
         <v>242</v>
@@ -9585,7 +9585,7 @@
         <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
         <v>86</v>
@@ -9612,76 +9612,76 @@
         <v>241</v>
       </c>
       <c r="L74">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M74">
-        <v>4.33</v>
+        <v>3.53</v>
       </c>
       <c r="N74">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O74">
         <v>1.67</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Q74">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S74">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T74">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U74">
         <v>1.62</v>
       </c>
       <c r="V74">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z74">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AA74">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="AB74">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AC74">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AD74">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE74">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF74">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH74">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="AI74">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ74" t="s">
         <v>242</v>
@@ -9701,7 +9701,7 @@
         <v>64</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D75" t="s">
         <v>86</v>
@@ -9728,76 +9728,76 @@
         <v>241</v>
       </c>
       <c r="L75">
+        <v>1.97</v>
+      </c>
+      <c r="M75">
+        <v>3.01</v>
+      </c>
+      <c r="N75">
+        <v>3.57</v>
+      </c>
+      <c r="O75">
+        <v>1.87</v>
+      </c>
+      <c r="P75">
+        <v>7</v>
+      </c>
+      <c r="Q75">
+        <v>2.3</v>
+      </c>
+      <c r="R75">
+        <v>1.44</v>
+      </c>
+      <c r="S75">
+        <v>2.6</v>
+      </c>
+      <c r="T75">
+        <v>3.34</v>
+      </c>
+      <c r="U75">
+        <v>1.3</v>
+      </c>
+      <c r="V75">
+        <v>10</v>
+      </c>
+      <c r="W75">
+        <v>1.06</v>
+      </c>
+      <c r="X75">
+        <v>1.09</v>
+      </c>
+      <c r="Y75">
+        <v>7.7</v>
+      </c>
+      <c r="Z75">
+        <v>1.48</v>
+      </c>
+      <c r="AA75">
+        <v>2.63</v>
+      </c>
+      <c r="AB75">
+        <v>2.43</v>
+      </c>
+      <c r="AC75">
+        <v>1.53</v>
+      </c>
+      <c r="AD75">
+        <v>4.6</v>
+      </c>
+      <c r="AE75">
+        <v>1.19</v>
+      </c>
+      <c r="AF75">
+        <v>1.93</v>
+      </c>
+      <c r="AG75">
         <v>1.79</v>
       </c>
-      <c r="M75">
-        <v>3.9</v>
-      </c>
-      <c r="N75">
-        <v>3.6</v>
-      </c>
-      <c r="O75">
-        <v>1.8</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>2.05</v>
-      </c>
-      <c r="R75">
-        <v>1.22</v>
-      </c>
-      <c r="S75">
-        <v>3.5</v>
-      </c>
-      <c r="T75">
-        <v>2.05</v>
-      </c>
-      <c r="U75">
-        <v>1.62</v>
-      </c>
-      <c r="V75">
-        <v>4.5</v>
-      </c>
-      <c r="W75">
-        <v>1.17</v>
-      </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>11</v>
-      </c>
-      <c r="Z75">
-        <v>1.13</v>
-      </c>
-      <c r="AA75">
-        <v>4.7</v>
-      </c>
-      <c r="AB75">
-        <v>1.46</v>
-      </c>
-      <c r="AC75">
-        <v>2.45</v>
-      </c>
-      <c r="AD75">
-        <v>2.2</v>
-      </c>
-      <c r="AE75">
-        <v>1.6</v>
-      </c>
-      <c r="AF75">
-        <v>1.45</v>
-      </c>
-      <c r="AG75">
-        <v>2.45</v>
-      </c>
       <c r="AH75">
-        <v>3.5</v>
+        <v>8.75</v>
       </c>
       <c r="AI75">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ75" t="s">
         <v>242</v>
@@ -9817,7 +9817,7 @@
         <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D76" t="s">
         <v>86</v>
@@ -9933,7 +9933,7 @@
         <v>64</v>
       </c>
       <c r="C77" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D77" t="s">
         <v>86</v>
@@ -9960,76 +9960,76 @@
         <v>241</v>
       </c>
       <c r="L77">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="M77">
-        <v>3.01</v>
+        <v>3.9</v>
       </c>
       <c r="N77">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="O77">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="P77">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="R77">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S77">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T77">
-        <v>3.34</v>
+        <v>2.05</v>
       </c>
       <c r="U77">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="V77">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X77">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="Z77">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AA77">
-        <v>2.63</v>
+        <v>4.7</v>
       </c>
       <c r="AB77">
-        <v>2.43</v>
+        <v>1.46</v>
       </c>
       <c r="AC77">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AD77">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="AE77">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AF77">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AG77">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="AH77">
-        <v>8.75</v>
+        <v>3.5</v>
       </c>
       <c r="AI77">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AJ77" t="s">
         <v>242</v>
@@ -10049,16 +10049,16 @@
         <v>65</v>
       </c>
       <c r="C78" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D78" t="s">
         <v>86</v>
       </c>
       <c r="E78" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="F78" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10076,76 +10076,76 @@
         <v>241</v>
       </c>
       <c r="L78">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="S78">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="T78">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="U78">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="V78">
-        <v>11</v>
+        <v>4.33</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="X78">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z78">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="AA78">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="AB78">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="AC78">
-        <v>1.48</v>
+        <v>2.59</v>
       </c>
       <c r="AD78">
-        <v>5.25</v>
+        <v>2.06</v>
       </c>
       <c r="AE78">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="AF78">
-        <v>2.75</v>
+        <v>1.42</v>
       </c>
       <c r="AG78">
-        <v>1.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH78">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="AI78">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="AJ78" t="s">
         <v>242</v>
@@ -10171,10 +10171,10 @@
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10281,16 +10281,16 @@
         <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D80" t="s">
         <v>86</v>
       </c>
       <c r="E80" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="F80" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10308,76 +10308,76 @@
         <v>241</v>
       </c>
       <c r="L80">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="M80">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N80">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O80">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q80">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R80">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="S80">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="T80">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="U80">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z80">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
       <c r="AA80">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="AB80">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="AC80">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="AD80">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="AE80">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AF80">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="AG80">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AH80">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AI80">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ80" t="s">
         <v>242</v>
@@ -10424,40 +10424,40 @@
         <v>241</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P81">
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R81">
         <v>1.22</v>
       </c>
       <c r="S81">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="T81">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U81">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="V81">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -10466,34 +10466,34 @@
         <v>0</v>
       </c>
       <c r="Z81">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AA81">
         <v>4.8</v>
       </c>
       <c r="AB81">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC81">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AD81">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE81">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF81">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AG81">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AH81">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI81">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AJ81" t="s">
         <v>242</v>
@@ -10513,7 +10513,7 @@
         <v>66</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D82" t="s">
         <v>86</v>

--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="250">
   <si>
     <t>Date</t>
   </si>
@@ -280,16 +280,19 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Central Coast II</t>
+    <t>Bucheon 1995</t>
   </si>
   <si>
     <t>Incheon United</t>
@@ -298,114 +301,111 @@
     <t>Ansan Greeners</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
+    <t>Hebei Kungfu</t>
+  </si>
+  <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
-    <t>Hebei Kungfu</t>
+    <t>Brommapojkarna</t>
   </si>
   <si>
     <t>GAIS</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Bryne</t>
   </si>
   <si>
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Gnistan</t>
-  </si>
-  <si>
     <t>Värnamo</t>
   </si>
   <si>
     <t>AIK</t>
   </si>
   <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
     <t>Huracán</t>
   </si>
   <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
     <t>Gimnasia La Plata</t>
   </si>
   <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
   </si>
   <si>
     <t>Argentinos Juniors</t>
   </si>
   <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
     <t>Rosario Central</t>
   </si>
   <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
+    <t>Santiago Morning</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
     <t>Antofagasta</t>
   </si>
   <si>
-    <t>Santiago Morning</t>
-  </si>
-  <si>
     <t>Colón</t>
   </si>
   <si>
@@ -415,30 +415,30 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Arsenal de Sarandí</t>
+  </si>
+  <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
     <t>Deportivo Maipú</t>
   </si>
   <si>
     <t>Alvarado</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Arsenal de Sarandí</t>
-  </si>
-  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
+    <t>Philadelphia Union II</t>
+  </si>
+  <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Philadelphia Union II</t>
-  </si>
-  <si>
     <t>Criciúma</t>
   </si>
   <si>
@@ -454,15 +454,18 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>Caxias</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
     <t>York9 FC</t>
   </si>
   <si>
@@ -472,9 +475,6 @@
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
     <t>Inter Miami II</t>
   </si>
   <si>
@@ -484,24 +484,24 @@
     <t>St. Louis City</t>
   </si>
   <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
+    <t>San Jose Earthquakes II</t>
+  </si>
+  <si>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -511,16 +511,19 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Sydney Olympic</t>
+  </si>
+  <si>
+    <t>St George City FA</t>
+  </si>
+  <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
-    <t>St George City FA</t>
-  </si>
-  <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
-    <t>Sydney Olympic</t>
+    <t>Gimpo Citizen</t>
   </si>
   <si>
     <t>Asan Mugunghwa</t>
@@ -529,114 +532,111 @@
     <t>Seoul E-Land</t>
   </si>
   <si>
-    <t>Gimpo Citizen</t>
-  </si>
-  <si>
     <t>Nanjing City</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
+    <t>Öster</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
     <t>Vålerenga</t>
   </si>
   <si>
     <t>Zhetysu</t>
   </si>
   <si>
+    <t>Haka</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Haka</t>
-  </si>
-  <si>
     <t>Djurgården</t>
   </si>
   <si>
     <t>Degerfors</t>
   </si>
   <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
     <t>Belgrano</t>
   </si>
   <si>
-    <t>Astana</t>
-  </si>
-  <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Independiente</t>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
   </si>
   <si>
     <t>Boca Juniors</t>
   </si>
   <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>Copiapó</t>
-  </si>
-  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
@@ -646,30 +646,30 @@
     <t>Viking</t>
   </si>
   <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
+    <t>New England II</t>
+  </si>
+  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
     <t>San Miguel</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
+    <t>Chattanooga FC</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Chattanooga FC</t>
-  </si>
-  <si>
     <t>Ferroviária</t>
   </si>
   <si>
@@ -685,15 +685,18 @@
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>Concepción</t>
   </si>
   <si>
-    <t>Remo</t>
-  </si>
-  <si>
     <t>Anápolis</t>
   </si>
   <si>
+    <t>Náutico</t>
+  </si>
+  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -703,9 +706,6 @@
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Náutico</t>
-  </si>
-  <si>
     <t>Crown Legacy</t>
   </si>
   <si>
@@ -715,34 +715,55 @@
     <t>Portland Timbers</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Cavalry FC</t>
   </si>
   <si>
     <t>Portland Timbers II</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['44', '75', '90+2']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['7', '69', '75']</t>
+  </si>
+  <si>
+    <t>['40', '17', '90+6', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1245,13 +1266,13 @@
         <v>164</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1260,13 +1281,13 @@
         <v>241</v>
       </c>
       <c r="L2">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M2">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="O2">
         <v>1.71</v>
@@ -1278,43 +1299,43 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
         <v>2.5</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AA2">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AB2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC2">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AD2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -1323,19 +1344,19 @@
         <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH2">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="AI2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AK2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL2" s="3">
         <v>45851</v>
@@ -1361,10 +1382,10 @@
         <v>165</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1376,82 +1397,82 @@
         <v>241</v>
       </c>
       <c r="L3">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="M3">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N3">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD3">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AE3">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AF3">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AK3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AL3" s="3">
         <v>45851.08333333334</v>
@@ -1477,28 +1498,28 @@
         <v>166</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
         <v>241</v>
       </c>
       <c r="L4">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="M4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N4">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
         <v>1.8</v>
@@ -1540,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC4">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1564,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AK4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AL4" s="3">
         <v>45851.08333333334</v>
@@ -1605,16 +1626,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L5">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M5">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>1.64</v>
@@ -1632,7 +1653,7 @@
         <v>3.2</v>
       </c>
       <c r="T5">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
         <v>1.5</v>
@@ -1641,49 +1662,49 @@
         <v>5.5</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA5">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB5">
         <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AE5">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG5">
         <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AI5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL5" s="3">
         <v>45851.08333333334</v>
@@ -1709,97 +1730,97 @@
         <v>168</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="s">
         <v>241</v>
       </c>
       <c r="L6">
-        <v>5.38</v>
+        <v>2.15</v>
       </c>
       <c r="M6">
-        <v>4.72</v>
+        <v>3.78</v>
       </c>
       <c r="N6">
-        <v>1.47</v>
+        <v>2.71</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB6">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC6">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD6">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AE6">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AJ6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AK6" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AL6" s="3">
         <v>45851.08333333334</v>
@@ -1837,25 +1858,25 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L7">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="M7">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="N7">
-        <v>4.63</v>
+        <v>3.09</v>
       </c>
       <c r="O7">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="P7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
         <v>1.44</v>
@@ -1864,10 +1885,10 @@
         <v>2.63</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1879,43 +1900,43 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Z7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AA7">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB7">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD7">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH7">
-        <v>6.95</v>
+        <v>7.7</v>
       </c>
       <c r="AI7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL7" s="3">
         <v>45851.29166666666</v>
@@ -1953,25 +1974,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L8">
-        <v>3.84</v>
+        <v>1.74</v>
       </c>
       <c r="M8">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>4.63</v>
       </c>
       <c r="O8">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="P8">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="R8">
         <v>1.44</v>
@@ -1980,10 +2001,10 @@
         <v>2.63</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1995,43 +2016,43 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z8">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA8">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC8">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD8">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH8">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AI8">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL8" s="3">
         <v>45851.29166666666</v>
@@ -2069,25 +2090,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L9">
-        <v>2.09</v>
+        <v>3.84</v>
       </c>
       <c r="M9">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N9">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2111,43 +2132,43 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AA9">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD9">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AE9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH9">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL9" s="3">
         <v>45851.29166666666</v>
@@ -2185,16 +2206,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L10">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="M10">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="O10">
         <v>1.62</v>
@@ -2212,58 +2233,58 @@
         <v>2.8</v>
       </c>
       <c r="T10">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V10">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AA10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB10">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AC10">
+        <v>1.8</v>
+      </c>
+      <c r="AD10">
+        <v>3.34</v>
+      </c>
+      <c r="AE10">
+        <v>1.25</v>
+      </c>
+      <c r="AF10">
         <v>1.85</v>
       </c>
-      <c r="AD10">
-        <v>3</v>
-      </c>
-      <c r="AE10">
-        <v>1.33</v>
-      </c>
-      <c r="AF10">
-        <v>1.7</v>
-      </c>
       <c r="AG10">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AH10">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AI10">
         <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL10" s="3">
         <v>45851.33333333334</v>
@@ -2301,16 +2322,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L11">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="M11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N11">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="O11">
         <v>1.8</v>
@@ -2322,52 +2343,52 @@
         <v>2.3</v>
       </c>
       <c r="R11">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U11">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V11">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AA11">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB11">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD11">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AH11">
         <v>8.1</v>
@@ -2376,10 +2397,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL11" s="3">
         <v>45851.33333333334</v>
@@ -2393,7 +2414,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>86</v>
@@ -2417,85 +2438,85 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L12">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="M12">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="O12">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="P12">
-        <v>19</v>
+        <v>10.75</v>
       </c>
       <c r="Q12">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
+        <v>2.75</v>
+      </c>
+      <c r="T12">
+        <v>2.95</v>
+      </c>
+      <c r="U12">
+        <v>1.36</v>
+      </c>
+      <c r="V12">
+        <v>7</v>
+      </c>
+      <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.06</v>
+      </c>
+      <c r="Y12">
+        <v>8.5</v>
+      </c>
+      <c r="Z12">
+        <v>1.33</v>
+      </c>
+      <c r="AA12">
+        <v>3</v>
+      </c>
+      <c r="AB12">
+        <v>1.98</v>
+      </c>
+      <c r="AC12">
+        <v>1.7</v>
+      </c>
+      <c r="AD12">
         <v>3.4</v>
       </c>
-      <c r="T12">
-        <v>2.1</v>
-      </c>
-      <c r="U12">
-        <v>1.67</v>
-      </c>
-      <c r="V12">
-        <v>4.8</v>
-      </c>
-      <c r="W12">
-        <v>1.14</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>17</v>
-      </c>
-      <c r="Z12">
-        <v>1.14</v>
-      </c>
-      <c r="AA12">
-        <v>5</v>
-      </c>
-      <c r="AB12">
-        <v>1.5</v>
-      </c>
-      <c r="AC12">
-        <v>2.5</v>
-      </c>
-      <c r="AD12">
-        <v>2.1</v>
-      </c>
       <c r="AE12">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AH12">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AI12">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AJ12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL12" s="3">
         <v>45851.35416666666</v>
@@ -2509,7 +2530,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>86</v>
@@ -2533,85 +2554,85 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L13">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="M13">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N13">
-        <v>4.75</v>
+        <v>1.97</v>
       </c>
       <c r="O13">
+        <v>2.13</v>
+      </c>
+      <c r="P13">
+        <v>19</v>
+      </c>
+      <c r="Q13">
+        <v>1.68</v>
+      </c>
+      <c r="R13">
+        <v>1.23</v>
+      </c>
+      <c r="S13">
+        <v>3.9</v>
+      </c>
+      <c r="T13">
+        <v>2.1</v>
+      </c>
+      <c r="U13">
+        <v>1.65</v>
+      </c>
+      <c r="V13">
+        <v>4.6</v>
+      </c>
+      <c r="W13">
+        <v>1.17</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>17</v>
+      </c>
+      <c r="Z13">
+        <v>1.11</v>
+      </c>
+      <c r="AA13">
+        <v>5</v>
+      </c>
+      <c r="AB13">
+        <v>1.5</v>
+      </c>
+      <c r="AC13">
+        <v>2.45</v>
+      </c>
+      <c r="AD13">
+        <v>2.15</v>
+      </c>
+      <c r="AE13">
+        <v>1.62</v>
+      </c>
+      <c r="AF13">
         <v>1.4</v>
       </c>
-      <c r="P13">
-        <v>10.75</v>
-      </c>
-      <c r="Q13">
-        <v>3.4</v>
-      </c>
-      <c r="R13">
-        <v>1.42</v>
-      </c>
-      <c r="S13">
-        <v>2.6</v>
-      </c>
-      <c r="T13">
-        <v>3.08</v>
-      </c>
-      <c r="U13">
-        <v>1.33</v>
-      </c>
-      <c r="V13">
-        <v>8.9</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>8</v>
-      </c>
-      <c r="Z13">
-        <v>1.32</v>
-      </c>
-      <c r="AA13">
-        <v>3.1</v>
-      </c>
-      <c r="AB13">
-        <v>2.05</v>
-      </c>
-      <c r="AC13">
-        <v>1.7</v>
-      </c>
-      <c r="AD13">
+      <c r="AG13">
+        <v>2.5</v>
+      </c>
+      <c r="AH13">
         <v>3.5</v>
       </c>
-      <c r="AE13">
-        <v>1.25</v>
-      </c>
-      <c r="AF13">
-        <v>1.85</v>
-      </c>
-      <c r="AG13">
-        <v>1.8</v>
-      </c>
-      <c r="AH13">
-        <v>6</v>
-      </c>
       <c r="AI13">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK13" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL13" s="3">
         <v>45851.35416666666</v>
@@ -2649,85 +2670,85 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L14">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="M14">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N14">
-        <v>2.35</v>
+        <v>3.77</v>
       </c>
       <c r="O14">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="P14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q14">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z14">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AA14">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB14">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AC14">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AD14">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AE14">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH14">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI14">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AJ14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL14" s="3">
         <v>45851.375</v>
@@ -2765,85 +2786,85 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L15">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="M15">
+        <v>3.19</v>
+      </c>
+      <c r="N15">
+        <v>2.35</v>
+      </c>
+      <c r="O15">
+        <v>2.1</v>
+      </c>
+      <c r="P15">
+        <v>9</v>
+      </c>
+      <c r="Q15">
+        <v>1.83</v>
+      </c>
+      <c r="R15">
+        <v>1.4</v>
+      </c>
+      <c r="S15">
+        <v>2.75</v>
+      </c>
+      <c r="T15">
+        <v>2.75</v>
+      </c>
+      <c r="U15">
+        <v>1.4</v>
+      </c>
+      <c r="V15">
+        <v>8</v>
+      </c>
+      <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.06</v>
+      </c>
+      <c r="Y15">
+        <v>9</v>
+      </c>
+      <c r="Z15">
+        <v>1.3</v>
+      </c>
+      <c r="AA15">
         <v>3.5</v>
       </c>
-      <c r="N15">
-        <v>3.77</v>
-      </c>
-      <c r="O15">
-        <v>1.44</v>
-      </c>
-      <c r="P15">
-        <v>11</v>
-      </c>
-      <c r="Q15">
-        <v>2.75</v>
-      </c>
-      <c r="R15">
-        <v>1.3</v>
-      </c>
-      <c r="S15">
-        <v>3.4</v>
-      </c>
-      <c r="T15">
-        <v>2.5</v>
-      </c>
-      <c r="U15">
-        <v>1.5</v>
-      </c>
-      <c r="V15">
-        <v>6</v>
-      </c>
-      <c r="W15">
-        <v>1.13</v>
-      </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>11</v>
-      </c>
-      <c r="Z15">
-        <v>1.22</v>
-      </c>
-      <c r="AA15">
-        <v>4.2</v>
-      </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AC15">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AD15">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="AE15">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH15">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI15">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AJ15" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK15" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL15" s="3">
         <v>45851.375</v>
@@ -2881,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L16">
         <v>2.3</v>
@@ -2956,10 +2977,10 @@
         <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK16" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL16" s="3">
         <v>45851.39583333334</v>
@@ -2997,16 +3018,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L17">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="M17">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
         <v>1.64</v>
@@ -3018,64 +3039,64 @@
         <v>2.61</v>
       </c>
       <c r="R17">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T17">
         <v>3.2</v>
       </c>
       <c r="U17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V17">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z17">
         <v>1.4</v>
       </c>
       <c r="AA17">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AB17">
         <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AD17">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AE17">
         <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH17">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AI17">
         <v>1.06</v>
       </c>
       <c r="AJ17" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK17" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL17" s="3">
         <v>45851.41666666666</v>
@@ -3089,7 +3110,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>86</v>
@@ -3113,85 +3134,85 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L18">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="M18">
-        <v>4.3</v>
+        <v>3.59</v>
       </c>
       <c r="N18">
-        <v>6.91</v>
+        <v>2.59</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="P18">
-        <v>9.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="Q18">
-        <v>3.28</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="T18">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="U18">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V18">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z18">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA18">
-        <v>3.4</v>
+        <v>5.19</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC18">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD18">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH18">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AI18">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AJ18" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK18" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL18" s="3">
         <v>45851.41666666666</v>
@@ -3205,7 +3226,7 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>86</v>
@@ -3229,85 +3250,85 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L19">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="M19">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N19">
+        <v>6</v>
+      </c>
+      <c r="O19">
+        <v>1.41</v>
+      </c>
+      <c r="P19">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q19">
+        <v>3.28</v>
+      </c>
+      <c r="R19">
+        <v>1.3</v>
+      </c>
+      <c r="S19">
+        <v>3.25</v>
+      </c>
+      <c r="T19">
+        <v>2.4</v>
+      </c>
+      <c r="U19">
+        <v>1.5</v>
+      </c>
+      <c r="V19">
+        <v>5.7</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>9.1</v>
+      </c>
+      <c r="Z19">
+        <v>1.2</v>
+      </c>
+      <c r="AA19">
+        <v>3.72</v>
+      </c>
+      <c r="AB19">
+        <v>1.77</v>
+      </c>
+      <c r="AC19">
+        <v>1.93</v>
+      </c>
+      <c r="AD19">
         <v>2.8</v>
       </c>
-      <c r="O19">
-        <v>1.67</v>
-      </c>
-      <c r="P19">
-        <v>12.5</v>
-      </c>
-      <c r="Q19">
-        <v>2.2</v>
-      </c>
-      <c r="R19">
-        <v>1.25</v>
-      </c>
-      <c r="S19">
-        <v>3.42</v>
-      </c>
-      <c r="T19">
-        <v>2.36</v>
-      </c>
-      <c r="U19">
-        <v>1.6</v>
-      </c>
-      <c r="V19">
-        <v>4.6</v>
-      </c>
-      <c r="W19">
+      <c r="AE19">
+        <v>1.38</v>
+      </c>
+      <c r="AF19">
+        <v>1.85</v>
+      </c>
+      <c r="AG19">
+        <v>1.83</v>
+      </c>
+      <c r="AH19">
+        <v>5</v>
+      </c>
+      <c r="AI19">
         <v>1.15</v>
       </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
-      <c r="Y19">
-        <v>12</v>
-      </c>
-      <c r="Z19">
-        <v>1.19</v>
-      </c>
-      <c r="AA19">
-        <v>4.65</v>
-      </c>
-      <c r="AB19">
-        <v>1.61</v>
-      </c>
-      <c r="AC19">
-        <v>2.18</v>
-      </c>
-      <c r="AD19">
-        <v>2.5</v>
-      </c>
-      <c r="AE19">
-        <v>1.45</v>
-      </c>
-      <c r="AF19">
-        <v>1.53</v>
-      </c>
-      <c r="AG19">
-        <v>2.45</v>
-      </c>
-      <c r="AH19">
-        <v>4.35</v>
-      </c>
-      <c r="AI19">
-        <v>1.18</v>
-      </c>
       <c r="AJ19" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK19" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL19" s="3">
         <v>45851.41666666666</v>
@@ -3345,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L20">
         <v>3.82</v>
@@ -3420,10 +3441,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL20" s="3">
         <v>45851.47916666666</v>
@@ -3461,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L21">
         <v>1.51</v>
@@ -3536,10 +3557,10 @@
         <v>1.12</v>
       </c>
       <c r="AJ21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK21" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL21" s="3">
         <v>45851.47916666666</v>
@@ -3577,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -3652,10 +3673,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK22" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL22" s="3">
         <v>45851.5</v>
@@ -3669,7 +3690,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -3693,85 +3714,85 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK23" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL23" s="3">
         <v>45851.5</v>
@@ -3809,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3884,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK24" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL24" s="3">
         <v>45851.5</v>
@@ -3925,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -4000,10 +4021,10 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK25" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL25" s="3">
         <v>45851.5</v>
@@ -4041,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -4116,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL26" s="3">
         <v>45851.5</v>
@@ -4133,7 +4154,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
         <v>86</v>
@@ -4157,85 +4178,85 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ27" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK27" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL27" s="3">
         <v>45851.5</v>
@@ -4249,7 +4270,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
         <v>86</v>
@@ -4273,85 +4294,85 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ28" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK28" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL28" s="3">
         <v>45851.5</v>
@@ -4389,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4464,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK29" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL29" s="3">
         <v>45851.5</v>
@@ -4505,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -4580,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK30" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL30" s="3">
         <v>45851.5</v>
@@ -4621,85 +4642,85 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L31">
-        <v>1.42</v>
+        <v>3.5</v>
       </c>
       <c r="M31">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N31">
-        <v>5.8</v>
+        <v>1.87</v>
       </c>
       <c r="O31">
+        <v>2.6</v>
+      </c>
+      <c r="P31">
+        <v>9.25</v>
+      </c>
+      <c r="Q31">
+        <v>1.57</v>
+      </c>
+      <c r="R31">
+        <v>1.36</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="T31">
+        <v>2.75</v>
+      </c>
+      <c r="U31">
+        <v>1.4</v>
+      </c>
+      <c r="V31">
+        <v>7</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.05</v>
+      </c>
+      <c r="Y31">
+        <v>9</v>
+      </c>
+      <c r="Z31">
+        <v>1.3</v>
+      </c>
+      <c r="AA31">
+        <v>3.45</v>
+      </c>
+      <c r="AB31">
+        <v>1.82</v>
+      </c>
+      <c r="AC31">
+        <v>1.88</v>
+      </c>
+      <c r="AD31">
+        <v>3.3</v>
+      </c>
+      <c r="AE31">
         <v>1.33</v>
       </c>
-      <c r="P31">
-        <v>11.5</v>
-      </c>
-      <c r="Q31">
-        <v>3.5</v>
-      </c>
-      <c r="R31">
-        <v>1.3</v>
-      </c>
-      <c r="S31">
-        <v>3.4</v>
-      </c>
-      <c r="T31">
-        <v>2.5</v>
-      </c>
-      <c r="U31">
-        <v>1.5</v>
-      </c>
-      <c r="V31">
-        <v>6</v>
-      </c>
-      <c r="W31">
-        <v>1.13</v>
-      </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
-      <c r="Y31">
-        <v>10</v>
-      </c>
-      <c r="Z31">
-        <v>1.22</v>
-      </c>
-      <c r="AA31">
-        <v>4.2</v>
-      </c>
-      <c r="AB31">
-        <v>1.63</v>
-      </c>
-      <c r="AC31">
-        <v>2.13</v>
-      </c>
-      <c r="AD31">
-        <v>2.8</v>
-      </c>
-      <c r="AE31">
-        <v>1.42</v>
-      </c>
       <c r="AF31">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH31">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AI31">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ31" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK31" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL31" s="3">
         <v>45851.5</v>
@@ -4737,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -4812,10 +4833,10 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK32" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL32" s="3">
         <v>45851.5</v>
@@ -4853,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -4928,10 +4949,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK33" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL33" s="3">
         <v>45851.5</v>
@@ -4969,31 +4990,31 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L34">
-        <v>3.38</v>
+        <v>1.42</v>
       </c>
       <c r="M34">
-        <v>3.27</v>
+        <v>4.1</v>
       </c>
       <c r="N34">
-        <v>1.93</v>
+        <v>5.8</v>
       </c>
       <c r="O34">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="P34">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q34">
-        <v>1.62</v>
+        <v>3.5</v>
       </c>
       <c r="R34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S34">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T34">
         <v>2.5</v>
@@ -5002,40 +5023,40 @@
         <v>1.5</v>
       </c>
       <c r="V34">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA34">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AB34">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AC34">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AD34">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="AE34">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG34">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH34">
         <v>5.25</v>
@@ -5044,10 +5065,10 @@
         <v>1.15</v>
       </c>
       <c r="AJ34" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK34" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL34" s="3">
         <v>45851.5</v>
@@ -5061,7 +5082,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
         <v>86</v>
@@ -5085,85 +5106,85 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK35" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL35" s="3">
         <v>45851.5</v>
@@ -5177,7 +5198,7 @@
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
         <v>86</v>
@@ -5201,85 +5222,85 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L36">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH36">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK36" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL36" s="3">
         <v>45851.5</v>
@@ -5317,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -5392,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK37" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL37" s="3">
         <v>45851.5</v>
@@ -5409,7 +5430,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
         <v>86</v>
@@ -5433,85 +5454,85 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ38" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK38" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL38" s="3">
         <v>45851.5</v>
@@ -5549,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -5624,10 +5645,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK39" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL39" s="3">
         <v>45851.5</v>
@@ -5665,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -5740,10 +5761,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK40" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL40" s="3">
         <v>45851.5</v>
@@ -5781,16 +5802,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L41">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="M41">
-        <v>3.9</v>
+        <v>3.57</v>
       </c>
       <c r="N41">
-        <v>4.1</v>
+        <v>3.23</v>
       </c>
       <c r="O41">
         <v>1.5</v>
@@ -5805,13 +5826,13 @@
         <v>1.29</v>
       </c>
       <c r="S41">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T41">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U41">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V41">
         <v>5.5</v>
@@ -5823,43 +5844,43 @@
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z41">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AA41">
         <v>4.4</v>
       </c>
       <c r="AB41">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC41">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AD41">
         <v>2.5</v>
       </c>
       <c r="AE41">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH41">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI41">
         <v>1.14</v>
       </c>
       <c r="AJ41" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK41" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL41" s="3">
         <v>45851.52083333334</v>
@@ -5873,7 +5894,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
         <v>86</v>
@@ -5897,85 +5918,85 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L42">
-        <v>1.56</v>
+        <v>3.03</v>
       </c>
       <c r="M42">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="N42">
-        <v>4.3</v>
+        <v>2.11</v>
       </c>
       <c r="O42">
+        <v>2.3</v>
+      </c>
+      <c r="P42">
+        <v>7.8</v>
+      </c>
+      <c r="Q42">
+        <v>1.81</v>
+      </c>
+      <c r="R42">
         <v>1.44</v>
       </c>
-      <c r="P42">
-        <v>11</v>
-      </c>
-      <c r="Q42">
-        <v>2.88</v>
-      </c>
-      <c r="R42">
-        <v>1.3</v>
-      </c>
       <c r="S42">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y42">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z42">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AA42">
-        <v>4.33</v>
+        <v>2.89</v>
       </c>
       <c r="AB42">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.13</v>
+        <v>1.57</v>
       </c>
       <c r="AD42">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="AE42">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="AF42">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH42">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AI42">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AJ42" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK42" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL42" s="3">
         <v>45851.5625</v>
@@ -5989,7 +6010,7 @@
         <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
         <v>86</v>
@@ -6013,85 +6034,85 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L43">
-        <v>2.32</v>
+        <v>1.56</v>
       </c>
       <c r="M43">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N43">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O43">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="P43">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="Q43">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S43">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="T43">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z43">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA43">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB43">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AC43">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AD43">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AE43">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF43">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH43">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AI43">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AJ43" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK43" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL43" s="3">
         <v>45851.5625</v>
@@ -6129,85 +6150,85 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L44">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="M44">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N44">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="O44">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="P44">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="Q44">
-        <v>1.81</v>
+        <v>2.61</v>
       </c>
       <c r="R44">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S44">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T44">
+        <v>2.8</v>
+      </c>
+      <c r="U44">
+        <v>1.38</v>
+      </c>
+      <c r="V44">
+        <v>6.6</v>
+      </c>
+      <c r="W44">
+        <v>1.09</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>10</v>
+      </c>
+      <c r="Z44">
+        <v>1.28</v>
+      </c>
+      <c r="AA44">
+        <v>3.14</v>
+      </c>
+      <c r="AB44">
+        <v>1.96</v>
+      </c>
+      <c r="AC44">
+        <v>1.74</v>
+      </c>
+      <c r="AD44">
         <v>3</v>
       </c>
-      <c r="U44">
-        <v>1.34</v>
-      </c>
-      <c r="V44">
-        <v>8</v>
-      </c>
-      <c r="W44">
-        <v>1.06</v>
-      </c>
-      <c r="X44">
-        <v>1.05</v>
-      </c>
-      <c r="Y44">
-        <v>8</v>
-      </c>
-      <c r="Z44">
+      <c r="AE44">
         <v>1.33</v>
       </c>
-      <c r="AA44">
-        <v>2.83</v>
-      </c>
-      <c r="AB44">
-        <v>2.1</v>
-      </c>
-      <c r="AC44">
-        <v>1.65</v>
-      </c>
-      <c r="AD44">
-        <v>3.8</v>
-      </c>
-      <c r="AE44">
-        <v>1.19</v>
-      </c>
       <c r="AF44">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AG44">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AH44">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AI44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ44" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK44" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL44" s="3">
         <v>45851.5625</v>
@@ -6245,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L45">
         <v>1.65</v>
@@ -6260,7 +6281,7 @@
         <v>1.5</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -6269,7 +6290,7 @@
         <v>1.53</v>
       </c>
       <c r="S45">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="T45">
         <v>3.4</v>
@@ -6293,37 +6314,37 @@
         <v>1.53</v>
       </c>
       <c r="AA45">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB45">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AC45">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD45">
         <v>5</v>
       </c>
       <c r="AE45">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AG45">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AH45">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ45" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK45" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL45" s="3">
         <v>45851.56944444445</v>
@@ -6361,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L46">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="M46">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="N46">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O46">
         <v>1.36</v>
@@ -6382,64 +6403,64 @@
         <v>4.5</v>
       </c>
       <c r="R46">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S46">
         <v>2.5</v>
       </c>
       <c r="T46">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V46">
         <v>8.5</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
         <v>1.1</v>
       </c>
       <c r="Y46">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="Z46">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AA46">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AB46">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
+        <v>1.47</v>
+      </c>
+      <c r="AD46">
+        <v>4.6</v>
+      </c>
+      <c r="AE46">
+        <v>1.11</v>
+      </c>
+      <c r="AF46">
+        <v>2.57</v>
+      </c>
+      <c r="AG46">
         <v>1.53</v>
       </c>
-      <c r="AD46">
-        <v>4.7</v>
-      </c>
-      <c r="AE46">
-        <v>1.12</v>
-      </c>
-      <c r="AF46">
-        <v>2.4</v>
-      </c>
-      <c r="AG46">
-        <v>1.5</v>
-      </c>
       <c r="AH46">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AI46">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ46" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK46" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL46" s="3">
         <v>45851.58333333334</v>
@@ -6477,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L47">
         <v>2.4</v>
@@ -6552,10 +6573,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ47" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK47" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL47" s="3">
         <v>45851.59375</v>
@@ -6575,10 +6596,10 @@
         <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F48" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -6593,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L48">
         <v>4</v>
@@ -6668,10 +6689,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ48" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK48" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL48" s="3">
         <v>45851.59375</v>
@@ -6709,85 +6730,85 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L49">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="M49">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="N49">
-        <v>3.7</v>
+        <v>2.67</v>
       </c>
       <c r="O49">
+        <v>2.5</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>1.91</v>
+      </c>
+      <c r="R49">
         <v>1.67</v>
       </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>2.88</v>
-      </c>
-      <c r="R49">
-        <v>1.64</v>
-      </c>
       <c r="S49">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T49">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V49">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y49">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z49">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA49">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB49">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="AC49">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AD49">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AE49">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
         <v>2.25</v>
       </c>
       <c r="AG49">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH49">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ49" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK49" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL49" s="3">
         <v>45851.625</v>
@@ -6801,7 +6822,7 @@
         <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
         <v>86</v>
@@ -6825,85 +6846,85 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L50">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="M50">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="P50">
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC50">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD50">
-        <v>6.25</v>
+        <v>2.25</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="AF50">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH50">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AI50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK50" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL50" s="3">
         <v>45851.625</v>
@@ -6917,7 +6938,7 @@
         <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
         <v>86</v>
@@ -6941,85 +6962,85 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L51">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="M51">
+        <v>2.92</v>
+      </c>
+      <c r="N51">
+        <v>4.1</v>
+      </c>
+      <c r="O51">
+        <v>1.67</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>2.88</v>
+      </c>
+      <c r="R51">
+        <v>1.63</v>
+      </c>
+      <c r="S51">
+        <v>2.24</v>
+      </c>
+      <c r="T51">
         <v>3.75</v>
       </c>
-      <c r="N51">
-        <v>3</v>
-      </c>
-      <c r="O51">
-        <v>1.62</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
+      <c r="U51">
+        <v>1.18</v>
+      </c>
+      <c r="V51">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W51">
+        <v>1.03</v>
+      </c>
+      <c r="X51">
+        <v>1.12</v>
+      </c>
+      <c r="Y51">
+        <v>5</v>
+      </c>
+      <c r="Z51">
+        <v>1.53</v>
+      </c>
+      <c r="AA51">
+        <v>2.25</v>
+      </c>
+      <c r="AB51">
+        <v>2.89</v>
+      </c>
+      <c r="AC51">
+        <v>1.36</v>
+      </c>
+      <c r="AD51">
+        <v>5.5</v>
+      </c>
+      <c r="AE51">
+        <v>1.09</v>
+      </c>
+      <c r="AF51">
         <v>2.3</v>
       </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
-      </c>
-      <c r="AB51">
-        <v>1.53</v>
-      </c>
-      <c r="AC51">
-        <v>2.38</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51">
-        <v>0</v>
-      </c>
-      <c r="AF51">
-        <v>0</v>
-      </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH51">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ51" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK51" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL51" s="3">
         <v>45851.625</v>
@@ -7057,40 +7078,40 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L52">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="M52">
         <v>2.61</v>
       </c>
       <c r="N52">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="O52">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R52">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="S52">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="T52">
         <v>4</v>
       </c>
       <c r="U52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V52">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="W52">
         <v>1.01</v>
@@ -7099,43 +7120,43 @@
         <v>1.14</v>
       </c>
       <c r="Y52">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Z52">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA52">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AC52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD52">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AG52">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH52">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ52" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK52" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL52" s="3">
         <v>45851.625</v>
@@ -7173,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L53">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="M53">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="N53">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="O53">
         <v>2</v>
@@ -7194,16 +7215,16 @@
         <v>2.5</v>
       </c>
       <c r="R53">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S53">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="T53">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V53">
         <v>10</v>
@@ -7212,46 +7233,46 @@
         <v>1.02</v>
       </c>
       <c r="X53">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y53">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="Z53">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AA53">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB53">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="AC53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD53">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AG53">
         <v>1.53</v>
       </c>
       <c r="AH53">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AI53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ53" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK53" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL53" s="3">
         <v>45851.64583333334</v>
@@ -7289,16 +7310,16 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L54">
         <v>2.14</v>
       </c>
       <c r="M54">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="N54">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
       <c r="O54">
         <v>1.8</v>
@@ -7310,64 +7331,64 @@
         <v>2.75</v>
       </c>
       <c r="R54">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S54">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="T54">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="U54">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V54">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="W54">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
+        <v>1.1</v>
+      </c>
+      <c r="Y54">
+        <v>5</v>
+      </c>
+      <c r="Z54">
+        <v>1.65</v>
+      </c>
+      <c r="AA54">
+        <v>2.05</v>
+      </c>
+      <c r="AB54">
+        <v>2.77</v>
+      </c>
+      <c r="AC54">
+        <v>1.39</v>
+      </c>
+      <c r="AD54">
+        <v>5.25</v>
+      </c>
+      <c r="AE54">
         <v>1.14</v>
-      </c>
-      <c r="Y54">
-        <v>5.5</v>
-      </c>
-      <c r="Z54">
-        <v>1.52</v>
-      </c>
-      <c r="AA54">
-        <v>2.35</v>
-      </c>
-      <c r="AB54">
-        <v>2.7</v>
-      </c>
-      <c r="AC54">
-        <v>1.4</v>
-      </c>
-      <c r="AD54">
-        <v>5.7</v>
-      </c>
-      <c r="AE54">
-        <v>1.13</v>
       </c>
       <c r="AF54">
         <v>2.2</v>
       </c>
       <c r="AG54">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH54">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ54" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK54" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL54" s="3">
         <v>45851.65625</v>
@@ -7381,7 +7402,7 @@
         <v>56</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D55" t="s">
         <v>86</v>
@@ -7405,85 +7426,85 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="M55">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N55">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="O55">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="P55">
-        <v>7</v>
+        <v>18.75</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R55">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S55">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="T55">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="U55">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="V55">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="Z55">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AA55">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="AB55">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AC55">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="AD55">
+        <v>2.2</v>
+      </c>
+      <c r="AE55">
+        <v>1.61</v>
+      </c>
+      <c r="AF55">
+        <v>1.63</v>
+      </c>
+      <c r="AG55">
+        <v>2.1</v>
+      </c>
+      <c r="AH55">
         <v>3.5</v>
       </c>
-      <c r="AE55">
+      <c r="AI55">
         <v>1.22</v>
       </c>
-      <c r="AF55">
-        <v>1.83</v>
-      </c>
-      <c r="AG55">
-        <v>1.87</v>
-      </c>
-      <c r="AH55">
-        <v>6.75</v>
-      </c>
-      <c r="AI55">
-        <v>1.04</v>
-      </c>
       <c r="AJ55" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK55" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL55" s="3">
         <v>45851.66666666666</v>
@@ -7497,7 +7518,7 @@
         <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D56" t="s">
         <v>86</v>
@@ -7521,85 +7542,85 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L56">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="M56">
-        <v>3.75</v>
+        <v>3.12</v>
       </c>
       <c r="N56">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="O56">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q56">
+        <v>2.25</v>
+      </c>
+      <c r="R56">
+        <v>1.42</v>
+      </c>
+      <c r="S56">
+        <v>2.8</v>
+      </c>
+      <c r="T56">
+        <v>2.9</v>
+      </c>
+      <c r="U56">
+        <v>1.36</v>
+      </c>
+      <c r="V56">
+        <v>7.5</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>8.5</v>
+      </c>
+      <c r="Z56">
+        <v>1.32</v>
+      </c>
+      <c r="AA56">
         <v>3.1</v>
       </c>
-      <c r="R56">
-        <v>1.25</v>
-      </c>
-      <c r="S56">
-        <v>3.6</v>
-      </c>
-      <c r="T56">
-        <v>2.1</v>
-      </c>
-      <c r="U56">
-        <v>1.65</v>
-      </c>
-      <c r="V56">
-        <v>4.5</v>
-      </c>
-      <c r="W56">
-        <v>1.17</v>
-      </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="Y56">
-        <v>12</v>
-      </c>
-      <c r="Z56">
-        <v>1.15</v>
-      </c>
-      <c r="AA56">
-        <v>5</v>
-      </c>
       <c r="AB56">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AC56">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD56">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE56">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AF56">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG56">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH56">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="AI56">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ56" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK56" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL56" s="3">
         <v>45851.66666666666</v>
@@ -7637,16 +7658,16 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L57">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="M57">
-        <v>3.44</v>
+        <v>2.97</v>
       </c>
       <c r="N57">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="O57">
         <v>1.5</v>
@@ -7661,40 +7682,40 @@
         <v>1.53</v>
       </c>
       <c r="S57">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="T57">
         <v>3.4</v>
       </c>
       <c r="U57">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V57">
         <v>10</v>
       </c>
       <c r="W57">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X57">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y57">
         <v>6.5</v>
       </c>
       <c r="Z57">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AA57">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB57">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD57">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AE57">
         <v>1.17</v>
@@ -7703,19 +7724,19 @@
         <v>2.2</v>
       </c>
       <c r="AG57">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH57">
         <v>11</v>
       </c>
       <c r="AI57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ57" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK57" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL57" s="3">
         <v>45851.66666666666</v>
@@ -7735,10 +7756,10 @@
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7753,37 +7774,37 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L58">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M58">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="O58">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P58">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q58">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="R58">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S58">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T58">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U58">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V58">
         <v>11</v>
@@ -7792,34 +7813,34 @@
         <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y58">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Z58">
+        <v>1.5</v>
+      </c>
+      <c r="AA58">
+        <v>2.38</v>
+      </c>
+      <c r="AB58">
+        <v>2.6</v>
+      </c>
+      <c r="AC58">
         <v>1.48</v>
       </c>
-      <c r="AA58">
-        <v>2.6</v>
-      </c>
-      <c r="AB58">
-        <v>2.5</v>
-      </c>
-      <c r="AC58">
-        <v>1.5</v>
-      </c>
       <c r="AD58">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG58">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH58">
         <v>9.5</v>
@@ -7828,10 +7849,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ58" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK58" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL58" s="3">
         <v>45851.6875</v>
@@ -7845,16 +7866,16 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D59" t="s">
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="F59" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -7869,85 +7890,85 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L59">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="M59">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="N59">
-        <v>4.27</v>
+        <v>4.75</v>
       </c>
       <c r="O59">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P59">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q59">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R59">
         <v>1.53</v>
       </c>
       <c r="S59">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T59">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U59">
         <v>1.29</v>
       </c>
       <c r="V59">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W59">
         <v>1.05</v>
       </c>
       <c r="X59">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y59">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="Z59">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA59">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AB59">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC59">
         <v>1.5</v>
       </c>
       <c r="AD59">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE59">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF59">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG59">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH59">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI59">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ59" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK59" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL59" s="3">
         <v>45851.6875</v>
@@ -7967,10 +7988,10 @@
         <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -7985,85 +8006,85 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L60">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="M60">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="N60">
-        <v>3.29</v>
+        <v>4.1</v>
       </c>
       <c r="O60">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="P60">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q60">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R60">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S60">
         <v>2.45</v>
       </c>
       <c r="T60">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V60">
         <v>9</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z60">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AA60">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AB60">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC60">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AD60">
-        <v>4.33</v>
+        <v>5.05</v>
       </c>
       <c r="AE60">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF60">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG60">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH60">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AI60">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ60" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK60" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL60" s="3">
         <v>45851.6875</v>
@@ -8077,16 +8098,16 @@
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D61" t="s">
         <v>86</v>
       </c>
       <c r="E61" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="F61" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8101,85 +8122,85 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L61">
+        <v>2.24</v>
+      </c>
+      <c r="M61">
+        <v>3.02</v>
+      </c>
+      <c r="N61">
+        <v>3.11</v>
+      </c>
+      <c r="O61">
+        <v>1.91</v>
+      </c>
+      <c r="P61">
+        <v>7.4</v>
+      </c>
+      <c r="Q61">
+        <v>2.25</v>
+      </c>
+      <c r="R61">
+        <v>1.55</v>
+      </c>
+      <c r="S61">
         <v>2.4</v>
       </c>
-      <c r="M61">
-        <v>3</v>
-      </c>
-      <c r="N61">
-        <v>3.25</v>
-      </c>
-      <c r="O61">
-        <v>1.83</v>
-      </c>
-      <c r="P61">
-        <v>6</v>
-      </c>
-      <c r="Q61">
-        <v>2.4</v>
-      </c>
-      <c r="R61">
-        <v>1.57</v>
-      </c>
-      <c r="S61">
-        <v>2.25</v>
-      </c>
       <c r="T61">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V61">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W61">
         <v>1.05</v>
       </c>
       <c r="X61">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y61">
-        <v>6.25</v>
+        <v>6.55</v>
       </c>
       <c r="Z61">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA61">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB61">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AC61">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD61">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE61">
         <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH61">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI61">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ61" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK61" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL61" s="3">
         <v>45851.6875</v>
@@ -8217,22 +8238,22 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L62">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M62">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N62">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="O62">
         <v>2</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q62">
         <v>1.8</v>
@@ -8241,7 +8262,7 @@
         <v>1.22</v>
       </c>
       <c r="S62">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T62">
         <v>2.1</v>
@@ -8256,10 +8277,10 @@
         <v>1.18</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z62">
         <v>1.11</v>
@@ -8268,34 +8289,34 @@
         <v>5.5</v>
       </c>
       <c r="AB62">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC62">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD62">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AE62">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AF62">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG62">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AH62">
         <v>3.28</v>
       </c>
       <c r="AI62">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AJ62" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK62" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL62" s="3">
         <v>45851.70833333334</v>
@@ -8333,16 +8354,16 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L63">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="N63">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="O63">
         <v>1.67</v>
@@ -8357,43 +8378,43 @@
         <v>1.44</v>
       </c>
       <c r="S63">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="T63">
+        <v>3.24</v>
+      </c>
+      <c r="U63">
+        <v>1.32</v>
+      </c>
+      <c r="V63">
+        <v>8.5</v>
+      </c>
+      <c r="W63">
+        <v>1.07</v>
+      </c>
+      <c r="X63">
+        <v>1.07</v>
+      </c>
+      <c r="Y63">
+        <v>7</v>
+      </c>
+      <c r="Z63">
+        <v>1.4</v>
+      </c>
+      <c r="AA63">
         <v>3.1</v>
       </c>
-      <c r="U63">
-        <v>1.3</v>
-      </c>
-      <c r="V63">
-        <v>6.8</v>
-      </c>
-      <c r="W63">
-        <v>1.05</v>
-      </c>
-      <c r="X63">
-        <v>1.08</v>
-      </c>
-      <c r="Y63">
-        <v>7.5</v>
-      </c>
-      <c r="Z63">
-        <v>1.35</v>
-      </c>
-      <c r="AA63">
-        <v>2.8</v>
-      </c>
       <c r="AB63">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC63">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD63">
         <v>4.2</v>
       </c>
       <c r="AE63">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF63">
         <v>1.95</v>
@@ -8402,16 +8423,16 @@
         <v>1.75</v>
       </c>
       <c r="AH63">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AJ63" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK63" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL63" s="3">
         <v>45851.75</v>
@@ -8425,7 +8446,7 @@
         <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D64" t="s">
         <v>86</v>
@@ -8449,85 +8470,85 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L64">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M64">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N64">
-        <v>2.7</v>
+        <v>3.23</v>
       </c>
       <c r="O64">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="P64">
-        <v>8.9</v>
+        <v>6.75</v>
       </c>
       <c r="Q64">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R64">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S64">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="T64">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="U64">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V64">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="W64">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
+        <v>1.05</v>
+      </c>
+      <c r="Y64">
+        <v>7.5</v>
+      </c>
+      <c r="Z64">
+        <v>1.44</v>
+      </c>
+      <c r="AA64">
+        <v>2.75</v>
+      </c>
+      <c r="AB64">
+        <v>2.25</v>
+      </c>
+      <c r="AC64">
+        <v>1.53</v>
+      </c>
+      <c r="AD64">
+        <v>4.33</v>
+      </c>
+      <c r="AE64">
+        <v>1.16</v>
+      </c>
+      <c r="AF64">
+        <v>2.02</v>
+      </c>
+      <c r="AG64">
+        <v>1.7</v>
+      </c>
+      <c r="AH64">
+        <v>8.5</v>
+      </c>
+      <c r="AI64">
         <v>1.06</v>
       </c>
-      <c r="Y64">
-        <v>9</v>
-      </c>
-      <c r="Z64">
-        <v>1.33</v>
-      </c>
-      <c r="AA64">
-        <v>3.2</v>
-      </c>
-      <c r="AB64">
-        <v>2.07</v>
-      </c>
-      <c r="AC64">
-        <v>1.75</v>
-      </c>
-      <c r="AD64">
-        <v>3.5</v>
-      </c>
-      <c r="AE64">
-        <v>1.25</v>
-      </c>
-      <c r="AF64">
-        <v>1.75</v>
-      </c>
-      <c r="AG64">
-        <v>1.95</v>
-      </c>
-      <c r="AH64">
-        <v>6</v>
-      </c>
-      <c r="AI64">
-        <v>1.08</v>
-      </c>
       <c r="AJ64" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK64" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL64" s="3">
         <v>45851.77083333334</v>
@@ -8541,7 +8562,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D65" t="s">
         <v>86</v>
@@ -8565,85 +8586,85 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L65">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="M65">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="N65">
-        <v>4.02</v>
+        <v>2.8</v>
       </c>
       <c r="O65">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="P65">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="Q65">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="R65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S65">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T65">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U65">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V65">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="W65">
         <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Z65">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AA65">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB65">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AC65">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AD65">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG65">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH65">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AI65">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AJ65" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK65" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL65" s="3">
         <v>45851.77083333334</v>
@@ -8663,10 +8684,10 @@
         <v>86</v>
       </c>
       <c r="E66" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F66" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -8681,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L66">
         <v>2.15</v>
@@ -8756,10 +8777,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ66" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK66" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL66" s="3">
         <v>45851.78125</v>
@@ -8797,16 +8818,16 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L67">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M67">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="N67">
-        <v>6.17</v>
+        <v>6.6</v>
       </c>
       <c r="O67">
         <v>1.36</v>
@@ -8827,31 +8848,31 @@
         <v>3.2</v>
       </c>
       <c r="U67">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V67">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W67">
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z67">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AA67">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AB67">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AC67">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD67">
         <v>4.2</v>
@@ -8860,22 +8881,22 @@
         <v>1.18</v>
       </c>
       <c r="AF67">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG67">
         <v>1.5</v>
       </c>
       <c r="AH67">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI67">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ67" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK67" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL67" s="3">
         <v>45851.79166666666</v>
@@ -8889,7 +8910,7 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
         <v>86</v>
@@ -8913,85 +8934,85 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L68">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="M68">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="N68">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O68">
+        <v>1.67</v>
+      </c>
+      <c r="P68">
+        <v>6.5</v>
+      </c>
+      <c r="Q68">
+        <v>2.75</v>
+      </c>
+      <c r="R68">
         <v>1.44</v>
       </c>
-      <c r="P68">
-        <v>12</v>
-      </c>
-      <c r="Q68">
-        <v>2.88</v>
-      </c>
-      <c r="R68">
-        <v>1.28</v>
-      </c>
       <c r="S68">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="T68">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="U68">
+        <v>1.3</v>
+      </c>
+      <c r="V68">
+        <v>9.25</v>
+      </c>
+      <c r="W68">
+        <v>1.05</v>
+      </c>
+      <c r="X68">
+        <v>1.1</v>
+      </c>
+      <c r="Y68">
+        <v>6.5</v>
+      </c>
+      <c r="Z68">
+        <v>1.44</v>
+      </c>
+      <c r="AA68">
+        <v>2.43</v>
+      </c>
+      <c r="AB68">
+        <v>2.37</v>
+      </c>
+      <c r="AC68">
         <v>1.48</v>
       </c>
-      <c r="V68">
-        <v>6.1</v>
-      </c>
-      <c r="W68">
+      <c r="AD68">
+        <v>4.5</v>
+      </c>
+      <c r="AE68">
         <v>1.13</v>
       </c>
-      <c r="X68">
-        <v>1.04</v>
-      </c>
-      <c r="Y68">
-        <v>11</v>
-      </c>
-      <c r="Z68">
-        <v>1.15</v>
-      </c>
-      <c r="AA68">
-        <v>4.2</v>
-      </c>
-      <c r="AB68">
+      <c r="AF68">
+        <v>2</v>
+      </c>
+      <c r="AG68">
         <v>1.67</v>
       </c>
-      <c r="AC68">
-        <v>2.1</v>
-      </c>
-      <c r="AD68">
-        <v>2.63</v>
-      </c>
-      <c r="AE68">
-        <v>1.4</v>
-      </c>
-      <c r="AF68">
-        <v>1.65</v>
-      </c>
-      <c r="AG68">
-        <v>2.05</v>
-      </c>
       <c r="AH68">
-        <v>4.65</v>
+        <v>9</v>
       </c>
       <c r="AI68">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ68" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK68" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL68" s="3">
         <v>45851.79166666666</v>
@@ -9005,7 +9026,7 @@
         <v>62</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D69" t="s">
         <v>86</v>
@@ -9029,85 +9050,85 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L69">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="M69">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N69">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O69">
+        <v>1.44</v>
+      </c>
+      <c r="P69">
+        <v>12</v>
+      </c>
+      <c r="Q69">
+        <v>2.88</v>
+      </c>
+      <c r="R69">
+        <v>1.3</v>
+      </c>
+      <c r="S69">
+        <v>3.3</v>
+      </c>
+      <c r="T69">
+        <v>2.38</v>
+      </c>
+      <c r="U69">
         <v>1.53</v>
       </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>2.5</v>
-      </c>
-      <c r="R69">
-        <v>1.22</v>
-      </c>
-      <c r="S69">
-        <v>3.5</v>
-      </c>
-      <c r="T69">
+      <c r="V69">
+        <v>5</v>
+      </c>
+      <c r="W69">
+        <v>1.13</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
+        <v>13</v>
+      </c>
+      <c r="Z69">
+        <v>1.2</v>
+      </c>
+      <c r="AA69">
+        <v>4</v>
+      </c>
+      <c r="AB69">
+        <v>1.6</v>
+      </c>
+      <c r="AC69">
         <v>2.1</v>
       </c>
-      <c r="U69">
-        <v>1.6</v>
-      </c>
-      <c r="V69">
-        <v>4.5</v>
-      </c>
-      <c r="W69">
-        <v>1.17</v>
-      </c>
-      <c r="X69">
-        <v>1</v>
-      </c>
-      <c r="Y69">
-        <v>12</v>
-      </c>
-      <c r="Z69">
-        <v>1.14</v>
-      </c>
-      <c r="AA69">
-        <v>4.75</v>
-      </c>
-      <c r="AB69">
-        <v>1.5</v>
-      </c>
-      <c r="AC69">
-        <v>2.3</v>
-      </c>
       <c r="AD69">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE69">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AF69">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AG69">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH69">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AI69">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ69" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK69" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL69" s="3">
         <v>45851.79166666666</v>
@@ -9121,7 +9142,7 @@
         <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D70" t="s">
         <v>86</v>
@@ -9145,85 +9166,85 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L70">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="M70">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="N70">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O70">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P70">
-        <v>6.75</v>
+        <v>23</v>
       </c>
       <c r="Q70">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R70">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S70">
+        <v>3.5</v>
+      </c>
+      <c r="T70">
+        <v>2.1</v>
+      </c>
+      <c r="U70">
+        <v>1.6</v>
+      </c>
+      <c r="V70">
+        <v>4.5</v>
+      </c>
+      <c r="W70">
+        <v>1.17</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="Y70">
+        <v>12</v>
+      </c>
+      <c r="Z70">
+        <v>1.14</v>
+      </c>
+      <c r="AA70">
+        <v>4.5</v>
+      </c>
+      <c r="AB70">
+        <v>1.45</v>
+      </c>
+      <c r="AC70">
+        <v>2.41</v>
+      </c>
+      <c r="AD70">
+        <v>2.25</v>
+      </c>
+      <c r="AE70">
+        <v>1.58</v>
+      </c>
+      <c r="AF70">
+        <v>1.42</v>
+      </c>
+      <c r="AG70">
         <v>2.5</v>
       </c>
-      <c r="T70">
-        <v>3.3</v>
-      </c>
-      <c r="U70">
-        <v>1.3</v>
-      </c>
-      <c r="V70">
-        <v>8.5</v>
-      </c>
-      <c r="W70">
-        <v>1.05</v>
-      </c>
-      <c r="X70">
-        <v>1.08</v>
-      </c>
-      <c r="Y70">
-        <v>6.5</v>
-      </c>
-      <c r="Z70">
-        <v>1.42</v>
-      </c>
-      <c r="AA70">
-        <v>2.62</v>
-      </c>
-      <c r="AB70">
-        <v>2.4</v>
-      </c>
-      <c r="AC70">
-        <v>1.57</v>
-      </c>
-      <c r="AD70">
-        <v>4.33</v>
-      </c>
-      <c r="AE70">
-        <v>1.18</v>
-      </c>
-      <c r="AF70">
-        <v>1.93</v>
-      </c>
-      <c r="AG70">
-        <v>1.75</v>
-      </c>
       <c r="AH70">
-        <v>8.75</v>
+        <v>3.6</v>
       </c>
       <c r="AI70">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ70" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK70" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL70" s="3">
         <v>45851.79166666666</v>
@@ -9237,7 +9258,7 @@
         <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
         <v>86</v>
@@ -9261,85 +9282,85 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L71">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="M71">
-        <v>2.98</v>
+        <v>3.07</v>
       </c>
       <c r="N71">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="O71">
         <v>1.67</v>
       </c>
       <c r="P71">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R71">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S71">
+        <v>2.49</v>
+      </c>
+      <c r="T71">
+        <v>3.5</v>
+      </c>
+      <c r="U71">
+        <v>1.28</v>
+      </c>
+      <c r="V71">
+        <v>8</v>
+      </c>
+      <c r="W71">
+        <v>1.03</v>
+      </c>
+      <c r="X71">
+        <v>1.04</v>
+      </c>
+      <c r="Y71">
+        <v>6.9</v>
+      </c>
+      <c r="Z71">
+        <v>1.54</v>
+      </c>
+      <c r="AA71">
+        <v>2.6</v>
+      </c>
+      <c r="AB71">
         <v>2.5</v>
-      </c>
-      <c r="T71">
-        <v>3.3</v>
-      </c>
-      <c r="U71">
-        <v>1.3</v>
-      </c>
-      <c r="V71">
-        <v>9.25</v>
-      </c>
-      <c r="W71">
-        <v>1.05</v>
-      </c>
-      <c r="X71">
-        <v>1.1</v>
-      </c>
-      <c r="Y71">
-        <v>6</v>
-      </c>
-      <c r="Z71">
-        <v>1.44</v>
-      </c>
-      <c r="AA71">
-        <v>2.43</v>
-      </c>
-      <c r="AB71">
-        <v>2.4</v>
       </c>
       <c r="AC71">
         <v>1.5</v>
       </c>
       <c r="AD71">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG71">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH71">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI71">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ71" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK71" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL71" s="3">
         <v>45851.79166666666</v>
@@ -9377,7 +9398,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L72">
         <v>2.05</v>
@@ -9392,7 +9413,7 @@
         <v>1.67</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -9404,10 +9425,10 @@
         <v>3.6</v>
       </c>
       <c r="T72">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U72">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V72">
         <v>4.33</v>
@@ -9428,19 +9449,19 @@
         <v>5</v>
       </c>
       <c r="AB72">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC72">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD72">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE72">
         <v>1.67</v>
       </c>
       <c r="AF72">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG72">
         <v>2.7</v>
@@ -9449,13 +9470,13 @@
         <v>3.2</v>
       </c>
       <c r="AI72">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AJ72" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK72" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL72" s="3">
         <v>45851.83333333334</v>
@@ -9493,43 +9514,43 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L73">
         <v>1.96</v>
       </c>
       <c r="M73">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="N73">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="O73">
         <v>1.62</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q73">
         <v>2.38</v>
       </c>
       <c r="R73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S73">
         <v>3.2</v>
       </c>
       <c r="T73">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U73">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V73">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W73">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -9538,40 +9559,40 @@
         <v>11</v>
       </c>
       <c r="Z73">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA73">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB73">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC73">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AD73">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="AE73">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AF73">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH73">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI73">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AJ73" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK73" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL73" s="3">
         <v>45851.83333333334</v>
@@ -9609,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L74">
         <v>2.06</v>
@@ -9684,10 +9705,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ74" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK74" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL74" s="3">
         <v>45851.83333333334</v>
@@ -9725,25 +9746,25 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L75">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="M75">
-        <v>3.01</v>
+        <v>3.64</v>
       </c>
       <c r="N75">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="O75">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="P75">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="Q75">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R75">
         <v>1.44</v>
@@ -9752,58 +9773,58 @@
         <v>2.6</v>
       </c>
       <c r="T75">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U75">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V75">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W75">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="Z75">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA75">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AB75">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AC75">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AD75">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AE75">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF75">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AG75">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH75">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="AI75">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ75" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK75" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL75" s="3">
         <v>45851.85416666666</v>
@@ -9841,85 +9862,85 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L76">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="M76">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N76">
-        <v>5.82</v>
+        <v>3.57</v>
       </c>
       <c r="O76">
+        <v>1.87</v>
+      </c>
+      <c r="P76">
+        <v>7</v>
+      </c>
+      <c r="Q76">
+        <v>2.3</v>
+      </c>
+      <c r="R76">
         <v>1.44</v>
       </c>
-      <c r="P76">
-        <v>7.25</v>
-      </c>
-      <c r="Q76">
-        <v>3.25</v>
-      </c>
-      <c r="R76">
-        <v>1.47</v>
-      </c>
       <c r="S76">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="T76">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="U76">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V76">
         <v>8</v>
       </c>
       <c r="W76">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y76">
         <v>7.5</v>
       </c>
       <c r="Z76">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AA76">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AB76">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC76">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AD76">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AE76">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF76">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG76">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH76">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AI76">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ76" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK76" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL76" s="3">
         <v>45851.85416666666</v>
@@ -9957,22 +9978,22 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L77">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M77">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="N77">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O77">
         <v>1.8</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q77">
         <v>2.05</v>
@@ -9981,19 +10002,19 @@
         <v>1.22</v>
       </c>
       <c r="S77">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T77">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U77">
         <v>1.62</v>
       </c>
       <c r="V77">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W77">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -10002,40 +10023,40 @@
         <v>11</v>
       </c>
       <c r="Z77">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA77">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB77">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC77">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD77">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE77">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF77">
         <v>1.45</v>
       </c>
       <c r="AG77">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AH77">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AI77">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AJ77" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK77" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL77" s="3">
         <v>45851.85416666666</v>
@@ -10073,25 +10094,25 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P78">
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R78">
         <v>1.22</v>
@@ -10100,58 +10121,58 @@
         <v>3.6</v>
       </c>
       <c r="T78">
+        <v>2.17</v>
+      </c>
+      <c r="U78">
+        <v>1.62</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>1.14</v>
+      </c>
+      <c r="AA78">
+        <v>4.5</v>
+      </c>
+      <c r="AB78">
+        <v>1.44</v>
+      </c>
+      <c r="AC78">
+        <v>2.45</v>
+      </c>
+      <c r="AD78">
         <v>2.1</v>
       </c>
-      <c r="U78">
-        <v>1.68</v>
-      </c>
-      <c r="V78">
-        <v>4.33</v>
-      </c>
-      <c r="W78">
-        <v>1.18</v>
-      </c>
-      <c r="X78">
-        <v>0</v>
-      </c>
-      <c r="Y78">
-        <v>0</v>
-      </c>
-      <c r="Z78">
-        <v>1.11</v>
-      </c>
-      <c r="AA78">
-        <v>4.8</v>
-      </c>
-      <c r="AB78">
-        <v>1.42</v>
-      </c>
-      <c r="AC78">
-        <v>2.59</v>
-      </c>
-      <c r="AD78">
-        <v>2.06</v>
-      </c>
       <c r="AE78">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF78">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AG78">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="AH78">
         <v>3.3</v>
       </c>
       <c r="AI78">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AJ78" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK78" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL78" s="3">
         <v>45851.875</v>
@@ -10165,16 +10186,16 @@
         <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D79" t="s">
         <v>86</v>
       </c>
       <c r="E79" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="F79" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10189,85 +10210,85 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L79">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="M79">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="N79">
-        <v>2.85</v>
+        <v>7.5</v>
       </c>
       <c r="O79">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q79">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="R79">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="S79">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="T79">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="U79">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="V79">
-        <v>4.75</v>
+        <v>11</v>
       </c>
       <c r="W79">
+        <v>1.05</v>
+      </c>
+      <c r="X79">
+        <v>1.1</v>
+      </c>
+      <c r="Y79">
+        <v>6.5</v>
+      </c>
+      <c r="Z79">
+        <v>1.45</v>
+      </c>
+      <c r="AA79">
+        <v>2.5</v>
+      </c>
+      <c r="AB79">
+        <v>2.6</v>
+      </c>
+      <c r="AC79">
+        <v>1.48</v>
+      </c>
+      <c r="AD79">
+        <v>5.25</v>
+      </c>
+      <c r="AE79">
         <v>1.15</v>
       </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>0</v>
-      </c>
-      <c r="Z79">
-        <v>1.14</v>
-      </c>
-      <c r="AA79">
-        <v>4.5</v>
-      </c>
-      <c r="AB79">
-        <v>1.5</v>
-      </c>
-      <c r="AC79">
-        <v>2.3</v>
-      </c>
-      <c r="AD79">
-        <v>2.2</v>
-      </c>
-      <c r="AE79">
-        <v>1.55</v>
-      </c>
       <c r="AF79">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AG79">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AH79">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="AI79">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AJ79" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK79" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL79" s="3">
         <v>45851.875</v>
@@ -10281,16 +10302,16 @@
         <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D80" t="s">
         <v>86</v>
       </c>
       <c r="E80" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="F80" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10305,85 +10326,85 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L80">
+        <v>2.18</v>
+      </c>
+      <c r="M80">
+        <v>3.6</v>
+      </c>
+      <c r="N80">
+        <v>2.8</v>
+      </c>
+      <c r="O80">
+        <v>1.73</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>2.05</v>
+      </c>
+      <c r="R80">
+        <v>1.22</v>
+      </c>
+      <c r="S80">
+        <v>3.5</v>
+      </c>
+      <c r="T80">
+        <v>2.2</v>
+      </c>
+      <c r="U80">
+        <v>1.6</v>
+      </c>
+      <c r="V80">
+        <v>4.75</v>
+      </c>
+      <c r="W80">
+        <v>1.15</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>1.15</v>
+      </c>
+      <c r="AA80">
+        <v>4.75</v>
+      </c>
+      <c r="AB80">
         <v>1.5</v>
       </c>
-      <c r="M80">
-        <v>3.9</v>
-      </c>
-      <c r="N80">
-        <v>7.5</v>
-      </c>
-      <c r="O80">
-        <v>1.36</v>
-      </c>
-      <c r="P80">
-        <v>6.25</v>
-      </c>
-      <c r="Q80">
-        <v>4.5</v>
-      </c>
-      <c r="R80">
-        <v>1.57</v>
-      </c>
-      <c r="S80">
+      <c r="AC80">
+        <v>2.3</v>
+      </c>
+      <c r="AD80">
         <v>2.25</v>
       </c>
-      <c r="T80">
-        <v>3.75</v>
-      </c>
-      <c r="U80">
-        <v>1.25</v>
-      </c>
-      <c r="V80">
-        <v>11</v>
-      </c>
-      <c r="W80">
-        <v>1.05</v>
-      </c>
-      <c r="X80">
-        <v>1.1</v>
-      </c>
-      <c r="Y80">
-        <v>6.5</v>
-      </c>
-      <c r="Z80">
+      <c r="AE80">
+        <v>1.55</v>
+      </c>
+      <c r="AF80">
         <v>1.45</v>
       </c>
-      <c r="AA80">
-        <v>2.5</v>
-      </c>
-      <c r="AB80">
-        <v>2.6</v>
-      </c>
-      <c r="AC80">
-        <v>1.48</v>
-      </c>
-      <c r="AD80">
-        <v>5.25</v>
-      </c>
-      <c r="AE80">
-        <v>1.15</v>
-      </c>
-      <c r="AF80">
-        <v>2.75</v>
-      </c>
       <c r="AG80">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH80">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="AI80">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AJ80" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK80" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL80" s="3">
         <v>45851.875</v>
@@ -10421,31 +10442,31 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L81">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P81">
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R81">
         <v>1.22</v>
       </c>
       <c r="S81">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="T81">
         <v>2.05</v>
@@ -10454,10 +10475,10 @@
         <v>1.62</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -10472,34 +10493,34 @@
         <v>4.8</v>
       </c>
       <c r="AB81">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC81">
         <v>2.45</v>
       </c>
       <c r="AD81">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE81">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF81">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AG81">
-        <v>1.83</v>
+        <v>2.78</v>
       </c>
       <c r="AH81">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI81">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AJ81" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK81" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL81" s="3">
         <v>45851.875</v>
@@ -10537,7 +10558,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L82">
         <v>4.3</v>
@@ -10588,10 +10609,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
+        <v>1.75</v>
+      </c>
+      <c r="AC82">
         <v>1.85</v>
-      </c>
-      <c r="AC82">
-        <v>1.95</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -10612,10 +10633,10 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK82" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL82" s="3">
         <v>45851.91666666666</v>
@@ -10653,7 +10674,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L83">
         <v>1.95</v>
@@ -10677,16 +10698,16 @@
         <v>1.2</v>
       </c>
       <c r="S83">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T83">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U83">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V83">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="W83">
         <v>1.2</v>
@@ -10698,13 +10719,13 @@
         <v>0</v>
       </c>
       <c r="Z83">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AA83">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AB83">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC83">
         <v>2.6</v>
@@ -10716,22 +10737,22 @@
         <v>1.72</v>
       </c>
       <c r="AF83">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AG83">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH83">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AI83">
         <v>1.3</v>
       </c>
       <c r="AJ83" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AK83" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL83" s="3">
         <v>45851.95833333334</v>

--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="298">
   <si>
     <t>Date</t>
   </si>
@@ -280,39 +280,39 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Rockdale City Suns</t>
   </si>
   <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Sydney United</t>
+    <t>Ansan Greeners</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
   </si>
   <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Ansan Greeners</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
+    <t>Tallinna Kalev</t>
+  </si>
+  <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
@@ -325,51 +325,51 @@
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Gnistan</t>
+    <t>Värnamo</t>
   </si>
   <si>
     <t>AIK</t>
   </si>
   <si>
-    <t>Värnamo</t>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
   </si>
   <si>
     <t>Strømsgodset</t>
   </si>
   <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
@@ -394,15 +394,15 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
     <t>Alvarado</t>
   </si>
   <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
@@ -415,70 +415,76 @@
     <t>Criciúma</t>
   </si>
   <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
-    <t>Recoleta</t>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Botafogo PB</t>
   </si>
   <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Botafogo PB</t>
-  </si>
-  <si>
     <t>Minnesota United II</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
     <t>Argentinos Juniors</t>
   </si>
   <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>FC Cincinnati II</t>
+  </si>
+  <si>
     <t>Caxias</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>Figueirense</t>
   </si>
   <si>
     <t>York9 FC</t>
   </si>
   <si>
-    <t>FC Cincinnati II</t>
+    <t>St. Louis City</t>
+  </si>
+  <si>
+    <t>Orlando City II</t>
   </si>
   <si>
     <t>Inter Miami II</t>
   </si>
   <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
-    <t>St. Louis City</t>
-  </si>
-  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Atlanta United II</t>
   </si>
   <si>
-    <t>Fortaleza</t>
+    <t>Houston Dynamo FC II</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes II</t>
   </si>
   <si>
     <t>River Plate</t>
@@ -487,12 +493,6 @@
     <t>Colorado Rapids II</t>
   </si>
   <si>
-    <t>Houston Dynamo FC II</t>
-  </si>
-  <si>
-    <t>San Jose Earthquakes II</t>
-  </si>
-  <si>
     <t>Vancouver FC</t>
   </si>
   <si>
@@ -502,39 +502,39 @@
     <t>El Paso Locomotive</t>
   </si>
   <si>
+    <t>Sydney Olympic</t>
+  </si>
+  <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
-    <t>Sydney Olympic</t>
-  </si>
-  <si>
     <t>St George City FA</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
+    <t>Seoul E-Land</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
   </si>
   <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Seoul E-Land</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
     <t>Nanjing City</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
@@ -547,51 +547,51 @@
     <t>Zhetysu</t>
   </si>
   <si>
+    <t>Haka</t>
+  </si>
+  <si>
     <t>Okzhetpes</t>
   </si>
   <si>
-    <t>Haka</t>
+    <t>Djurgården</t>
   </si>
   <si>
     <t>Degerfors</t>
   </si>
   <si>
-    <t>Djurgården</t>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>HamKam</t>
   </si>
   <si>
     <t>Tromsø</t>
   </si>
   <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
     <t>KFUM</t>
   </si>
   <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
@@ -616,15 +616,15 @@
     <t>Viking</t>
   </si>
   <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
     <t>San Miguel</t>
   </si>
   <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
     <t>New England II</t>
   </si>
   <si>
@@ -637,70 +637,76 @@
     <t>Ferroviária</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Magallanes</t>
+    <t>San Martín San Juan</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Londrina</t>
   </si>
   <si>
     <t>Ituano</t>
   </si>
   <si>
-    <t>San Martín San Juan</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
     <t>Real Monarchs</t>
   </si>
   <si>
     <t>Loudoun United</t>
   </si>
   <si>
+    <t>Concepción</t>
+  </si>
+  <si>
     <t>Remo</t>
   </si>
   <si>
-    <t>Concepción</t>
-  </si>
-  <si>
     <t>Boca Juniors</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Huntsville City</t>
+  </si>
+  <si>
     <t>Anápolis</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Náutico</t>
   </si>
   <si>
     <t>Valour FC</t>
   </si>
   <si>
-    <t>Huntsville City</t>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>Carolina Core</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Carolina Core</t>
-  </si>
-  <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
     <t>Grêmio</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
-    <t>Ceará</t>
+    <t>North Texas</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Platense</t>
@@ -709,12 +715,6 @@
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>North Texas</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Cavalry FC</t>
   </si>
   <si>
@@ -730,36 +730,36 @@
     <t>['44', '75', '90+2']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>['64']</t>
   </si>
   <si>
-    <t>['76']</t>
-  </si>
-  <si>
     <t>['72']</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>['63', '83']</t>
+  </si>
+  <si>
+    <t>['27', '89']</t>
   </si>
   <si>
     <t>['38']</t>
   </si>
   <si>
-    <t>['63', '83']</t>
-  </si>
-  <si>
-    <t>['27', '89']</t>
-  </si>
-  <si>
     <t>['33', '57', '77']</t>
   </si>
   <si>
+    <t>['4', '43', '69']</t>
+  </si>
+  <si>
     <t>['12']</t>
   </si>
   <si>
-    <t>['4', '43', '69']</t>
-  </si>
-  <si>
     <t>['62', '78']</t>
   </si>
   <si>
@@ -769,33 +769,33 @@
     <t>['31', '41', '61']</t>
   </si>
   <si>
+    <t>['56', '71']</t>
+  </si>
+  <si>
     <t>['63', '72']</t>
   </si>
   <si>
-    <t>['56', '71']</t>
+    <t>['90+4']</t>
   </si>
   <si>
     <t>['30', '64', '90+2']</t>
   </si>
   <si>
-    <t>['90+4']</t>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['15', '45+8']</t>
   </si>
   <si>
     <t>['42', '68']</t>
   </si>
   <si>
-    <t>['15', '45+8']</t>
-  </si>
-  <si>
-    <t>['84']</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
-    <t>['45+2']</t>
-  </si>
-  <si>
     <t>['75', '58', '55']</t>
   </si>
   <si>
@@ -808,21 +808,45 @@
     <t>['17', '19', '45', '48']</t>
   </si>
   <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['71', '90+2']</t>
+  </si>
+  <si>
+    <t>['33', '55']</t>
+  </si>
+  <si>
+    <t>['18', '28', '77']</t>
+  </si>
+  <si>
+    <t>['44', '42']</t>
+  </si>
+  <si>
+    <t>['14', '50']</t>
+  </si>
+  <si>
+    <t>['11', '27', '86']</t>
+  </si>
+  <si>
+    <t>['18', '85', '87']</t>
+  </si>
+  <si>
     <t>['40', '17', '90+6', '90+3']</t>
   </si>
   <si>
     <t>['7', '69', '75']</t>
   </si>
   <si>
+    <t>['46', '90+1']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
     <t>['52']</t>
   </si>
   <si>
-    <t>['46', '90+1']</t>
-  </si>
-  <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['22']</t>
   </si>
   <si>
@@ -838,27 +862,27 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['3', '85']</t>
+  </si>
+  <si>
     <t>['9', '14', '90+6']</t>
   </si>
   <si>
+    <t>['4', '56', '90+5']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['90+13']</t>
+  </si>
+  <si>
     <t>['43', '86']</t>
   </si>
   <si>
-    <t>['4', '56', '90+5']</t>
-  </si>
-  <si>
-    <t>['44']</t>
-  </si>
-  <si>
-    <t>['90+13']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
-  </si>
-  <si>
-    <t>['3', '85']</t>
-  </si>
-  <si>
     <t>['43', '89']</t>
   </si>
   <si>
@@ -866,6 +890,24 @@
   </si>
   <si>
     <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['46', '83']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['6', '1', '37', '54']</t>
+  </si>
+  <si>
+    <t>['45+6', '67', '57']</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1500,7 @@
         <v>237</v>
       </c>
       <c r="AK2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL2" s="3">
         <v>45851</v>
@@ -1487,94 +1529,94 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="s">
         <v>235</v>
       </c>
       <c r="L3">
-        <v>2.15</v>
+        <v>5.3</v>
       </c>
       <c r="M3">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="N3">
-        <v>2.71</v>
+        <v>1.44</v>
       </c>
       <c r="O3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD3">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AE3">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AF3">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
         <v>238</v>
       </c>
       <c r="AK3" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="AL3" s="3">
         <v>45851.08333333334</v>
@@ -1600,10 +1642,10 @@
         <v>163</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1612,85 +1654,85 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L4">
-        <v>5.3</v>
+        <v>1.84</v>
       </c>
       <c r="M4">
-        <v>4.6</v>
+        <v>3.67</v>
       </c>
       <c r="N4">
-        <v>1.44</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB4">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AC4">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AD4">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AE4">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="s">
         <v>239</v>
       </c>
       <c r="AK4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL4" s="3">
         <v>45851.08333333334</v>
@@ -1719,94 +1761,94 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="s">
         <v>235</v>
       </c>
       <c r="L5">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="M5">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="N5">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="O5">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB5">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AC5">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AJ5" t="s">
         <v>240</v>
       </c>
       <c r="AK5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="AL5" s="3">
         <v>45851.08333333334</v>
@@ -1832,97 +1874,97 @@
         <v>165</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L6">
-        <v>1.84</v>
+        <v>2.58</v>
       </c>
       <c r="M6">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>2.33</v>
       </c>
       <c r="O6">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="P6">
-        <v>16.75</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>241</v>
       </c>
       <c r="AK6" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="AL6" s="3">
         <v>45851.08333333334</v>
@@ -1948,13 +1990,13 @@
         <v>166</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1963,22 +2005,22 @@
         <v>235</v>
       </c>
       <c r="L7">
-        <v>2.09</v>
+        <v>3.84</v>
       </c>
       <c r="M7">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N7">
-        <v>3.09</v>
+        <v>1.8</v>
       </c>
       <c r="O7">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P7">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="R7">
         <v>1.44</v>
@@ -2002,43 +2044,43 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AA7">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD7">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>242</v>
       </c>
       <c r="AK7" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AL7" s="3">
         <v>45851.29166666666</v>
@@ -2067,34 +2109,34 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
         <v>235</v>
       </c>
       <c r="L8">
-        <v>3.84</v>
+        <v>1.74</v>
       </c>
       <c r="M8">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>4.63</v>
       </c>
       <c r="O8">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="P8">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="R8">
         <v>1.44</v>
@@ -2103,10 +2145,10 @@
         <v>2.63</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -2118,43 +2160,43 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z8">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA8">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC8">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD8">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH8">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AI8">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ8" t="s">
         <v>243</v>
       </c>
       <c r="AK8" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AL8" s="3">
         <v>45851.29166666666</v>
@@ -2180,7 +2222,7 @@
         <v>168</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2189,28 +2231,28 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="s">
         <v>235</v>
       </c>
       <c r="L9">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="M9">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="N9">
-        <v>4.63</v>
+        <v>3.09</v>
       </c>
       <c r="O9">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2219,10 +2261,10 @@
         <v>2.63</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -2234,43 +2276,43 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Z9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AA9">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB9">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC9">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD9">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AE9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH9">
-        <v>6.95</v>
+        <v>7.7</v>
       </c>
       <c r="AI9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>244</v>
       </c>
       <c r="AK9" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AL9" s="3">
         <v>45851.29166666666</v>
@@ -2383,10 +2425,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK10" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AL10" s="3">
         <v>45851.33333333334</v>
@@ -2502,7 +2544,7 @@
         <v>245</v>
       </c>
       <c r="AK11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AL11" s="3">
         <v>45851.33333333334</v>
@@ -2516,7 +2558,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>86</v>
@@ -2528,97 +2570,97 @@
         <v>171</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="s">
         <v>235</v>
       </c>
       <c r="L12">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="M12">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="N12">
-        <v>4.75</v>
+        <v>1.97</v>
       </c>
       <c r="O12">
+        <v>2.13</v>
+      </c>
+      <c r="P12">
+        <v>19</v>
+      </c>
+      <c r="Q12">
+        <v>1.68</v>
+      </c>
+      <c r="R12">
+        <v>1.23</v>
+      </c>
+      <c r="S12">
+        <v>3.9</v>
+      </c>
+      <c r="T12">
+        <v>2.1</v>
+      </c>
+      <c r="U12">
+        <v>1.65</v>
+      </c>
+      <c r="V12">
+        <v>4.6</v>
+      </c>
+      <c r="W12">
+        <v>1.17</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>17</v>
+      </c>
+      <c r="Z12">
+        <v>1.11</v>
+      </c>
+      <c r="AA12">
+        <v>5</v>
+      </c>
+      <c r="AB12">
+        <v>1.5</v>
+      </c>
+      <c r="AC12">
+        <v>2.45</v>
+      </c>
+      <c r="AD12">
+        <v>2.15</v>
+      </c>
+      <c r="AE12">
+        <v>1.62</v>
+      </c>
+      <c r="AF12">
         <v>1.4</v>
       </c>
-      <c r="P12">
-        <v>10.75</v>
-      </c>
-      <c r="Q12">
-        <v>3.4</v>
-      </c>
-      <c r="R12">
-        <v>1.42</v>
-      </c>
-      <c r="S12">
-        <v>2.75</v>
-      </c>
-      <c r="T12">
-        <v>2.95</v>
-      </c>
-      <c r="U12">
-        <v>1.36</v>
-      </c>
-      <c r="V12">
-        <v>7</v>
-      </c>
-      <c r="W12">
-        <v>1.07</v>
-      </c>
-      <c r="X12">
-        <v>1.06</v>
-      </c>
-      <c r="Y12">
-        <v>8.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.33</v>
-      </c>
-      <c r="AA12">
-        <v>3</v>
-      </c>
-      <c r="AB12">
-        <v>1.98</v>
-      </c>
-      <c r="AC12">
-        <v>1.7</v>
-      </c>
-      <c r="AD12">
-        <v>3.4</v>
-      </c>
-      <c r="AE12">
-        <v>1.25</v>
-      </c>
-      <c r="AF12">
-        <v>2</v>
-      </c>
       <c r="AG12">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AH12">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AI12">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
         <v>246</v>
       </c>
       <c r="AK12" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="AL12" s="3">
         <v>45851.35416666666</v>
@@ -2632,7 +2674,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>86</v>
@@ -2644,97 +2686,97 @@
         <v>172</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="s">
         <v>235</v>
       </c>
       <c r="L13">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="M13">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="N13">
-        <v>1.97</v>
+        <v>4.75</v>
       </c>
       <c r="O13">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="P13">
-        <v>19</v>
+        <v>10.75</v>
       </c>
       <c r="Q13">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="R13">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S13">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="T13">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="U13">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="V13">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="Z13">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB13">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AC13">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AD13">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AE13">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH13">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AI13">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AJ13" t="s">
         <v>247</v>
       </c>
       <c r="AK13" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="AL13" s="3">
         <v>45851.35416666666</v>
@@ -2850,7 +2892,7 @@
         <v>248</v>
       </c>
       <c r="AK14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL14" s="3">
         <v>45851.375</v>
@@ -2966,7 +3008,7 @@
         <v>249</v>
       </c>
       <c r="AK15" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AL15" s="3">
         <v>45851.375</v>
@@ -3079,10 +3121,10 @@
         <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
+        <v>238</v>
+      </c>
+      <c r="AK16" t="s">
         <v>239</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>241</v>
       </c>
       <c r="AL16" s="3">
         <v>45851.39583333334</v>
@@ -3198,7 +3240,7 @@
         <v>250</v>
       </c>
       <c r="AK17" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="AL17" s="3">
         <v>45851.41666666666</v>
@@ -3212,7 +3254,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>86</v>
@@ -3227,94 +3269,94 @@
         <v>2</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="s">
         <v>235</v>
       </c>
       <c r="L18">
-        <v>1.35</v>
+        <v>2.19</v>
       </c>
       <c r="M18">
-        <v>4.38</v>
+        <v>3.79</v>
       </c>
       <c r="N18">
-        <v>7.04</v>
+        <v>3.14</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="P18">
-        <v>9.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="Q18">
-        <v>3.28</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S18">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U18">
+        <v>1.55</v>
+      </c>
+      <c r="V18">
+        <v>5</v>
+      </c>
+      <c r="W18">
+        <v>1.15</v>
+      </c>
+      <c r="X18">
+        <v>1.04</v>
+      </c>
+      <c r="Y18">
+        <v>15</v>
+      </c>
+      <c r="Z18">
+        <v>1.2</v>
+      </c>
+      <c r="AA18">
+        <v>5.08</v>
+      </c>
+      <c r="AB18">
+        <v>1.57</v>
+      </c>
+      <c r="AC18">
+        <v>2.25</v>
+      </c>
+      <c r="AD18">
+        <v>2.49</v>
+      </c>
+      <c r="AE18">
         <v>1.5</v>
       </c>
-      <c r="V18">
-        <v>5.65</v>
-      </c>
-      <c r="W18">
-        <v>1.11</v>
-      </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
-      <c r="Y18">
-        <v>9.1</v>
-      </c>
-      <c r="Z18">
-        <v>1.19</v>
-      </c>
-      <c r="AA18">
-        <v>3.9</v>
-      </c>
-      <c r="AB18">
-        <v>1.77</v>
-      </c>
-      <c r="AC18">
-        <v>2.06</v>
-      </c>
-      <c r="AD18">
-        <v>2.9</v>
-      </c>
-      <c r="AE18">
-        <v>1.38</v>
-      </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AH18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI18">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ18" t="s">
         <v>251</v>
       </c>
       <c r="AK18" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="AL18" s="3">
         <v>45851.41666666666</v>
@@ -3328,7 +3370,7 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>86</v>
@@ -3343,94 +3385,94 @@
         <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
         <v>235</v>
       </c>
       <c r="L19">
-        <v>2.19</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
-        <v>3.79</v>
+        <v>4.38</v>
       </c>
       <c r="N19">
-        <v>3.14</v>
+        <v>7.04</v>
       </c>
       <c r="O19">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="P19">
-        <v>12.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q19">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="R19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="T19">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="V19">
+        <v>5.65</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>9.1</v>
+      </c>
+      <c r="Z19">
+        <v>1.19</v>
+      </c>
+      <c r="AA19">
+        <v>3.9</v>
+      </c>
+      <c r="AB19">
+        <v>1.77</v>
+      </c>
+      <c r="AC19">
+        <v>2.06</v>
+      </c>
+      <c r="AD19">
+        <v>2.9</v>
+      </c>
+      <c r="AE19">
+        <v>1.38</v>
+      </c>
+      <c r="AF19">
+        <v>1.85</v>
+      </c>
+      <c r="AG19">
+        <v>1.83</v>
+      </c>
+      <c r="AH19">
         <v>5</v>
       </c>
-      <c r="W19">
-        <v>1.15</v>
-      </c>
-      <c r="X19">
-        <v>1.04</v>
-      </c>
-      <c r="Y19">
-        <v>15</v>
-      </c>
-      <c r="Z19">
-        <v>1.2</v>
-      </c>
-      <c r="AA19">
-        <v>5.08</v>
-      </c>
-      <c r="AB19">
-        <v>1.57</v>
-      </c>
-      <c r="AC19">
-        <v>2.25</v>
-      </c>
-      <c r="AD19">
-        <v>2.49</v>
-      </c>
-      <c r="AE19">
-        <v>1.5</v>
-      </c>
-      <c r="AF19">
-        <v>1.51</v>
-      </c>
-      <c r="AG19">
-        <v>2.45</v>
-      </c>
-      <c r="AH19">
-        <v>4</v>
-      </c>
       <c r="AI19">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ19" t="s">
         <v>252</v>
       </c>
       <c r="AK19" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="AL19" s="3">
         <v>45851.41666666666</v>
@@ -3456,13 +3498,13 @@
         <v>179</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3471,22 +3513,22 @@
         <v>235</v>
       </c>
       <c r="L20">
-        <v>1.51</v>
+        <v>3.82</v>
       </c>
       <c r="M20">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="N20">
-        <v>5.3</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="R20">
         <v>1.36</v>
@@ -3501,52 +3543,52 @@
         <v>1.4</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>1.3</v>
       </c>
       <c r="AA20">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC20">
+        <v>1.79</v>
+      </c>
+      <c r="AD20">
+        <v>3.45</v>
+      </c>
+      <c r="AE20">
+        <v>1.3</v>
+      </c>
+      <c r="AF20">
         <v>1.8</v>
       </c>
-      <c r="AD20">
-        <v>3.25</v>
-      </c>
-      <c r="AE20">
-        <v>1.35</v>
-      </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>1.95</v>
       </c>
-      <c r="AG20">
-        <v>1.8</v>
-      </c>
       <c r="AH20">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI20">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
         <v>253</v>
       </c>
       <c r="AK20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL20" s="3">
         <v>45851.47916666666</v>
@@ -3572,13 +3614,13 @@
         <v>180</v>
       </c>
       <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>1</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3587,22 +3629,22 @@
         <v>235</v>
       </c>
       <c r="L21">
-        <v>3.82</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
-        <v>3.37</v>
+        <v>3.76</v>
       </c>
       <c r="N21">
-        <v>1.78</v>
+        <v>5.3</v>
       </c>
       <c r="O21">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="P21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="R21">
         <v>1.36</v>
@@ -3617,52 +3659,52 @@
         <v>1.4</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>1.3</v>
       </c>
       <c r="AA21">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AB21">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD21">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AE21">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF21">
+        <v>1.95</v>
+      </c>
+      <c r="AG21">
         <v>1.8</v>
       </c>
-      <c r="AG21">
-        <v>1.95</v>
-      </c>
       <c r="AH21">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ21" t="s">
         <v>254</v>
       </c>
       <c r="AK21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL21" s="3">
         <v>45851.47916666666</v>
@@ -3676,7 +3718,7 @@
         <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
         <v>86</v>
@@ -3688,97 +3730,97 @@
         <v>181</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="s">
         <v>235</v>
       </c>
       <c r="L22">
-        <v>3.38</v>
+        <v>5.3</v>
       </c>
       <c r="M22">
-        <v>3.27</v>
+        <v>3.9</v>
       </c>
       <c r="N22">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="O22">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="P22">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
+        <v>1.4</v>
+      </c>
+      <c r="S22">
+        <v>2.8</v>
+      </c>
+      <c r="T22">
+        <v>2.9</v>
+      </c>
+      <c r="U22">
+        <v>1.36</v>
+      </c>
+      <c r="V22">
+        <v>8</v>
+      </c>
+      <c r="W22">
+        <v>1.06</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>9</v>
+      </c>
+      <c r="Z22">
         <v>1.33</v>
       </c>
-      <c r="S22">
-        <v>3.25</v>
-      </c>
-      <c r="T22">
-        <v>2.5</v>
-      </c>
-      <c r="U22">
-        <v>1.5</v>
-      </c>
-      <c r="V22">
-        <v>6.5</v>
-      </c>
-      <c r="W22">
-        <v>1.11</v>
-      </c>
-      <c r="X22">
-        <v>1.05</v>
-      </c>
-      <c r="Y22">
-        <v>9.5</v>
-      </c>
-      <c r="Z22">
+      <c r="AA22">
+        <v>3.2</v>
+      </c>
+      <c r="AB22">
+        <v>1.99</v>
+      </c>
+      <c r="AC22">
+        <v>1.75</v>
+      </c>
+      <c r="AD22">
+        <v>3.4</v>
+      </c>
+      <c r="AE22">
         <v>1.25</v>
       </c>
-      <c r="AA22">
-        <v>3.85</v>
-      </c>
-      <c r="AB22">
-        <v>1.54</v>
-      </c>
-      <c r="AC22">
-        <v>2.3</v>
-      </c>
-      <c r="AD22">
-        <v>2.31</v>
-      </c>
-      <c r="AE22">
-        <v>1.62</v>
-      </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG22">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AH22">
-        <v>5.25</v>
+        <v>6.85</v>
       </c>
       <c r="AI22">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AJ22" t="s">
         <v>255</v>
       </c>
       <c r="AK22" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="AL22" s="3">
         <v>45851.5</v>
@@ -3792,7 +3834,7 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -3807,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3819,82 +3861,82 @@
         <v>235</v>
       </c>
       <c r="L23">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK23" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="AL23" s="3">
         <v>45851.5</v>
@@ -3920,16 +3962,16 @@
         <v>183</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
         <v>235</v>
@@ -4007,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="AK24" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="AL24" s="3">
         <v>45851.5</v>
@@ -4024,7 +4066,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
         <v>86</v>
@@ -4036,97 +4078,97 @@
         <v>184</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="s">
         <v>235</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ25" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AK25" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="AL25" s="3">
         <v>45851.5</v>
@@ -4140,7 +4182,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>86</v>
@@ -4152,97 +4194,97 @@
         <v>185</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
         <v>1</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="s">
         <v>235</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ26" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="AK26" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="AL26" s="3">
         <v>45851.5</v>
@@ -4256,7 +4298,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
         <v>86</v>
@@ -4268,97 +4310,97 @@
         <v>186</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="s">
         <v>235</v>
       </c>
       <c r="L27">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="AK27" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="AL27" s="3">
         <v>45851.5</v>
@@ -4372,7 +4414,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
         <v>86</v>
@@ -4384,7 +4426,7 @@
         <v>187</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4399,82 +4441,82 @@
         <v>235</v>
       </c>
       <c r="L28">
-        <v>5.3</v>
+        <v>2.68</v>
       </c>
       <c r="M28">
-        <v>3.9</v>
+        <v>3.18</v>
       </c>
       <c r="N28">
+        <v>2.32</v>
+      </c>
+      <c r="O28">
+        <v>2.05</v>
+      </c>
+      <c r="P28">
+        <v>12.5</v>
+      </c>
+      <c r="Q28">
+        <v>1.73</v>
+      </c>
+      <c r="R28">
+        <v>1.25</v>
+      </c>
+      <c r="S28">
+        <v>3.75</v>
+      </c>
+      <c r="T28">
+        <v>2.25</v>
+      </c>
+      <c r="U28">
+        <v>1.57</v>
+      </c>
+      <c r="V28">
+        <v>5.5</v>
+      </c>
+      <c r="W28">
+        <v>1.14</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>10</v>
+      </c>
+      <c r="Z28">
+        <v>1.18</v>
+      </c>
+      <c r="AA28">
+        <v>4.75</v>
+      </c>
+      <c r="AB28">
+        <v>1.67</v>
+      </c>
+      <c r="AC28">
+        <v>2</v>
+      </c>
+      <c r="AD28">
+        <v>2.25</v>
+      </c>
+      <c r="AE28">
+        <v>1.57</v>
+      </c>
+      <c r="AF28">
         <v>1.5</v>
       </c>
-      <c r="O28">
-        <v>2.52</v>
-      </c>
-      <c r="P28">
-        <v>8</v>
-      </c>
-      <c r="Q28">
-        <v>1.68</v>
-      </c>
-      <c r="R28">
-        <v>1.4</v>
-      </c>
-      <c r="S28">
-        <v>2.8</v>
-      </c>
-      <c r="T28">
-        <v>2.9</v>
-      </c>
-      <c r="U28">
-        <v>1.36</v>
-      </c>
-      <c r="V28">
-        <v>8</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.03</v>
-      </c>
-      <c r="Y28">
-        <v>9</v>
-      </c>
-      <c r="Z28">
-        <v>1.33</v>
-      </c>
-      <c r="AA28">
-        <v>3.2</v>
-      </c>
-      <c r="AB28">
-        <v>1.99</v>
-      </c>
-      <c r="AC28">
-        <v>1.75</v>
-      </c>
-      <c r="AD28">
-        <v>3.4</v>
-      </c>
-      <c r="AE28">
-        <v>1.25</v>
-      </c>
-      <c r="AF28">
-        <v>2.05</v>
-      </c>
       <c r="AG28">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH28">
-        <v>6.85</v>
+        <v>4.2</v>
       </c>
       <c r="AI28">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AJ28" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="AK28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL28" s="3">
         <v>45851.5</v>
@@ -4503,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -4587,10 +4629,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK29" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="AL29" s="3">
         <v>45851.5</v>
@@ -4703,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AK30" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="AL30" s="3">
         <v>45851.5</v>
@@ -4732,16 +4774,16 @@
         <v>190</v>
       </c>
       <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
         <v>1</v>
       </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
       <c r="I31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="s">
         <v>235</v>
@@ -4819,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="AK31" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="AL31" s="3">
         <v>45851.5</v>
@@ -4851,94 +4893,94 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="s">
         <v>235</v>
       </c>
       <c r="L32">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="M32">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="N32">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="O32">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="P32">
-        <v>12.5</v>
+        <v>9.25</v>
       </c>
       <c r="Q32">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="R32">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S32">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T32">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V32">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z32">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AA32">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="AB32">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC32">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AD32">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AE32">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH32">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AI32">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK32" t="s">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="AL32" s="3">
         <v>45851.5</v>
@@ -5054,7 +5096,7 @@
         <v>260</v>
       </c>
       <c r="AK33" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="AL33" s="3">
         <v>45851.52083333334</v>
@@ -5170,7 +5212,7 @@
         <v>261</v>
       </c>
       <c r="AK34" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL34" s="3">
         <v>45851.5625</v>
@@ -5286,7 +5328,7 @@
         <v>262</v>
       </c>
       <c r="AK35" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="AL35" s="3">
         <v>45851.5625</v>
@@ -5402,7 +5444,7 @@
         <v>263</v>
       </c>
       <c r="AK36" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="AL36" s="3">
         <v>45851.5625</v>
@@ -5428,19 +5470,19 @@
         <v>196</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L37">
         <v>1.65</v>
@@ -5515,10 +5557,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ37" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="AK37" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL37" s="3">
         <v>45851.56944444445</v>
@@ -5544,19 +5586,19 @@
         <v>197</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L38">
         <v>1.47</v>
@@ -5631,10 +5673,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ38" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="AK38" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="AL38" s="3">
         <v>45851.58333333334</v>
@@ -5660,19 +5702,19 @@
         <v>198</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -5747,10 +5789,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="AK39" t="s">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="AL39" s="3">
         <v>45851.59375</v>
@@ -5764,109 +5806,109 @@
         <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
         <v>86</v>
       </c>
       <c r="E40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L40">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M40">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N40">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="P40">
-        <v>14.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q40">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="R40">
+        <v>1.57</v>
+      </c>
+      <c r="S40">
+        <v>2.25</v>
+      </c>
+      <c r="T40">
+        <v>3.75</v>
+      </c>
+      <c r="U40">
         <v>1.25</v>
       </c>
-      <c r="S40">
-        <v>3.75</v>
-      </c>
-      <c r="T40">
-        <v>2.1</v>
-      </c>
-      <c r="U40">
-        <v>1.67</v>
-      </c>
       <c r="V40">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
+        <v>1.11</v>
+      </c>
+      <c r="Y40">
+        <v>6.25</v>
+      </c>
+      <c r="Z40">
+        <v>1.53</v>
+      </c>
+      <c r="AA40">
+        <v>2.3</v>
+      </c>
+      <c r="AB40">
+        <v>2.7</v>
+      </c>
+      <c r="AC40">
+        <v>1.44</v>
+      </c>
+      <c r="AD40">
+        <v>5.25</v>
+      </c>
+      <c r="AE40">
+        <v>1.15</v>
+      </c>
+      <c r="AF40">
+        <v>2.25</v>
+      </c>
+      <c r="AG40">
+        <v>1.57</v>
+      </c>
+      <c r="AH40">
+        <v>10</v>
+      </c>
+      <c r="AI40">
         <v>1.04</v>
       </c>
-      <c r="Y40">
-        <v>10</v>
-      </c>
-      <c r="Z40">
-        <v>1.17</v>
-      </c>
-      <c r="AA40">
-        <v>5</v>
-      </c>
-      <c r="AB40">
-        <v>1.57</v>
-      </c>
-      <c r="AC40">
-        <v>2.15</v>
-      </c>
-      <c r="AD40">
-        <v>2.27</v>
-      </c>
-      <c r="AE40">
-        <v>1.56</v>
-      </c>
-      <c r="AF40">
-        <v>1.4</v>
-      </c>
-      <c r="AG40">
-        <v>2.75</v>
-      </c>
-      <c r="AH40">
-        <v>3.7</v>
-      </c>
-      <c r="AI40">
-        <v>1.25</v>
-      </c>
       <c r="AJ40" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="AK40" t="s">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="AL40" s="3">
         <v>45851.59375</v>
@@ -5880,109 +5922,109 @@
         <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D41" t="s">
         <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M41">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N41">
+        <v>2.46</v>
+      </c>
+      <c r="O41">
+        <v>1.73</v>
+      </c>
+      <c r="P41">
+        <v>14.5</v>
+      </c>
+      <c r="Q41">
+        <v>2.05</v>
+      </c>
+      <c r="R41">
+        <v>1.25</v>
+      </c>
+      <c r="S41">
+        <v>3.75</v>
+      </c>
+      <c r="T41">
         <v>2.1</v>
       </c>
-      <c r="O41">
-        <v>2.88</v>
-      </c>
-      <c r="P41">
-        <v>5.75</v>
-      </c>
-      <c r="Q41">
+      <c r="U41">
         <v>1.67</v>
       </c>
-      <c r="R41">
+      <c r="V41">
+        <v>4.5</v>
+      </c>
+      <c r="W41">
+        <v>1.18</v>
+      </c>
+      <c r="X41">
+        <v>1.04</v>
+      </c>
+      <c r="Y41">
+        <v>10</v>
+      </c>
+      <c r="Z41">
+        <v>1.17</v>
+      </c>
+      <c r="AA41">
+        <v>5</v>
+      </c>
+      <c r="AB41">
         <v>1.57</v>
       </c>
-      <c r="S41">
-        <v>2.25</v>
-      </c>
-      <c r="T41">
-        <v>3.75</v>
-      </c>
-      <c r="U41">
+      <c r="AC41">
+        <v>2.15</v>
+      </c>
+      <c r="AD41">
+        <v>2.27</v>
+      </c>
+      <c r="AE41">
+        <v>1.56</v>
+      </c>
+      <c r="AF41">
+        <v>1.4</v>
+      </c>
+      <c r="AG41">
+        <v>2.75</v>
+      </c>
+      <c r="AH41">
+        <v>3.7</v>
+      </c>
+      <c r="AI41">
         <v>1.25</v>
       </c>
-      <c r="V41">
-        <v>13</v>
-      </c>
-      <c r="W41">
-        <v>1.04</v>
-      </c>
-      <c r="X41">
-        <v>1.11</v>
-      </c>
-      <c r="Y41">
-        <v>6.25</v>
-      </c>
-      <c r="Z41">
-        <v>1.53</v>
-      </c>
-      <c r="AA41">
-        <v>2.3</v>
-      </c>
-      <c r="AB41">
-        <v>2.7</v>
-      </c>
-      <c r="AC41">
-        <v>1.44</v>
-      </c>
-      <c r="AD41">
-        <v>5.25</v>
-      </c>
-      <c r="AE41">
-        <v>1.15</v>
-      </c>
-      <c r="AF41">
-        <v>2.25</v>
-      </c>
-      <c r="AG41">
-        <v>1.57</v>
-      </c>
-      <c r="AH41">
-        <v>10</v>
-      </c>
-      <c r="AI41">
-        <v>1.04</v>
-      </c>
       <c r="AJ41" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="AK41" t="s">
-        <v>241</v>
+        <v>293</v>
       </c>
       <c r="AL41" s="3">
         <v>45851.59375</v>
@@ -6008,97 +6050,97 @@
         <v>200</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L42">
-        <v>3.95</v>
+        <v>1.9</v>
       </c>
       <c r="M42">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O42">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R42">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="S42">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="T42">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="V42">
-        <v>15.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y42">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="Z42">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AA42">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AB42">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC42">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AD42">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AG42">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH42">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AI42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ42" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="AK42" t="s">
-        <v>241</v>
+        <v>294</v>
       </c>
       <c r="AL42" s="3">
         <v>45851.625</v>
@@ -6136,85 +6178,85 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L43">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="M43">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O43">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43">
+        <v>1.83</v>
+      </c>
+      <c r="R43">
+        <v>1.8</v>
+      </c>
+      <c r="S43">
         <v>1.91</v>
       </c>
-      <c r="R43">
-        <v>1.73</v>
-      </c>
-      <c r="S43">
-        <v>2.2</v>
-      </c>
       <c r="T43">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="U43">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V43">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="W43">
         <v>1.01</v>
       </c>
       <c r="X43">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y43">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Z43">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB43">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AD43">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AG43">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH43">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AI43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ43" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK43" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL43" s="3">
         <v>45851.625</v>
@@ -6240,73 +6282,73 @@
         <v>202</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L44">
-        <v>1.9</v>
+        <v>2.94</v>
       </c>
       <c r="M44">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="O44">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R44">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="S44">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="T44">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="U44">
         <v>1.18</v>
       </c>
       <c r="V44">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y44">
         <v>5</v>
       </c>
       <c r="Z44">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA44">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB44">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC44">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD44">
         <v>6</v>
@@ -6321,16 +6363,16 @@
         <v>1.53</v>
       </c>
       <c r="AH44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ44" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="AK44" t="s">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="AL44" s="3">
         <v>45851.625</v>
@@ -6356,19 +6398,19 @@
         <v>203</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L45">
         <v>1.95</v>
@@ -6443,10 +6485,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="AK45" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
       <c r="AL45" s="3">
         <v>45851.625</v>
@@ -6472,7 +6514,7 @@
         <v>204</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -6484,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L46">
         <v>2.17</v>
@@ -6559,10 +6601,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ46" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="AK46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL46" s="3">
         <v>45851.64583333334</v>
@@ -6675,10 +6717,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL47" s="3">
         <v>45851.65625</v>
@@ -6791,10 +6833,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ48" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK48" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL48" s="3">
         <v>45851.66666666666</v>
@@ -6808,7 +6850,7 @@
         <v>56</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s">
         <v>86</v>
@@ -6835,82 +6877,82 @@
         <v>236</v>
       </c>
       <c r="L49">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="M49">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N49">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="O49">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="P49">
-        <v>18.75</v>
+        <v>7</v>
       </c>
       <c r="Q49">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R49">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S49">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="T49">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="U49">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V49">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="W49">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Z49">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AA49">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AB49">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AC49">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="AD49">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AE49">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG49">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH49">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="AI49">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AJ49" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK49" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL49" s="3">
         <v>45851.66666666666</v>
@@ -6924,7 +6966,7 @@
         <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D50" t="s">
         <v>86</v>
@@ -6936,97 +6978,97 @@
         <v>208</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L50">
+        <v>1.57</v>
+      </c>
+      <c r="M50">
+        <v>3.75</v>
+      </c>
+      <c r="N50">
+        <v>4.75</v>
+      </c>
+      <c r="O50">
+        <v>1.4</v>
+      </c>
+      <c r="P50">
+        <v>18.75</v>
+      </c>
+      <c r="Q50">
+        <v>3.1</v>
+      </c>
+      <c r="R50">
+        <v>1.22</v>
+      </c>
+      <c r="S50">
+        <v>3.6</v>
+      </c>
+      <c r="T50">
         <v>2.05</v>
       </c>
-      <c r="M50">
-        <v>3.15</v>
-      </c>
-      <c r="N50">
-        <v>3.15</v>
-      </c>
-      <c r="O50">
-        <v>1.89</v>
-      </c>
-      <c r="P50">
-        <v>7</v>
-      </c>
-      <c r="Q50">
-        <v>2.25</v>
-      </c>
-      <c r="R50">
-        <v>1.42</v>
-      </c>
-      <c r="S50">
-        <v>2.7</v>
-      </c>
-      <c r="T50">
-        <v>2.85</v>
-      </c>
       <c r="U50">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V50">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z50">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AA50">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AB50">
-        <v>2.09</v>
+        <v>1.46</v>
       </c>
       <c r="AC50">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD50">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="AE50">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH50">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="AI50">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AJ50" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="AK50" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="AL50" s="3">
         <v>45851.66666666666</v>
@@ -7040,7 +7082,7 @@
         <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
         <v>86</v>
@@ -7067,82 +7109,82 @@
         <v>236</v>
       </c>
       <c r="L51">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH51">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI51">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK51" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL51" s="3">
         <v>45851.6875</v>
@@ -7183,82 +7225,82 @@
         <v>236</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AI52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ52" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK52" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL52" s="3">
         <v>45851.6875</v>
@@ -7272,7 +7314,7 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
         <v>86</v>
@@ -7299,82 +7341,82 @@
         <v>236</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH53">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AI53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL53" s="3">
         <v>45851.6875</v>
@@ -7394,10 +7436,10 @@
         <v>86</v>
       </c>
       <c r="E54" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F54" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7415,34 +7457,34 @@
         <v>236</v>
       </c>
       <c r="L54">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N54">
+        <v>4.75</v>
+      </c>
+      <c r="O54">
+        <v>1.5</v>
+      </c>
+      <c r="P54">
+        <v>6.5</v>
+      </c>
+      <c r="Q54">
         <v>3.25</v>
       </c>
-      <c r="O54">
-        <v>1.83</v>
-      </c>
-      <c r="P54">
-        <v>6</v>
-      </c>
-      <c r="Q54">
-        <v>2.4</v>
-      </c>
       <c r="R54">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S54">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T54">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V54">
         <v>11</v>
@@ -7451,34 +7493,34 @@
         <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y54">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Z54">
+        <v>1.48</v>
+      </c>
+      <c r="AA54">
+        <v>2.6</v>
+      </c>
+      <c r="AB54">
+        <v>2.5</v>
+      </c>
+      <c r="AC54">
         <v>1.5</v>
       </c>
-      <c r="AA54">
-        <v>2.38</v>
-      </c>
-      <c r="AB54">
-        <v>2.6</v>
-      </c>
-      <c r="AC54">
-        <v>1.48</v>
-      </c>
       <c r="AD54">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE54">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG54">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH54">
         <v>9.5</v>
@@ -7487,10 +7529,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ54" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK54" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL54" s="3">
         <v>45851.6875</v>
@@ -7504,16 +7546,16 @@
         <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
         <v>86</v>
       </c>
       <c r="E55" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F55" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7531,82 +7573,82 @@
         <v>236</v>
       </c>
       <c r="L55">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N55">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="Z55">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH55">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AI55">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL55" s="3">
         <v>45851.6875</v>
@@ -7620,16 +7662,16 @@
         <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
         <v>86</v>
       </c>
       <c r="E56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F56" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7647,82 +7689,82 @@
         <v>236</v>
       </c>
       <c r="L56">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="M56">
-        <v>3.5</v>
+        <v>2.71</v>
       </c>
       <c r="N56">
-        <v>4.75</v>
+        <v>4.28</v>
       </c>
       <c r="O56">
+        <v>1.62</v>
+      </c>
+      <c r="P56">
+        <v>7.5</v>
+      </c>
+      <c r="Q56">
+        <v>3</v>
+      </c>
+      <c r="R56">
         <v>1.5</v>
       </c>
-      <c r="P56">
-        <v>6.5</v>
-      </c>
-      <c r="Q56">
-        <v>3.25</v>
-      </c>
-      <c r="R56">
-        <v>1.53</v>
-      </c>
       <c r="S56">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U56">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V56">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W56">
         <v>1.05</v>
       </c>
       <c r="X56">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z56">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AA56">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC56">
         <v>1.5</v>
       </c>
       <c r="AD56">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF56">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG56">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH56">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AI56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL56" s="3">
         <v>45851.6875</v>
@@ -7835,10 +7877,10 @@
         <v>1.27</v>
       </c>
       <c r="AJ57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL57" s="3">
         <v>45851.70833333334</v>
@@ -7951,10 +7993,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ58" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK58" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL58" s="3">
         <v>45851.75</v>
@@ -7968,7 +8010,7 @@
         <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D59" t="s">
         <v>86</v>
@@ -7995,82 +8037,82 @@
         <v>236</v>
       </c>
       <c r="L59">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M59">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N59">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O59">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="P59">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="Q59">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="R59">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S59">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T59">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U59">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V59">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W59">
         <v>1.06</v>
       </c>
       <c r="X59">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Z59">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AA59">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB59">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AC59">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD59">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE59">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF59">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AG59">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AH59">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI59">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ59" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK59" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL59" s="3">
         <v>45851.77083333334</v>
@@ -8084,7 +8126,7 @@
         <v>60</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
         <v>86</v>
@@ -8111,82 +8153,82 @@
         <v>236</v>
       </c>
       <c r="L60">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M60">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N60">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="O60">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="P60">
-        <v>8.9</v>
+        <v>6.75</v>
       </c>
       <c r="Q60">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R60">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S60">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T60">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U60">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V60">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W60">
         <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y60">
+        <v>7</v>
+      </c>
+      <c r="Z60">
+        <v>1.4</v>
+      </c>
+      <c r="AA60">
+        <v>2.7</v>
+      </c>
+      <c r="AB60">
+        <v>2.3</v>
+      </c>
+      <c r="AC60">
+        <v>1.62</v>
+      </c>
+      <c r="AD60">
+        <v>4.5</v>
+      </c>
+      <c r="AE60">
+        <v>1.16</v>
+      </c>
+      <c r="AF60">
+        <v>2.05</v>
+      </c>
+      <c r="AG60">
+        <v>1.73</v>
+      </c>
+      <c r="AH60">
         <v>8.5</v>
       </c>
-      <c r="Z60">
-        <v>1.36</v>
-      </c>
-      <c r="AA60">
-        <v>3</v>
-      </c>
-      <c r="AB60">
-        <v>2.06</v>
-      </c>
-      <c r="AC60">
-        <v>1.7</v>
-      </c>
-      <c r="AD60">
-        <v>3.8</v>
-      </c>
-      <c r="AE60">
-        <v>1.21</v>
-      </c>
-      <c r="AF60">
-        <v>1.72</v>
-      </c>
-      <c r="AG60">
-        <v>1.95</v>
-      </c>
-      <c r="AH60">
-        <v>6.5</v>
-      </c>
       <c r="AI60">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AJ60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL60" s="3">
         <v>45851.77083333334</v>
@@ -8227,82 +8269,82 @@
         <v>236</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK61" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL61" s="3">
         <v>45851.78125</v>
@@ -8343,82 +8385,82 @@
         <v>236</v>
       </c>
       <c r="L62">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH62">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI62">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK62" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL62" s="3">
         <v>45851.78125</v>
@@ -8432,7 +8474,7 @@
         <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s">
         <v>86</v>
@@ -8459,82 +8501,82 @@
         <v>236</v>
       </c>
       <c r="L63">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="M63">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="N63">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O63">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="P63">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q63">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R63">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S63">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T63">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U63">
         <v>1.25</v>
       </c>
       <c r="V63">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="W63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y63">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="Z63">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AA63">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AB63">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC63">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AD63">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AG63">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH63">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AI63">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ63" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK63" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL63" s="3">
         <v>45851.79166666666</v>
@@ -8548,7 +8590,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D64" t="s">
         <v>86</v>
@@ -8575,82 +8617,82 @@
         <v>236</v>
       </c>
       <c r="L64">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="M64">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="N64">
         <v>3.6</v>
       </c>
       <c r="O64">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="P64">
-        <v>6.75</v>
+        <v>23</v>
       </c>
       <c r="Q64">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S64">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V64">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>6.95</v>
+        <v>9</v>
       </c>
       <c r="Z64">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AA64">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="AB64">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AC64">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AD64">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="AF64">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG64">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AH64">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AI64">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AJ64" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK64" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL64" s="3">
         <v>45851.79166666666</v>
@@ -8691,82 +8733,82 @@
         <v>236</v>
       </c>
       <c r="L65">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="M65">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="N65">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O65">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="P65">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q65">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="R65">
+        <v>1.55</v>
+      </c>
+      <c r="S65">
+        <v>2.4</v>
+      </c>
+      <c r="T65">
+        <v>3.6</v>
+      </c>
+      <c r="U65">
+        <v>1.25</v>
+      </c>
+      <c r="V65">
+        <v>11</v>
+      </c>
+      <c r="W65">
+        <v>1.02</v>
+      </c>
+      <c r="X65">
+        <v>1.06</v>
+      </c>
+      <c r="Y65">
+        <v>7</v>
+      </c>
+      <c r="Z65">
+        <v>1.47</v>
+      </c>
+      <c r="AA65">
+        <v>2.5</v>
+      </c>
+      <c r="AB65">
+        <v>2.5</v>
+      </c>
+      <c r="AC65">
         <v>1.44</v>
       </c>
-      <c r="S65">
-        <v>2.5</v>
-      </c>
-      <c r="T65">
-        <v>3.3</v>
-      </c>
-      <c r="U65">
-        <v>1.3</v>
-      </c>
-      <c r="V65">
-        <v>9.25</v>
-      </c>
-      <c r="W65">
-        <v>1.03</v>
-      </c>
-      <c r="X65">
-        <v>1.09</v>
-      </c>
-      <c r="Y65">
-        <v>6.5</v>
-      </c>
-      <c r="Z65">
-        <v>1.42</v>
-      </c>
-      <c r="AA65">
-        <v>2.49</v>
-      </c>
-      <c r="AB65">
-        <v>2.35</v>
-      </c>
-      <c r="AC65">
-        <v>1.5</v>
-      </c>
       <c r="AD65">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AG65">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH65">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AI65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK65" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL65" s="3">
         <v>45851.79166666666</v>
@@ -8780,7 +8822,7 @@
         <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D66" t="s">
         <v>86</v>
@@ -8807,82 +8849,82 @@
         <v>236</v>
       </c>
       <c r="L66">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M66">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="N66">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="O66">
+        <v>1.67</v>
+      </c>
+      <c r="P66">
+        <v>6.5</v>
+      </c>
+      <c r="Q66">
+        <v>2.75</v>
+      </c>
+      <c r="R66">
         <v>1.44</v>
       </c>
-      <c r="P66">
-        <v>12</v>
-      </c>
-      <c r="Q66">
-        <v>2.88</v>
-      </c>
-      <c r="R66">
-        <v>1.37</v>
-      </c>
       <c r="S66">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T66">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V66">
-        <v>7.5</v>
+        <v>9.25</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y66">
+        <v>6.5</v>
+      </c>
+      <c r="Z66">
+        <v>1.42</v>
+      </c>
+      <c r="AA66">
+        <v>2.49</v>
+      </c>
+      <c r="AB66">
+        <v>2.35</v>
+      </c>
+      <c r="AC66">
+        <v>1.5</v>
+      </c>
+      <c r="AD66">
+        <v>4.5</v>
+      </c>
+      <c r="AE66">
+        <v>1.14</v>
+      </c>
+      <c r="AF66">
+        <v>2.05</v>
+      </c>
+      <c r="AG66">
+        <v>1.62</v>
+      </c>
+      <c r="AH66">
         <v>9</v>
       </c>
-      <c r="Z66">
-        <v>1.3</v>
-      </c>
-      <c r="AA66">
-        <v>3.25</v>
-      </c>
-      <c r="AB66">
-        <v>1.88</v>
-      </c>
-      <c r="AC66">
-        <v>1.73</v>
-      </c>
-      <c r="AD66">
-        <v>3.1</v>
-      </c>
-      <c r="AE66">
-        <v>1.3</v>
-      </c>
-      <c r="AF66">
-        <v>1.8</v>
-      </c>
-      <c r="AG66">
-        <v>1.91</v>
-      </c>
-      <c r="AH66">
-        <v>6.5</v>
-      </c>
       <c r="AI66">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AJ66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL66" s="3">
         <v>45851.79166666666</v>
@@ -8896,7 +8938,7 @@
         <v>62</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D67" t="s">
         <v>86</v>
@@ -8923,37 +8965,37 @@
         <v>236</v>
       </c>
       <c r="L67">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M67">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="N67">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="O67">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="P67">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Q67">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R67">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S67">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T67">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U67">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V67">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W67">
         <v>1.08</v>
@@ -8965,40 +9007,40 @@
         <v>9</v>
       </c>
       <c r="Z67">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA67">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB67">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AC67">
+        <v>1.73</v>
+      </c>
+      <c r="AD67">
+        <v>3.1</v>
+      </c>
+      <c r="AE67">
+        <v>1.3</v>
+      </c>
+      <c r="AF67">
         <v>1.8</v>
       </c>
-      <c r="AD67">
-        <v>2.75</v>
-      </c>
-      <c r="AE67">
-        <v>1.41</v>
-      </c>
-      <c r="AF67">
-        <v>1.73</v>
-      </c>
       <c r="AG67">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH67">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI67">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AJ67" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK67" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL67" s="3">
         <v>45851.79166666666</v>
@@ -9012,7 +9054,7 @@
         <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D68" t="s">
         <v>86</v>
@@ -9039,22 +9081,22 @@
         <v>236</v>
       </c>
       <c r="L68">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M68">
-        <v>4.33</v>
+        <v>3.53</v>
       </c>
       <c r="N68">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O68">
         <v>1.67</v>
       </c>
       <c r="P68">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Q68">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R68">
         <v>1.25</v>
@@ -9063,58 +9105,58 @@
         <v>3.75</v>
       </c>
       <c r="T68">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U68">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V68">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W68">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z68">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AA68">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="AB68">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AC68">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD68">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AE68">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH68">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AI68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AJ68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL68" s="3">
         <v>45851.83333333334</v>
@@ -9179,10 +9221,10 @@
         <v>3.5</v>
       </c>
       <c r="T69">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U69">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V69">
         <v>4.75</v>
@@ -9197,28 +9239,28 @@
         <v>12</v>
       </c>
       <c r="Z69">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AA69">
         <v>4.5</v>
       </c>
       <c r="AB69">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC69">
         <v>2.3</v>
       </c>
       <c r="AD69">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AE69">
         <v>1.53</v>
       </c>
       <c r="AF69">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH69">
         <v>4</v>
@@ -9227,10 +9269,10 @@
         <v>1.22</v>
       </c>
       <c r="AJ69" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK69" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL69" s="3">
         <v>45851.83333333334</v>
@@ -9244,7 +9286,7 @@
         <v>63</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D70" t="s">
         <v>86</v>
@@ -9271,22 +9313,22 @@
         <v>236</v>
       </c>
       <c r="L70">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M70">
-        <v>3.53</v>
+        <v>4.33</v>
       </c>
       <c r="N70">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
         <v>1.67</v>
       </c>
       <c r="P70">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="Q70">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R70">
         <v>1.25</v>
@@ -9295,58 +9337,58 @@
         <v>3.75</v>
       </c>
       <c r="T70">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U70">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V70">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z70">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AA70">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="AB70">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AC70">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AD70">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AE70">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AF70">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH70">
-        <v>3.92</v>
+        <v>3.4</v>
       </c>
       <c r="AI70">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AJ70" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK70" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL70" s="3">
         <v>45851.83333333334</v>
@@ -9459,10 +9501,10 @@
         <v>1.01</v>
       </c>
       <c r="AJ71" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK71" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL71" s="3">
         <v>45851.85416666666</v>
@@ -9476,7 +9518,7 @@
         <v>64</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D72" t="s">
         <v>86</v>
@@ -9503,82 +9545,82 @@
         <v>236</v>
       </c>
       <c r="L72">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="M72">
-        <v>4.18</v>
+        <v>3.01</v>
       </c>
       <c r="N72">
-        <v>4.84</v>
+        <v>3.57</v>
       </c>
       <c r="O72">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="P72">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Q72">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="R72">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="S72">
-        <v>3.28</v>
+        <v>2.51</v>
       </c>
       <c r="T72">
-        <v>2.1</v>
+        <v>3.56</v>
       </c>
       <c r="U72">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="V72">
-        <v>4.33</v>
+        <v>9</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z72">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AA72">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB72">
-        <v>1.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC72">
-        <v>2.62</v>
+        <v>1.52</v>
       </c>
       <c r="AD72">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="AE72">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AG72">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="AH72">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="AI72">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AJ72" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK72" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL72" s="3">
         <v>45851.85416666666</v>
@@ -9592,7 +9634,7 @@
         <v>64</v>
       </c>
       <c r="C73" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D73" t="s">
         <v>86</v>
@@ -9619,82 +9661,82 @@
         <v>236</v>
       </c>
       <c r="L73">
-        <v>1.97</v>
+        <v>1.51</v>
       </c>
       <c r="M73">
-        <v>3.01</v>
+        <v>4.27</v>
       </c>
       <c r="N73">
-        <v>3.57</v>
+        <v>4.91</v>
       </c>
       <c r="O73">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="P73">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="R73">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="S73">
-        <v>2.51</v>
+        <v>3.28</v>
       </c>
       <c r="T73">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="U73">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="V73">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z73">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AA73">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="AB73">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC73">
-        <v>1.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD73">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>1.7</v>
       </c>
       <c r="AF73">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH73">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="AI73">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AJ73" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK73" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL73" s="3">
         <v>45851.85416666666</v>
@@ -9708,7 +9750,7 @@
         <v>65</v>
       </c>
       <c r="C74" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D74" t="s">
         <v>86</v>
@@ -9735,82 +9777,82 @@
         <v>236</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P74">
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL74" s="3">
         <v>45851.875</v>
@@ -9851,82 +9893,82 @@
         <v>236</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P75">
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S75">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T75">
+        <v>2.17</v>
+      </c>
+      <c r="U75">
+        <v>1.62</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>1.14</v>
+      </c>
+      <c r="AA75">
+        <v>4.5</v>
+      </c>
+      <c r="AB75">
+        <v>1.45</v>
+      </c>
+      <c r="AC75">
+        <v>2.4</v>
+      </c>
+      <c r="AD75">
         <v>2.1</v>
       </c>
-      <c r="U75">
-        <v>1.67</v>
-      </c>
-      <c r="V75">
-        <v>4.33</v>
-      </c>
-      <c r="W75">
-        <v>1.2</v>
-      </c>
-      <c r="X75">
-        <v>1.02</v>
-      </c>
-      <c r="Y75">
-        <v>13</v>
-      </c>
-      <c r="Z75">
-        <v>1.13</v>
-      </c>
-      <c r="AA75">
-        <v>5.5</v>
-      </c>
-      <c r="AB75">
-        <v>1.44</v>
-      </c>
-      <c r="AC75">
-        <v>2.63</v>
-      </c>
-      <c r="AD75">
-        <v>2.05</v>
-      </c>
       <c r="AE75">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF75">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AG75">
-        <v>2.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH75">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AI75">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AJ75" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK75" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL75" s="3">
         <v>45851.875</v>
@@ -9940,7 +9982,7 @@
         <v>65</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D76" t="s">
         <v>86</v>
@@ -9967,82 +10009,82 @@
         <v>236</v>
       </c>
       <c r="L76">
-        <v>2.09</v>
+        <v>1.5</v>
       </c>
       <c r="M76">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="N76">
-        <v>2.94</v>
+        <v>7.5</v>
       </c>
       <c r="O76">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q76">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="R76">
+        <v>1.57</v>
+      </c>
+      <c r="S76">
+        <v>2.25</v>
+      </c>
+      <c r="T76">
+        <v>3.75</v>
+      </c>
+      <c r="U76">
         <v>1.25</v>
       </c>
-      <c r="S76">
-        <v>3.75</v>
-      </c>
-      <c r="T76">
-        <v>2.1</v>
-      </c>
-      <c r="U76">
-        <v>1.67</v>
-      </c>
       <c r="V76">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="W76">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y76">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="Z76">
+        <v>1.45</v>
+      </c>
+      <c r="AA76">
+        <v>2.5</v>
+      </c>
+      <c r="AB76">
+        <v>2.6</v>
+      </c>
+      <c r="AC76">
+        <v>1.48</v>
+      </c>
+      <c r="AD76">
+        <v>5.25</v>
+      </c>
+      <c r="AE76">
         <v>1.15</v>
       </c>
-      <c r="AA76">
-        <v>5</v>
-      </c>
-      <c r="AB76">
-        <v>1.45</v>
-      </c>
-      <c r="AC76">
-        <v>2.5</v>
-      </c>
-      <c r="AD76">
-        <v>2.2</v>
-      </c>
-      <c r="AE76">
-        <v>1.62</v>
-      </c>
       <c r="AF76">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="AG76">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AH76">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AI76">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AJ76" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK76" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL76" s="3">
         <v>45851.875</v>
@@ -10062,10 +10104,10 @@
         <v>86</v>
       </c>
       <c r="E77" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F77" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10083,82 +10125,82 @@
         <v>236</v>
       </c>
       <c r="L77">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N77">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S77">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T77">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U77">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X77">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y77">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA77">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH77">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI77">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK77" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL77" s="3">
         <v>45851.875</v>
@@ -10199,82 +10241,82 @@
         <v>236</v>
       </c>
       <c r="L78">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P78">
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S78">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T78">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U78">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z78">
         <v>1.14</v>
       </c>
       <c r="AA78">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AB78">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC78">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AD78">
         <v>2.1</v>
       </c>
       <c r="AE78">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF78">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="AG78">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AH78">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AI78">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ78" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK78" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL78" s="3">
         <v>45851.875</v>
@@ -10387,10 +10429,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ79" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK79" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL79" s="3">
         <v>45851.91666666666</v>
@@ -10473,13 +10515,13 @@
         <v>15</v>
       </c>
       <c r="Z80">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AA80">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AB80">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC80">
         <v>2.75</v>
@@ -10491,22 +10533,22 @@
         <v>1.82</v>
       </c>
       <c r="AF80">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG80">
         <v>2.75</v>
       </c>
       <c r="AH80">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AI80">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AJ80" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK80" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AL80" s="3">
         <v>45851.95833333334</v>

--- a/jogos_2025-07-13.xlsx
+++ b/jogos_2025-07-13.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>2.58</v>
       </c>
       <c r="M3" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['7', '69', '75']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.24</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45851.08333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.58</v>
+        <v>5.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -966,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -985,12 +985,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['7', '69', '75']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45851.08333333334</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.3</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>3.78</v>
       </c>
       <c r="N5" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['40', '17', '90+6', '90+3']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45851.08333333334</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="N6" t="n">
-        <v>2.71</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.02</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['40', '17', '90+6', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
         <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45851.08333333334</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.74</v>
+        <v>3.84</v>
       </c>
       <c r="M8" t="n">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>4.63</v>
+        <v>1.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.44</v>
@@ -1467,59 +1467,59 @@
         <v>2.63</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['27', '89']</t>
+          <t>['63', '83']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['46', '90+1']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45851.29166666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.84</v>
+        <v>1.74</v>
       </c>
       <c r="M9" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8</v>
+        <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -1596,59 +1596,59 @@
         <v>2.63</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['27', '89']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['63', '83']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['46', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45851.29166666666</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>3.77</v>
       </c>
       <c r="O14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.4</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['62', '78']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['30', '60', '81']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['52', '85']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45851.375</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="M15" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X15" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.2</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['62', '78']</t>
+          <t>['30', '60', '81']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '85']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45851.375</v>
@@ -3223,54 +3223,54 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>3.38</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>3.27</v>
       </c>
       <c r="N22" t="n">
-        <v>5.8</v>
+        <v>1.93</v>
       </c>
       <c r="O22" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
         <v>2.5</v>
@@ -3279,53 +3279,53 @@
         <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['15', '45+8']</t>
+          <t>['42', '68']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '14', '90+6']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.13</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45851.5</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['15', '45+8']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45851.5</v>
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Huracán</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '56', '90+5']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45851.5</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,19 +3868,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['90+13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45851.5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['42', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['9', '14', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45851.5</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4215,20 +4215,20 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['43', '86']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45851.5</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huracán</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4344,20 +4344,20 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['4', '56', '90+5']</t>
+          <t>['43', '86']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45851.5</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Instituto</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['90+13']</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.68</v>
+        <v>5.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.18</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>6.45</v>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.25</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG32" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45851.5</v>
@@ -4761,119 +4761,119 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75', '58', '55']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '89']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45851.52083333334</v>
@@ -4890,119 +4890,119 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['75', '58', '55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['43', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45851.52083333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
       </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>2.05</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['17', '19', '45', '48']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['8', '83']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45851.5625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.56</v>
+        <v>3.35</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O38" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="P38" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.75</v>
+        <v>2.94</v>
       </c>
       <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X38" t="n">
-        <v>4.33</v>
+        <v>2.78</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['17', '19', '45', '48']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.2</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.88</v>
+        <v>1.81</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45851.5625</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T39" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.33</v>
       </c>
-      <c r="X39" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="AC39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '83']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.81</v>
+        <v>2.61</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45851.5625</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2</v>
       </c>
-      <c r="J44" t="n">
-        <v>3</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['11', '27', '86']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['6', '1', '37', '54']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45851.625</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" t="n">
         <v>2</v>
       </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.94</v>
+        <v>1.95</v>
       </c>
       <c r="M45" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2.25</v>
       </c>
-      <c r="O45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>6</v>
-      </c>
       <c r="AB45" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['14', '50']</t>
+          <t>['11', '27', '86']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['6', '1', '37', '54']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45851.625</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['14', '50']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI46" t="n">
         <v>2.5</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45851.625</v>
@@ -6844,94 +6844,94 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '90+4']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,19 +7093,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="M52" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O52" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="P52" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="S52" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="T52" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="U52" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="V52" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="X52" t="n">
-        <v>2.47</v>
+        <v>4.5</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.54</v>
+        <v>2.62</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB52" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['18', '85', '87']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>['45+6', '67', '57']</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
         <v>1.13</v>
       </c>
-      <c r="AC52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['43', '77']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH52" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ52" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45851.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N53" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O53" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S53" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="T53" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>['43', '77']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
         <v>1.33</v>
       </c>
-      <c r="V53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X53" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['37', '80']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH53" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45851.66666666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="M54" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N54" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="O54" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="P54" t="n">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.5</v>
+        <v>4.05</v>
       </c>
       <c r="R54" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S54" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="T54" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="U54" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="V54" t="n">
         <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="X54" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['18', '85', '87']</t>
+          <t>['37', '80']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['45+6', '67', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="AJ54" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45851.66666666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G56" t="n">
         <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="M56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O56" t="n">
         <v>3.5</v>
       </c>
-      <c r="N56" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S56" t="n">
         <v>2.4</v>
       </c>
-      <c r="P56" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>6</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T56" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U56" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V56" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W56" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X56" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Y56" t="n">
         <v>2.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA56" t="n">
         <v>4.75</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>['11', '45+2']</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ56" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>['4', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45851.6875</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O58" t="n">
         <v>2.63</v>
       </c>
-      <c r="M58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3.5</v>
-      </c>
       <c r="P58" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="R58" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S58" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T58" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U58" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V58" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W58" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="X58" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="AB58" t="n">
         <v>1.17</v>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['11', '45+2']</t>
+          <t>['4', '90+5']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45851.6875</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,22 +8512,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="M63" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O63" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.31</v>
+        <v>3.85</v>
       </c>
       <c r="R63" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S63" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T63" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="U63" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V63" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W63" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X63" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.8</v>
+        <v>4.38</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['1', '80']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45851.77083333334</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,22 +8641,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="M64" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X64" t="n">
         <v>3</v>
       </c>
-      <c r="N64" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.63</v>
-      </c>
       <c r="Y64" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.38</v>
+        <v>3.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['1', '80']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45851.77083333334</v>
@@ -8796,43 +8796,43 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P65" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q65" t="n">
         <v>4.5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S65" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U65" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V65" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W65" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X65" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Y65" t="n">
         <v>2.88</v>
@@ -8841,10 +8841,10 @@
         <v>1.4</v>
       </c>
       <c r="AA65" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC65" t="n">
         <v>2.38</v>
@@ -8863,13 +8863,13 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ65" t="n">
         <v>2.75</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,22 +8899,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="N66" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R66" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="S66" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="T66" t="n">
-        <v>2.5</v>
+        <v>3.94</v>
       </c>
       <c r="U66" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="V66" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="X66" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>['45+1', '45+4', '47']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>['22', '61']</t>
+          <t>['31', '90+7']</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI66" t="n">
         <v>1.67</v>
       </c>
-      <c r="AI66" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ66" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45851.79166666666</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,109 +9028,109 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y67" t="n">
         <v>2</v>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="M67" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R67" t="n">
+      <c r="Z67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI67" t="n">
         <v>1.53</v>
       </c>
-      <c r="S67" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T67" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X67" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>['31', '90+7']</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45851.79166666666</v>
@@ -9157,16 +9157,16 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -9183,65 +9183,65 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="M68" t="n">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="N68" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O68" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="P68" t="n">
         <v>1.95</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.88</v>
+        <v>5.75</v>
       </c>
       <c r="R68" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S68" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y68" t="n">
         <v>2.5</v>
       </c>
-      <c r="T68" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X68" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Z68" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AB68" t="n">
         <v>1.14</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -9253,13 +9253,13 @@
         <v>1.33</v>
       </c>
       <c r="AH68" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45851.79166666666</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,16 +9286,16 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="M69" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="N69" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
-        <v>3.15</v>
+        <v>2.37</v>
       </c>
       <c r="P69" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q69" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T69" t="n">
         <v>3.3</v>
       </c>
-      <c r="R69" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ69" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T69" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X69" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45851.79166666666</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,109 +9415,109 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="M70" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="O70" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P70" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="R70" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="S70" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="T70" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="U70" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="V70" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W70" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="X70" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AA70" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['45+1', '45+4', '47']</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '61']</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH70" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ70" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45851.79166666666</v>
@@ -9544,25 +9544,25 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G71" t="n">
         <v>3</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -9570,83 +9570,83 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="N71" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="O71" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P71" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="R71" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S71" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T71" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="U71" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V71" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W71" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X71" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>['36', '48', '55']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>['25', '17', '58']</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
         <v>1.17</v>
       </c>
-      <c r="X71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>['22', '54', '84']</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH71" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ71" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45851.83333333334</v>
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="M72" t="n">
-        <v>3.95</v>
+        <v>3.53</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O72" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="P72" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S72" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T72" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U72" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="V72" t="n">
         <v>1.02</v>
       </c>
       <c r="W72" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X72" t="n">
-        <v>5.75</v>
+        <v>5.36</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,16 +9766,16 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45851.83333333334</v>
@@ -9931,25 +9931,25 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -9957,83 +9957,83 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M74" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="N74" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="O74" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P74" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>['22', '54', '84']</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ74" t="n">
         <v>2.38</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S74" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T74" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V74" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X74" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>['36', '48', '55']</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>['25', '17', '58']</t>
-        </is>
-      </c>
-      <c r="AG74" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45851.83333333334</v>
@@ -10060,22 +10060,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -10086,83 +10086,83 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="M75" t="n">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="N75" t="n">
-        <v>3.57</v>
+        <v>4.8</v>
       </c>
       <c r="O75" t="n">
-        <v>3.17</v>
+        <v>2.31</v>
       </c>
       <c r="P75" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="R75" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S75" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T75" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U75" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V75" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W75" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>['33', '25', '54', '77']</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI75" t="n">
         <v>1.44</v>
       </c>
-      <c r="X75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AG75" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AJ75" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45851.85416666666</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,19 +10318,19 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>2</v>
@@ -10344,83 +10344,83 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="M77" t="n">
-        <v>3.12</v>
+        <v>4.36</v>
       </c>
       <c r="N77" t="n">
-        <v>4.8</v>
+        <v>5.46</v>
       </c>
       <c r="O77" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="P77" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="Q77" t="n">
         <v>5.5</v>
       </c>
       <c r="R77" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S77" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="T77" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="U77" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V77" t="n">
         <v>1.01</v>
       </c>
       <c r="W77" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="X77" t="n">
-        <v>3.1</v>
+        <v>6.05</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="Z77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC77" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA77" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD77" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>['33', '25', '54', '77']</t>
+          <t>['17', '45+1', '75']</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['57', '73', '85']</t>
         </is>
       </c>
       <c r="AG77" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AI77" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH77" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ77" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AK77" s="3" t="n">
         <v>45851.85416666666</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,22 +10447,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10473,83 +10473,83 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="O78" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R78" t="n">
         <v>1.5</v>
       </c>
-      <c r="M78" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="N78" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="O78" t="n">
-        <v>2</v>
-      </c>
-      <c r="P78" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1.25</v>
-      </c>
       <c r="S78" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="T78" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="U78" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH78" t="n">
         <v>1.62</v>
       </c>
-      <c r="V78" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X78" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>['17', '45+1', '75']</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>['57', '73', '85']</t>
-        </is>
-      </c>
-      <c r="AG78" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AI78" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AJ78" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK78" s="3" t="n">
         <v>45851.85416666666</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10723,7 +10723,7 @@
         <v>2</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -10731,83 +10731,83 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U80" t="n">
         <v>1.62</v>
       </c>
-      <c r="M80" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N80" t="n">
-        <v>6</v>
-      </c>
-      <c r="O80" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P80" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>7</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S80" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T80" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U80" t="n">
-        <v>1.25</v>
-      </c>
       <c r="V80" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="X80" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="AA80" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>['7', '39', '90+1']</t>
+          <t>['12', '53', '36']</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG80" t="n">
         <v>1.12</v>
       </c>
       <c r="AH80" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AJ80" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AK80" s="3" t="n">
         <v>45851.875</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,25 +10834,25 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -10860,83 +10860,83 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O81" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="P81" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.35</v>
+        <v>8.5</v>
       </c>
       <c r="R81" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U81" t="n">
         <v>1.25</v>
       </c>
-      <c r="S81" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T81" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1.67</v>
-      </c>
       <c r="V81" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W81" t="n">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="X81" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '39', '90+1']</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AH81" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK81" s="3" t="n">
         <v>45851.875</v>
@@ -10963,22 +10963,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -10989,83 +10989,83 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1.52</v>
+        <v>2.19</v>
       </c>
       <c r="P82" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="Q82" t="n">
-        <v>8.199999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="R82" t="n">
         <v>1.25</v>
       </c>
       <c r="S82" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T82" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U82" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W82" t="n">
         <v>1.14</v>
       </c>
       <c r="X82" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AA82" t="n">
         <v>2.1</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>['12', '53', '36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH82" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
         <v>45851.875</v>
